--- a/Grid/test_trøndelagsnettet.xlsx
+++ b/Grid/test_trøndelagsnettet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0348cbc925570652/Master/Kraftsystemer/Kraftsystemer-2/Grid/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b57458e082dedb4f/Dokumenter/EMIL 1. klasse høst/TET4205 Power system analysis 2/Kraftsystemer-2/Grid/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="18" documentId="11_057EBA57FA9E57F87E476CE1F4362D3B786B1A4C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE75181C-1E1D-4F2E-9CF4-6554412DA2D6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="754" yWindow="754" windowWidth="18515" windowHeight="10740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bus" sheetId="1" r:id="rId1"/>
@@ -753,15 +753,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -779,10 +776,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1071,9 +1064,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1114,7 +1107,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>30</v>
       </c>
@@ -1155,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>45</v>
       </c>
@@ -1196,7 +1189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>46</v>
       </c>
@@ -1237,7 +1230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>60</v>
       </c>
@@ -1278,7 +1271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>61</v>
       </c>
@@ -1319,7 +1312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>62</v>
       </c>
@@ -1360,7 +1353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>76</v>
       </c>
@@ -1401,7 +1394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>77</v>
       </c>
@@ -1442,7 +1435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>78</v>
       </c>
@@ -1483,7 +1476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>79</v>
       </c>
@@ -1524,7 +1517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>80</v>
       </c>
@@ -1565,7 +1558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>105</v>
       </c>
@@ -1606,7 +1599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>106</v>
       </c>
@@ -1647,7 +1640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>107</v>
       </c>
@@ -1688,7 +1681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>108</v>
       </c>
@@ -1729,7 +1722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>109</v>
       </c>
@@ -1770,7 +1763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>138</v>
       </c>
@@ -1811,7 +1804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>139</v>
       </c>
@@ -1852,7 +1845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>141</v>
       </c>
@@ -1893,7 +1886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>161</v>
       </c>
@@ -1934,7 +1927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>176</v>
       </c>
@@ -1983,9 +1976,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2020,7 +2013,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -2049,7 +2042,7 @@
         <v>8.8044759999999993</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -2078,7 +2071,7 @@
         <v>11.871930600000001</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -2107,7 +2100,7 @@
         <v>5.2955095999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -2136,7 +2129,7 @@
         <v>8.8866494000000031</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -2165,7 +2158,7 @@
         <v>10.0126685</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -2194,7 +2187,7 @@
         <v>11.08352</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -2223,7 +2216,7 @@
         <v>10.481959399999999</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -2252,7 +2245,7 @@
         <v>5.6666667000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -2281,7 +2274,7 @@
         <v>11.1900113</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -2310,7 +2303,7 @@
         <v>11.0058121</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -2339,7 +2332,7 @@
         <v>12.458487</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -2368,7 +2361,7 @@
         <v>5.9323598000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -2397,7 +2390,7 @@
         <v>12.426399999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>54</v>
       </c>
@@ -2426,7 +2419,7 @@
         <v>8.0306999999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -2455,7 +2448,7 @@
         <v>6.9432999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -2484,7 +2477,7 @@
         <v>8.9611000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -2513,7 +2506,7 @@
         <v>10.3950528</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -2542,7 +2535,7 @@
         <v>9.7151951999999984</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -2571,7 +2564,7 @@
         <v>11.439399999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>62</v>
       </c>
@@ -2600,7 +2593,7 @@
         <v>11.230700000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -2629,7 +2622,7 @@
         <v>7.2199947</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>64</v>
       </c>
@@ -2658,7 +2651,7 @@
         <v>5.5803419999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -2687,7 +2680,7 @@
         <v>9.3017813999999994</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -2716,7 +2709,7 @@
         <v>6.8948</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -2745,7 +2738,7 @@
         <v>11.1072278</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>68</v>
       </c>
@@ -2774,7 +2767,7 @@
         <v>7.8511770000000034</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -2803,7 +2796,7 @@
         <v>6.8848000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -2832,7 +2825,7 @@
         <v>7.2545709999999994</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -2861,7 +2854,7 @@
         <v>11.8285</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -2890,7 +2883,7 @@
         <v>9.7574403499999995</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -2919,7 +2912,7 @@
         <v>6.0833482000000014</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -2948,7 +2941,7 @@
         <v>7.4153287000000017</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -2977,7 +2970,7 @@
         <v>10.436579999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -3006,7 +2999,7 @@
         <v>12.036899999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -3035,7 +3028,7 @@
         <v>11.520841900000001</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>78</v>
       </c>
@@ -3064,7 +3057,7 @@
         <v>11.6968</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -3093,7 +3086,7 @@
         <v>11.239599999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>80</v>
       </c>
@@ -3122,7 +3115,7 @@
         <v>7.5333332999999989</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -3151,7 +3144,7 @@
         <v>8.9330416999999969</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -3180,7 +3173,7 @@
         <v>8.157</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -3209,7 +3202,7 @@
         <v>10.9664</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -3238,7 +3231,7 @@
         <v>6.6169454999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>85</v>
       </c>
@@ -3267,7 +3260,7 @@
         <v>6.5069116999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>86</v>
       </c>
@@ -3296,7 +3289,7 @@
         <v>11.5484121</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>87</v>
       </c>
@@ -3325,7 +3318,7 @@
         <v>6.5741103000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>88</v>
       </c>
@@ -3354,7 +3347,7 @@
         <v>5.8376893999999986</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>89</v>
       </c>
@@ -3383,7 +3376,7 @@
         <v>11.051768900000001</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>90</v>
       </c>
@@ -3412,7 +3405,7 @@
         <v>8.1743355999999991</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>91</v>
       </c>
@@ -3441,7 +3434,7 @@
         <v>11.763260900000001</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>92</v>
       </c>
@@ -3470,7 +3463,7 @@
         <v>5.8235750999999993</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>93</v>
       </c>
@@ -3499,7 +3492,7 @@
         <v>6.8139132</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>94</v>
       </c>
@@ -3528,7 +3521,7 @@
         <v>8.5725324999999994</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>95</v>
       </c>
@@ -3557,7 +3550,7 @@
         <v>6.9097999999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>96</v>
       </c>
@@ -3586,7 +3579,7 @@
         <v>6.0118764999999996</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>97</v>
       </c>
@@ -3615,7 +3608,7 @@
         <v>10.4582701</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>98</v>
       </c>
@@ -3644,7 +3637,7 @@
         <v>5.8372717999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>99</v>
       </c>
@@ -3673,7 +3666,7 @@
         <v>7.828136999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>100</v>
       </c>
@@ -3702,7 +3695,7 @@
         <v>6.15</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>101</v>
       </c>
@@ -3731,7 +3724,7 @@
         <v>11.04129</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>102</v>
       </c>
@@ -3760,7 +3753,7 @@
         <v>9.0890899999999988</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>103</v>
       </c>
@@ -3789,7 +3782,7 @@
         <v>5.5608660999999966</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>104</v>
       </c>
@@ -3818,7 +3811,7 @@
         <v>6.9358199999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>105</v>
       </c>
@@ -3847,7 +3840,7 @@
         <v>5.8543174000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>106</v>
       </c>
@@ -3876,7 +3869,7 @@
         <v>6.9920547000000024</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>107</v>
       </c>
@@ -3905,7 +3898,7 @@
         <v>9.8333333000000014</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>108</v>
       </c>
@@ -3934,7 +3927,7 @@
         <v>6.2766851000000008</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>109</v>
       </c>
@@ -3963,7 +3956,7 @@
         <v>6.5668392999999998</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>110</v>
       </c>
@@ -3992,7 +3985,7 @@
         <v>6.5005457999999994</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
         <v>111</v>
       </c>
@@ -4021,7 +4014,7 @@
         <v>6.5980089000000008</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>112</v>
       </c>
@@ -4050,7 +4043,7 @@
         <v>9.6333333000000021</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>113</v>
       </c>
@@ -4079,7 +4072,7 @@
         <v>8.6937046000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>114</v>
       </c>
@@ -4108,7 +4101,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
         <v>115</v>
       </c>
@@ -4137,7 +4130,7 @@
         <v>11.7372151</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>116</v>
       </c>
@@ -4166,7 +4159,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
         <v>117</v>
       </c>
@@ -4195,7 +4188,7 @@
         <v>10.0377767</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>118</v>
       </c>
@@ -4224,7 +4217,7 @@
         <v>6.5719160000000008</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>119</v>
       </c>
@@ -4253,7 +4246,7 @@
         <v>5.8013399999999997</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>120</v>
       </c>
@@ -4282,7 +4275,7 @@
         <v>9.0191520000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
         <v>121</v>
       </c>
@@ -4311,7 +4304,7 @@
         <v>9.6812501999999991</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>122</v>
       </c>
@@ -4340,7 +4333,7 @@
         <v>9.7131293000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>123</v>
       </c>
@@ -4369,7 +4362,7 @@
         <v>9.1879674999999992</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>124</v>
       </c>
@@ -4398,7 +4391,7 @@
         <v>5.4489538999999994</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>125</v>
       </c>
@@ -4427,7 +4420,7 @@
         <v>6.2465699999999984</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>126</v>
       </c>
@@ -4456,7 +4449,7 @@
         <v>10.981521600000001</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
         <v>127</v>
       </c>
@@ -4485,7 +4478,7 @@
         <v>11.006936400000001</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
         <v>128</v>
       </c>
@@ -4514,7 +4507,7 @@
         <v>5.1708737999999999</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
         <v>129</v>
       </c>
@@ -4543,7 +4536,7 @@
         <v>8.7299540000000011</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
         <v>130</v>
       </c>
@@ -4572,7 +4565,7 @@
         <v>9.1423079999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
         <v>131</v>
       </c>
@@ -4601,7 +4594,7 @@
         <v>8.0138783</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
         <v>132</v>
       </c>
@@ -4630,7 +4623,7 @@
         <v>10.0280798</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
         <v>133</v>
       </c>
@@ -4659,7 +4652,7 @@
         <v>6.2347906999999996</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
         <v>134</v>
       </c>
@@ -4688,7 +4681,7 @@
         <v>11.188310299999999</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
         <v>135</v>
       </c>
@@ -4717,7 +4710,7 @@
         <v>11.4618021</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
         <v>136</v>
       </c>
@@ -4746,7 +4739,7 @@
         <v>11.510163</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
         <v>137</v>
       </c>
@@ -4775,7 +4768,7 @@
         <v>8.8672097000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
         <v>138</v>
       </c>
@@ -4804,7 +4797,7 @@
         <v>11.4952627</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
         <v>139</v>
       </c>
@@ -4833,7 +4826,7 @@
         <v>9.8477710999999992</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
         <v>140</v>
       </c>
@@ -4862,7 +4855,7 @@
         <v>11.04129</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -4891,7 +4884,7 @@
         <v>9.8825433</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
         <v>142</v>
       </c>
@@ -4920,7 +4913,7 @@
         <v>9.0966266000000005</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
         <v>143</v>
       </c>
@@ -4949,7 +4942,7 @@
         <v>11.916895</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
         <v>144</v>
       </c>
@@ -4978,7 +4971,7 @@
         <v>8.0588759000000003</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
         <v>145</v>
       </c>
@@ -5007,7 +5000,7 @@
         <v>6.8477066000000004</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
         <v>146</v>
       </c>
@@ -5044,12 +5037,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="12" max="12" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>147</v>
       </c>
@@ -5086,11 +5079,11 @@
       <c r="L1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1166</v>
       </c>
@@ -5131,7 +5124,7 @@
         <v>10943</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1334</v>
       </c>
@@ -5172,7 +5165,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1335</v>
       </c>
@@ -5210,7 +5203,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1336</v>
       </c>
@@ -5251,7 +5244,7 @@
         <v>3343</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1165</v>
       </c>
@@ -5289,7 +5282,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1289</v>
       </c>
@@ -5327,7 +5320,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1290</v>
       </c>
@@ -5368,7 +5361,7 @@
         <v>343321</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1291</v>
       </c>
@@ -5406,7 +5399,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1173</v>
       </c>
@@ -5444,7 +5437,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>1174</v>
       </c>
@@ -5482,7 +5475,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>1292</v>
       </c>
@@ -5520,7 +5513,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>1175</v>
       </c>
@@ -5558,7 +5551,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>6798</v>
       </c>
@@ -5596,7 +5589,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>1288</v>
       </c>
@@ -5634,7 +5627,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>6562</v>
       </c>
@@ -5672,7 +5665,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>1293</v>
       </c>
@@ -5710,7 +5703,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>1176</v>
       </c>
@@ -5748,7 +5741,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>1317</v>
       </c>
@@ -5794,9 +5787,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>208</v>
       </c>
@@ -5819,7 +5812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>43</v>
       </c>
@@ -5842,7 +5835,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>44</v>
       </c>
@@ -5865,7 +5858,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>45</v>
       </c>
@@ -5888,7 +5881,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>46</v>
       </c>
@@ -5919,9 +5912,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>214</v>
       </c>

--- a/Grid/test_trøndelagsnettet.xlsx
+++ b/Grid/test_trøndelagsnettet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b57458e082dedb4f/Dokumenter/EMIL 1. klasse høst/TET4205 Power system analysis 2/Kraftsystemer-2/Grid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_057EBA57FA9E57F87E476CE1F4362D3B786B1A4C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE75181C-1E1D-4F2E-9CF4-6554412DA2D6}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_057EBA57FA9E57F87E476CE1F4362D3B786B1A4C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE410DF7-B8CF-4B1F-92A6-3E640775DBB2}"/>
   <bookViews>
-    <workbookView xWindow="754" yWindow="754" windowWidth="18515" windowHeight="10740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bus" sheetId="1" r:id="rId1"/>
@@ -776,6 +776,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1065,6 +1069,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="7" max="7" width="17.921875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
@@ -5039,6 +5046,8 @@
   <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="9" max="9" width="11.3046875" customWidth="1"/>
+    <col min="10" max="10" width="13.23046875" customWidth="1"/>
     <col min="12" max="12" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5788,6 +5797,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="22.3828125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">

--- a/Grid/test_trøndelagsnettet.xlsx
+++ b/Grid/test_trøndelagsnettet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0348cbc925570652/Master/Kraftsystemer/Kraftsystemer-2/Grid/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2d06795444358214/Dokumenter/Kraftsystemer2/Kraftsystemer-2/Grid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_057EBA57FA9E57F87E476CE1F4362D3B786B1A4C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE75181C-1E1D-4F2E-9CF4-6554412DA2D6}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="11_057EBA57FA9E57F87E476CE1F4362D3B786B1A4C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D0F19DB-79DD-49A2-B821-E57BDDFB7D4D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bus" sheetId="1" r:id="rId1"/>
@@ -693,6 +693,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -761,9 +764,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -779,10 +780,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1071,9 +1068,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1114,7 +1111,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>30</v>
       </c>
@@ -1142,8 +1139,8 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
-        <v>124.5229528220266</v>
+      <c r="J2" s="3">
+        <v>100</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1152,10 +1149,10 @@
         <v>30.622222356505979</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>45</v>
       </c>
@@ -1183,8 +1180,8 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
-        <v>303.73016438495603</v>
+      <c r="J3" s="3">
+        <v>300</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -1193,10 +1190,10 @@
         <v>1127.8018812523951</v>
       </c>
       <c r="M3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>46</v>
       </c>
@@ -1224,7 +1221,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="3">
         <v>0</v>
       </c>
       <c r="K4">
@@ -1237,7 +1234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>60</v>
       </c>
@@ -1265,7 +1262,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="3">
         <v>0</v>
       </c>
       <c r="K5">
@@ -1278,7 +1275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>61</v>
       </c>
@@ -1306,7 +1303,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="3">
         <v>0</v>
       </c>
       <c r="K6">
@@ -1319,7 +1316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>62</v>
       </c>
@@ -1347,8 +1344,8 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
-        <v>84.191307445671541</v>
+      <c r="J7" s="3">
+        <v>100</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -1357,10 +1354,10 @@
         <v>19.35034456687892</v>
       </c>
       <c r="M7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>76</v>
       </c>
@@ -1388,8 +1385,8 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8">
-        <v>34.077433966105147</v>
+      <c r="J8" s="3">
+        <v>50</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1398,10 +1395,10 @@
         <v>43.879193478150057</v>
       </c>
       <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>77</v>
       </c>
@@ -1429,8 +1426,8 @@
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="J9">
-        <v>53.887491958854582</v>
+      <c r="J9" s="3">
+        <v>50</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1439,10 +1436,10 @@
         <v>203.61215672430819</v>
       </c>
       <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>78</v>
       </c>
@@ -1470,7 +1467,7 @@
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="3">
         <v>0</v>
       </c>
       <c r="K10">
@@ -1483,7 +1480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>79</v>
       </c>
@@ -1511,8 +1508,8 @@
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11">
-        <v>198.77166776935209</v>
+      <c r="J11" s="3">
+        <v>200</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -1521,10 +1518,10 @@
         <v>60.640285872832877</v>
       </c>
       <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>80</v>
       </c>
@@ -1552,8 +1549,8 @@
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12">
-        <v>145.9315995724973</v>
+      <c r="J12" s="3">
+        <v>150</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -1562,10 +1559,10 @@
         <v>36.197745367301607</v>
       </c>
       <c r="M12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>105</v>
       </c>
@@ -1593,8 +1590,8 @@
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13">
-        <v>56.047356099547059</v>
+      <c r="J13" s="3">
+        <v>50</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1603,10 +1600,10 @@
         <v>330.6820257517391</v>
       </c>
       <c r="M13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>106</v>
       </c>
@@ -1634,8 +1631,8 @@
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14">
-        <v>247.92335487811081</v>
+      <c r="J14" s="3">
+        <v>250</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1644,10 +1641,10 @@
         <v>553.16071277585593</v>
       </c>
       <c r="M14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>107</v>
       </c>
@@ -1675,8 +1672,8 @@
       <c r="I15">
         <v>0</v>
       </c>
-      <c r="J15">
-        <v>219.6096351554171</v>
+      <c r="J15" s="3">
+        <v>250</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1688,7 +1685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>108</v>
       </c>
@@ -1716,8 +1713,8 @@
       <c r="I16">
         <v>0</v>
       </c>
-      <c r="J16">
-        <v>416.30596976945401</v>
+      <c r="J16" s="3">
+        <v>450</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1726,10 +1723,10 @@
         <v>68.338995664829312</v>
       </c>
       <c r="M16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>109</v>
       </c>
@@ -1757,8 +1754,8 @@
       <c r="I17">
         <v>0</v>
       </c>
-      <c r="J17">
-        <v>16.196803908595861</v>
+      <c r="J17" s="3">
+        <v>50</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1767,10 +1764,10 @@
         <v>22.388400448922361</v>
       </c>
       <c r="M17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>138</v>
       </c>
@@ -1798,8 +1795,8 @@
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18">
-        <v>77.215456257315893</v>
+      <c r="J18" s="3">
+        <v>100</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1808,10 +1805,10 @@
         <v>77.803671695189564</v>
       </c>
       <c r="M18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>139</v>
       </c>
@@ -1839,8 +1836,8 @@
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19">
-        <v>136.7908290498244</v>
+      <c r="J19" s="3">
+        <v>150</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -1849,10 +1846,10 @@
         <v>100.3076291508773</v>
       </c>
       <c r="M19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>141</v>
       </c>
@@ -1880,8 +1877,8 @@
       <c r="I20">
         <v>0</v>
       </c>
-      <c r="J20">
-        <v>425.25110434788922</v>
+      <c r="J20" s="3">
+        <v>450</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1890,10 +1887,10 @@
         <v>788.45967046733961</v>
       </c>
       <c r="M20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>161</v>
       </c>
@@ -1921,8 +1918,8 @@
       <c r="I21">
         <v>0</v>
       </c>
-      <c r="J21">
-        <v>542.83347753066312</v>
+      <c r="J21" s="3">
+        <v>550</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -1931,10 +1928,10 @@
         <v>242.61276485375299</v>
       </c>
       <c r="M21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>176</v>
       </c>
@@ -1962,8 +1959,8 @@
       <c r="I22">
         <v>0</v>
       </c>
-      <c r="J22">
-        <v>102.71339508371931</v>
+      <c r="J22" s="3">
+        <v>100</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1972,7 +1969,7 @@
         <v>94.863624312781539</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1983,9 +1980,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2020,7 +2017,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -2049,7 +2046,7 @@
         <v>8.8044759999999993</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -2078,7 +2075,7 @@
         <v>11.871930600000001</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -2107,7 +2104,7 @@
         <v>5.2955095999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -2136,7 +2133,7 @@
         <v>8.8866494000000031</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -2165,7 +2162,7 @@
         <v>10.0126685</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -2194,7 +2191,7 @@
         <v>11.08352</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -2223,7 +2220,7 @@
         <v>10.481959399999999</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -2252,7 +2249,7 @@
         <v>5.6666667000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -2281,7 +2278,7 @@
         <v>11.1900113</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -2310,7 +2307,7 @@
         <v>11.0058121</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -2339,7 +2336,7 @@
         <v>12.458487</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -2368,7 +2365,7 @@
         <v>5.9323598000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -2397,7 +2394,7 @@
         <v>12.426399999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>54</v>
       </c>
@@ -2426,7 +2423,7 @@
         <v>8.0306999999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -2455,7 +2452,7 @@
         <v>6.9432999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -2484,7 +2481,7 @@
         <v>8.9611000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -2513,7 +2510,7 @@
         <v>10.3950528</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -2542,7 +2539,7 @@
         <v>9.7151951999999984</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -2571,7 +2568,7 @@
         <v>11.439399999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>62</v>
       </c>
@@ -2600,7 +2597,7 @@
         <v>11.230700000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -2629,7 +2626,7 @@
         <v>7.2199947</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>64</v>
       </c>
@@ -2658,7 +2655,7 @@
         <v>5.5803419999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -2687,7 +2684,7 @@
         <v>9.3017813999999994</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -2716,7 +2713,7 @@
         <v>6.8948</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -2745,7 +2742,7 @@
         <v>11.1072278</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>68</v>
       </c>
@@ -2774,7 +2771,7 @@
         <v>7.8511770000000034</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -2803,7 +2800,7 @@
         <v>6.8848000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -2832,7 +2829,7 @@
         <v>7.2545709999999994</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -2861,7 +2858,7 @@
         <v>11.8285</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -2890,7 +2887,7 @@
         <v>9.7574403499999995</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -2919,7 +2916,7 @@
         <v>6.0833482000000014</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -2948,7 +2945,7 @@
         <v>7.4153287000000017</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -2977,7 +2974,7 @@
         <v>10.436579999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -3006,7 +3003,7 @@
         <v>12.036899999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -3035,7 +3032,7 @@
         <v>11.520841900000001</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>78</v>
       </c>
@@ -3064,7 +3061,7 @@
         <v>11.6968</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -3093,7 +3090,7 @@
         <v>11.239599999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>80</v>
       </c>
@@ -3122,7 +3119,7 @@
         <v>7.5333332999999989</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -3151,7 +3148,7 @@
         <v>8.9330416999999969</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -3180,7 +3177,7 @@
         <v>8.157</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -3209,7 +3206,7 @@
         <v>10.9664</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -3238,7 +3235,7 @@
         <v>6.6169454999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>85</v>
       </c>
@@ -3267,7 +3264,7 @@
         <v>6.5069116999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>86</v>
       </c>
@@ -3296,7 +3293,7 @@
         <v>11.5484121</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>87</v>
       </c>
@@ -3325,7 +3322,7 @@
         <v>6.5741103000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>88</v>
       </c>
@@ -3354,7 +3351,7 @@
         <v>5.8376893999999986</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>89</v>
       </c>
@@ -3383,7 +3380,7 @@
         <v>11.051768900000001</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>90</v>
       </c>
@@ -3412,7 +3409,7 @@
         <v>8.1743355999999991</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>91</v>
       </c>
@@ -3441,7 +3438,7 @@
         <v>11.763260900000001</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>92</v>
       </c>
@@ -3470,7 +3467,7 @@
         <v>5.8235750999999993</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>93</v>
       </c>
@@ -3499,7 +3496,7 @@
         <v>6.8139132</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>94</v>
       </c>
@@ -3528,7 +3525,7 @@
         <v>8.5725324999999994</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>95</v>
       </c>
@@ -3557,7 +3554,7 @@
         <v>6.9097999999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>96</v>
       </c>
@@ -3586,7 +3583,7 @@
         <v>6.0118764999999996</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>97</v>
       </c>
@@ -3615,7 +3612,7 @@
         <v>10.4582701</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>98</v>
       </c>
@@ -3644,7 +3641,7 @@
         <v>5.8372717999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>99</v>
       </c>
@@ -3673,7 +3670,7 @@
         <v>7.828136999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>100</v>
       </c>
@@ -3702,7 +3699,7 @@
         <v>6.15</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>101</v>
       </c>
@@ -3731,7 +3728,7 @@
         <v>11.04129</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>102</v>
       </c>
@@ -3760,7 +3757,7 @@
         <v>9.0890899999999988</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>103</v>
       </c>
@@ -3789,7 +3786,7 @@
         <v>5.5608660999999966</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>104</v>
       </c>
@@ -3818,7 +3815,7 @@
         <v>6.9358199999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>105</v>
       </c>
@@ -3847,7 +3844,7 @@
         <v>5.8543174000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>106</v>
       </c>
@@ -3876,7 +3873,7 @@
         <v>6.9920547000000024</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>107</v>
       </c>
@@ -3905,7 +3902,7 @@
         <v>9.8333333000000014</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>108</v>
       </c>
@@ -3934,7 +3931,7 @@
         <v>6.2766851000000008</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>109</v>
       </c>
@@ -3963,7 +3960,7 @@
         <v>6.5668392999999998</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>110</v>
       </c>
@@ -3992,7 +3989,7 @@
         <v>6.5005457999999994</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>111</v>
       </c>
@@ -4021,7 +4018,7 @@
         <v>6.5980089000000008</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>112</v>
       </c>
@@ -4050,7 +4047,7 @@
         <v>9.6333333000000021</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>113</v>
       </c>
@@ -4079,7 +4076,7 @@
         <v>8.6937046000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>114</v>
       </c>
@@ -4108,7 +4105,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>115</v>
       </c>
@@ -4137,7 +4134,7 @@
         <v>11.7372151</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>116</v>
       </c>
@@ -4166,7 +4163,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>117</v>
       </c>
@@ -4195,7 +4192,7 @@
         <v>10.0377767</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>118</v>
       </c>
@@ -4224,7 +4221,7 @@
         <v>6.5719160000000008</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>119</v>
       </c>
@@ -4253,7 +4250,7 @@
         <v>5.8013399999999997</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>120</v>
       </c>
@@ -4282,7 +4279,7 @@
         <v>9.0191520000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>121</v>
       </c>
@@ -4311,7 +4308,7 @@
         <v>9.6812501999999991</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>122</v>
       </c>
@@ -4340,7 +4337,7 @@
         <v>9.7131293000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>123</v>
       </c>
@@ -4369,7 +4366,7 @@
         <v>9.1879674999999992</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>124</v>
       </c>
@@ -4398,7 +4395,7 @@
         <v>5.4489538999999994</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>125</v>
       </c>
@@ -4427,7 +4424,7 @@
         <v>6.2465699999999984</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>126</v>
       </c>
@@ -4456,7 +4453,7 @@
         <v>10.981521600000001</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>127</v>
       </c>
@@ -4485,7 +4482,7 @@
         <v>11.006936400000001</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>128</v>
       </c>
@@ -4514,7 +4511,7 @@
         <v>5.1708737999999999</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>129</v>
       </c>
@@ -4543,7 +4540,7 @@
         <v>8.7299540000000011</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>130</v>
       </c>
@@ -4572,7 +4569,7 @@
         <v>9.1423079999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>131</v>
       </c>
@@ -4601,7 +4598,7 @@
         <v>8.0138783</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>132</v>
       </c>
@@ -4630,7 +4627,7 @@
         <v>10.0280798</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>133</v>
       </c>
@@ -4659,7 +4656,7 @@
         <v>6.2347906999999996</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>134</v>
       </c>
@@ -4688,7 +4685,7 @@
         <v>11.188310299999999</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>135</v>
       </c>
@@ -4717,7 +4714,7 @@
         <v>11.4618021</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>136</v>
       </c>
@@ -4746,7 +4743,7 @@
         <v>11.510163</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>137</v>
       </c>
@@ -4775,7 +4772,7 @@
         <v>8.8672097000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>138</v>
       </c>
@@ -4804,7 +4801,7 @@
         <v>11.4952627</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>139</v>
       </c>
@@ -4833,7 +4830,7 @@
         <v>9.8477710999999992</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>140</v>
       </c>
@@ -4862,7 +4859,7 @@
         <v>11.04129</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>141</v>
       </c>
@@ -4891,7 +4888,7 @@
         <v>9.8825433</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>142</v>
       </c>
@@ -4920,7 +4917,7 @@
         <v>9.0966266000000005</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>143</v>
       </c>
@@ -4949,7 +4946,7 @@
         <v>11.916895</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>144</v>
       </c>
@@ -4978,7 +4975,7 @@
         <v>8.0588759000000003</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>145</v>
       </c>
@@ -5007,7 +5004,7 @@
         <v>6.8477066000000004</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>146</v>
       </c>
@@ -5044,12 +5041,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="12" max="12" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>147</v>
       </c>
@@ -5086,11 +5083,11 @@
       <c r="L1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>1166</v>
       </c>
@@ -5131,7 +5128,7 @@
         <v>10943</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>1334</v>
       </c>
@@ -5172,7 +5169,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>1335</v>
       </c>
@@ -5210,7 +5207,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>1336</v>
       </c>
@@ -5251,7 +5248,7 @@
         <v>3343</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>1165</v>
       </c>
@@ -5289,7 +5286,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>1289</v>
       </c>
@@ -5327,7 +5324,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>1290</v>
       </c>
@@ -5368,7 +5365,7 @@
         <v>343321</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>1291</v>
       </c>
@@ -5406,7 +5403,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>1173</v>
       </c>
@@ -5444,7 +5441,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>1174</v>
       </c>
@@ -5482,7 +5479,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>1292</v>
       </c>
@@ -5520,7 +5517,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>1175</v>
       </c>
@@ -5558,7 +5555,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>6798</v>
       </c>
@@ -5596,7 +5593,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>1288</v>
       </c>
@@ -5634,7 +5631,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>6562</v>
       </c>
@@ -5672,7 +5669,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>1293</v>
       </c>
@@ -5710,7 +5707,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>1176</v>
       </c>
@@ -5748,7 +5745,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>1317</v>
       </c>
@@ -5794,9 +5791,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>208</v>
       </c>
@@ -5819,7 +5816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>43</v>
       </c>
@@ -5842,7 +5839,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>44</v>
       </c>
@@ -5865,7 +5862,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>45</v>
       </c>
@@ -5888,7 +5885,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>46</v>
       </c>
@@ -5919,9 +5916,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>214</v>
       </c>

--- a/Grid/test_trøndelagsnettet.xlsx
+++ b/Grid/test_trøndelagsnettet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2d06795444358214/Dokumenter/Kraftsystemer2/Kraftsystemer-2/Grid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_057EBA57FA9E57F87E476CE1F4362D3B786B1A4C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D0F19DB-79DD-49A2-B821-E57BDDFB7D4D}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="11_057EBA57FA9E57F87E476CE1F4362D3B786B1A4C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BDF9EC8-C6E4-4903-A70C-A73CAEE0C7D1}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,20 @@
     <sheet name="trafo" sheetId="4" r:id="rId4"/>
     <sheet name="link" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1143,10 +1156,11 @@
         <v>100</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <f>0.25*J2</f>
+        <v>25</v>
       </c>
       <c r="L2">
-        <v>30.622222356505979</v>
+        <v>30</v>
       </c>
       <c r="M2">
         <v>30</v>
@@ -1184,10 +1198,11 @@
         <v>300</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <f t="shared" ref="K3:K22" si="0">0.25*J3</f>
+        <v>75</v>
       </c>
       <c r="L3">
-        <v>1127.8018812523951</v>
+        <v>1150</v>
       </c>
       <c r="M3">
         <v>90</v>
@@ -1225,6 +1240,7 @@
         <v>0</v>
       </c>
       <c r="K4">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L4">
@@ -1266,6 +1282,7 @@
         <v>0</v>
       </c>
       <c r="K5">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L5">
@@ -1307,6 +1324,7 @@
         <v>0</v>
       </c>
       <c r="K6">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L6">
@@ -1348,10 +1366,11 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="L7">
-        <v>19.35034456687892</v>
+        <v>50</v>
       </c>
       <c r="M7">
         <v>30</v>
@@ -1389,10 +1408,11 @@
         <v>50</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>12.5</v>
       </c>
       <c r="L8">
-        <v>43.879193478150057</v>
+        <v>40</v>
       </c>
       <c r="M8">
         <v>15</v>
@@ -1430,10 +1450,11 @@
         <v>50</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>12.5</v>
       </c>
       <c r="L9">
-        <v>203.61215672430819</v>
+        <v>200</v>
       </c>
       <c r="M9">
         <v>15</v>
@@ -1471,6 +1492,7 @@
         <v>0</v>
       </c>
       <c r="K10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L10">
@@ -1512,10 +1534,11 @@
         <v>200</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="L11">
-        <v>60.640285872832877</v>
+        <v>60</v>
       </c>
       <c r="M11">
         <v>60</v>
@@ -1553,10 +1576,11 @@
         <v>150</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>37.5</v>
       </c>
       <c r="L12">
-        <v>36.197745367301607</v>
+        <v>40</v>
       </c>
       <c r="M12">
         <v>45</v>
@@ -1594,10 +1618,11 @@
         <v>50</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>12.5</v>
       </c>
       <c r="L13">
-        <v>330.6820257517391</v>
+        <v>330</v>
       </c>
       <c r="M13">
         <v>15</v>
@@ -1635,10 +1660,11 @@
         <v>250</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>62.5</v>
       </c>
       <c r="L14">
-        <v>553.16071277585593</v>
+        <v>550</v>
       </c>
       <c r="M14">
         <v>75</v>
@@ -1676,7 +1702,8 @@
         <v>250</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>62.5</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1717,10 +1744,11 @@
         <v>450</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>112.5</v>
       </c>
       <c r="L16">
-        <v>68.338995664829312</v>
+        <v>70</v>
       </c>
       <c r="M16">
         <v>135</v>
@@ -1758,10 +1786,11 @@
         <v>50</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>12.5</v>
       </c>
       <c r="L17">
-        <v>22.388400448922361</v>
+        <v>20</v>
       </c>
       <c r="M17">
         <v>15</v>
@@ -1799,10 +1828,11 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="L18">
-        <v>77.803671695189564</v>
+        <v>80</v>
       </c>
       <c r="M18">
         <v>30</v>
@@ -1840,10 +1870,11 @@
         <v>150</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>37.5</v>
       </c>
       <c r="L19">
-        <v>100.3076291508773</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>45</v>
@@ -1881,10 +1912,11 @@
         <v>450</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>112.5</v>
       </c>
       <c r="L20">
-        <v>788.45967046733961</v>
+        <v>800</v>
       </c>
       <c r="M20">
         <v>135</v>
@@ -1922,10 +1954,11 @@
         <v>550</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>137.5</v>
       </c>
       <c r="L21">
-        <v>242.61276485375299</v>
+        <v>250</v>
       </c>
       <c r="M21">
         <v>165</v>
@@ -1963,10 +1996,11 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="L22">
-        <v>94.863624312781539</v>
+        <v>100</v>
       </c>
       <c r="M22">
         <v>30</v>

--- a/Grid/test_trøndelagsnettet.xlsx
+++ b/Grid/test_trøndelagsnettet.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0348cbc925570652/Master/Kraftsystemer/Kraftsystemer-2/Grid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A10BD20-A0B5-432D-8B98-093B257C5735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_D66F0DED9A5C76CD19CE15FAE4E891D83F9B944B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68021297-1237-4FD7-B733-4D36A35FCEB3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bus" sheetId="1" r:id="rId1"/>
     <sheet name="gen" sheetId="2" r:id="rId2"/>
     <sheet name="line" sheetId="3" r:id="rId3"/>
     <sheet name="trafo" sheetId="4" r:id="rId4"/>
-    <sheet name="link" sheetId="6" r:id="rId5"/>
+    <sheet name="link" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,26 +37,209 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="223">
+  <si>
+    <t>line_id</t>
+  </si>
+  <si>
+    <t>area0</t>
+  </si>
+  <si>
+    <t>bus0</t>
+  </si>
+  <si>
+    <t>bus1</t>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>Vbase</t>
+  </si>
+  <si>
+    <t>lat</t>
+  </si>
+  <si>
+    <t>lon</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>eic code</t>
+  </si>
+  <si>
+    <t>NO3</t>
+  </si>
+  <si>
+    <t>[63.0581865391036, 63.169235, 63.271747122419]</t>
+  </si>
+  <si>
+    <t>[9.6024199750926, 9.95773300000001, 9.93306218856054]</t>
+  </si>
+  <si>
+    <t>Thamshavn trafostasjon – Grana koblingsstasjon</t>
+  </si>
+  <si>
+    <t>[62.6815788399503, 62.6288473888959]</t>
+  </si>
+  <si>
+    <t>[10.1228770726635, 10.2663749273365]</t>
+  </si>
+  <si>
+    <t>Brattset trafostasjon – Brattset trafostasjon</t>
+  </si>
+  <si>
+    <t>3rr4</t>
+  </si>
+  <si>
+    <t>[62.764642333228, 62.6818480622148]</t>
+  </si>
+  <si>
+    <t>[9.93059299951052, 10.1222020004895]</t>
+  </si>
+  <si>
+    <t>[63.0578905163084, 62.7649652979347]</t>
+  </si>
+  <si>
+    <t>[9.60225399160166, 9.93006400839835]</t>
+  </si>
+  <si>
+    <t>Grana koblingsstasjon – Brattset trafostasjon</t>
+  </si>
+  <si>
+    <t>[62.4779336946648, 61.7329656956376]</t>
+  </si>
+  <si>
+    <t>[7.03366082879706, 5.21884217120294]</t>
+  </si>
+  <si>
+    <t>Ørskog trafostasjon – Svelgen trafostasjon</t>
+  </si>
+  <si>
+    <t>[63.979469495752, 63.951246, 63.7796426966659]</t>
+  </si>
+  <si>
+    <t>[11.4783430752882, 11.578217, 11.4725900216729]</t>
+  </si>
+  <si>
+    <t>Ogndal trafostasjon – Verdal trafostasjon</t>
+  </si>
+  <si>
+    <t>[63.7792842667966, 63.4574296446683]</t>
+  </si>
+  <si>
+    <t>[11.4722350100571, 11.0181519899429]</t>
+  </si>
+  <si>
+    <t>Verdal trafostasjon – Eidum trafostasjon</t>
+  </si>
+  <si>
+    <t>[63.4013872743893, 63.423488, 63.4571907093831]</t>
+  </si>
+  <si>
+    <t>[10.4402013779148, 10.813293, 11.0174939283141]</t>
+  </si>
+  <si>
+    <t>Eidum trafostasjon – Strinda koblingsstasjon</t>
+  </si>
+  <si>
+    <t>[63.779267150403, 63.703506, 63.409354, 63.2769667913878]</t>
+  </si>
+  <si>
+    <t>[11.4726336570695, 11.538391, 11.15387, 10.4580241866236]</t>
+  </si>
+  <si>
+    <t>Verdal trafostasjon – Klæbu transformatorstasjon</t>
+  </si>
+  <si>
+    <t>[63.2770887040084, 63.4011611611364]</t>
+  </si>
+  <si>
+    <t>[10.4575822753626, 10.4397867246374]</t>
+  </si>
+  <si>
+    <t>Strinda koblingsstasjon – Klæbu transformatorstasjon</t>
+  </si>
+  <si>
+    <t>[63.2719119610727, 63.268241, 63.23672, 63.2768450273625]</t>
+  </si>
+  <si>
+    <t>[9.93345548452976, 9.979706, 10.04837, 10.4571728802973]</t>
+  </si>
+  <si>
+    <t>Klæbu transformatorstasjon – Orkdal transformatorstasjon</t>
+  </si>
+  <si>
+    <t>[62.6799952696754, 63.021959, 63.202068, 63.2717982207385]</t>
+  </si>
+  <si>
+    <t>[8.48028947595439, 8.897552, 9.79156500000001, 9.93271247746952]</t>
+  </si>
+  <si>
+    <t>Orkdal transformatorstasjon – Aura trafostasjon</t>
+  </si>
+  <si>
+    <t>[61.8861304294624, 62.6796217603448]</t>
+  </si>
+  <si>
+    <t>[9.06357629708208, 8.48021670291793]</t>
+  </si>
+  <si>
+    <t>Aura trafostasjon – Vågåmo trafo stasjon</t>
+  </si>
+  <si>
+    <t>[63.9797705313635, 64.4536577724636]</t>
+  </si>
+  <si>
+    <t>[11.4780240828036, 11.6207309171964]</t>
+  </si>
+  <si>
+    <t>Ogndal trafostasjon – Namsos (Statnett) trafostasjon</t>
+  </si>
+  <si>
+    <t>[62.5263493502315, 62.6797261154976]</t>
+  </si>
+  <si>
+    <t>[7.79520216211446, 8.47966983788554]</t>
+  </si>
+  <si>
+    <t>Viklandet trafostasjon – Grytten trafostasjon</t>
+  </si>
+  <si>
+    <t>[63.2769332188306, 63.325632, 63.085435, 62.6800121989769]</t>
+  </si>
+  <si>
+    <t>[10.4571743955897, 9.986572, 8.751984, 8.480202620587]</t>
+  </si>
+  <si>
+    <t>Klæbu transformatorstasjon – Viklandet trafostasjon</t>
+  </si>
+  <si>
+    <t>[62.4780980928918, 62.5262309524377]</t>
+  </si>
+  <si>
+    <t>[7.03444016980177, 7.79435683019823]</t>
+  </si>
+  <si>
+    <t>Ørskog trafostasjon – Grytten trafostasjon</t>
+  </si>
+  <si>
+    <t>[63.0357063153294, 63.061804, 63.22373, 63.2768185449166]</t>
+  </si>
+  <si>
+    <t>[11.7274675384392, 11.469727, 10.778961, 10.4580312550914]</t>
+  </si>
+  <si>
+    <t>Klæbu transformatorstasjon – Nea trafostasjon</t>
+  </si>
   <si>
     <t>bus_id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>bidz</t>
   </si>
   <si>
-    <t>Vbase</t>
-  </si>
-  <si>
-    <t>lat</t>
-  </si>
-  <si>
-    <t>lon</t>
-  </si>
-  <si>
     <t xml:space="preserve">S_base [MVA] </t>
   </si>
   <si>
@@ -81,9 +264,6 @@
     <t>Vågåmo trafo stasjon</t>
   </si>
   <si>
-    <t>NO3</t>
-  </si>
-  <si>
     <t>Aura trafostasjon</t>
   </si>
   <si>
@@ -141,6 +321,12 @@
     <t>Pmax</t>
   </si>
   <si>
+    <t>Qmax</t>
+  </si>
+  <si>
+    <t>Qmin</t>
+  </si>
+  <si>
     <t>bus</t>
   </si>
   <si>
@@ -480,19 +666,10 @@
     <t>Viddal</t>
   </si>
   <si>
-    <t>line_id</t>
-  </si>
-  <si>
-    <t>area0</t>
-  </si>
-  <si>
-    <t>bus0</t>
-  </si>
-  <si>
-    <t>bus1</t>
-  </si>
-  <si>
-    <t>length</t>
+    <t>transformer_id</t>
+  </si>
+  <si>
+    <t>ratio</t>
   </si>
   <si>
     <t>R</t>
@@ -501,174 +678,6 @@
     <t>X</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>[63.0581865391036, 63.169235, 63.271747122419]</t>
-  </si>
-  <si>
-    <t>[9.6024199750926, 9.95773300000001, 9.93306218856054]</t>
-  </si>
-  <si>
-    <t>Thamshavn trafostasjon – Grana koblingsstasjon</t>
-  </si>
-  <si>
-    <t>[62.6815788399503, 62.6288473888959]</t>
-  </si>
-  <si>
-    <t>[10.1228770726635, 10.2663749273365]</t>
-  </si>
-  <si>
-    <t>Brattset trafostasjon – Brattset trafostasjon</t>
-  </si>
-  <si>
-    <t>[62.764642333228, 62.6818480622148]</t>
-  </si>
-  <si>
-    <t>[9.93059299951052, 10.1222020004895]</t>
-  </si>
-  <si>
-    <t>[63.0578905163084, 62.7649652979347]</t>
-  </si>
-  <si>
-    <t>[9.60225399160166, 9.93006400839835]</t>
-  </si>
-  <si>
-    <t>Grana koblingsstasjon – Brattset trafostasjon</t>
-  </si>
-  <si>
-    <t>[62.4779336946648, 61.7329656956376]</t>
-  </si>
-  <si>
-    <t>[7.03366082879706, 5.21884217120294]</t>
-  </si>
-  <si>
-    <t>Ørskog trafostasjon – Svelgen trafostasjon</t>
-  </si>
-  <si>
-    <t>[63.979469495752, 63.951246, 63.7796426966659]</t>
-  </si>
-  <si>
-    <t>[11.4783430752882, 11.578217, 11.4725900216729]</t>
-  </si>
-  <si>
-    <t>Ogndal trafostasjon – Verdal trafostasjon</t>
-  </si>
-  <si>
-    <t>[63.7792842667966, 63.4574296446683]</t>
-  </si>
-  <si>
-    <t>[11.4722350100571, 11.0181519899429]</t>
-  </si>
-  <si>
-    <t>Verdal trafostasjon – Eidum trafostasjon</t>
-  </si>
-  <si>
-    <t>[63.4013872743893, 63.423488, 63.4571907093831]</t>
-  </si>
-  <si>
-    <t>[10.4402013779148, 10.813293, 11.0174939283141]</t>
-  </si>
-  <si>
-    <t>Eidum trafostasjon – Strinda koblingsstasjon</t>
-  </si>
-  <si>
-    <t>[63.779267150403, 63.703506, 63.409354, 63.2769667913878]</t>
-  </si>
-  <si>
-    <t>[11.4726336570695, 11.538391, 11.15387, 10.4580241866236]</t>
-  </si>
-  <si>
-    <t>Verdal trafostasjon – Klæbu transformatorstasjon</t>
-  </si>
-  <si>
-    <t>[63.2770887040084, 63.4011611611364]</t>
-  </si>
-  <si>
-    <t>[10.4575822753626, 10.4397867246374]</t>
-  </si>
-  <si>
-    <t>Strinda koblingsstasjon – Klæbu transformatorstasjon</t>
-  </si>
-  <si>
-    <t>[63.2719119610727, 63.268241, 63.23672, 63.2768450273625]</t>
-  </si>
-  <si>
-    <t>[9.93345548452976, 9.979706, 10.04837, 10.4571728802973]</t>
-  </si>
-  <si>
-    <t>Klæbu transformatorstasjon – Orkdal transformatorstasjon</t>
-  </si>
-  <si>
-    <t>[62.6799952696754, 63.021959, 63.202068, 63.2717982207385]</t>
-  </si>
-  <si>
-    <t>[8.48028947595439, 8.897552, 9.79156500000001, 9.93271247746952]</t>
-  </si>
-  <si>
-    <t>Orkdal transformatorstasjon – Aura trafostasjon</t>
-  </si>
-  <si>
-    <t>[61.8861304294624, 62.6796217603448]</t>
-  </si>
-  <si>
-    <t>[9.06357629708208, 8.48021670291793]</t>
-  </si>
-  <si>
-    <t>Aura trafostasjon – Vågåmo trafo stasjon</t>
-  </si>
-  <si>
-    <t>[63.9797705313635, 64.4536577724636]</t>
-  </si>
-  <si>
-    <t>[11.4780240828036, 11.6207309171964]</t>
-  </si>
-  <si>
-    <t>Ogndal trafostasjon – Namsos (Statnett) trafostasjon</t>
-  </si>
-  <si>
-    <t>[62.5263493502315, 62.6797261154976]</t>
-  </si>
-  <si>
-    <t>[7.79520216211446, 8.47966983788554]</t>
-  </si>
-  <si>
-    <t>Viklandet trafostasjon – Grytten trafostasjon</t>
-  </si>
-  <si>
-    <t>[63.2769332188306, 63.325632, 63.085435, 62.6800121989769]</t>
-  </si>
-  <si>
-    <t>[10.4571743955897, 9.986572, 8.751984, 8.480202620587]</t>
-  </si>
-  <si>
-    <t>Klæbu transformatorstasjon – Viklandet trafostasjon</t>
-  </si>
-  <si>
-    <t>[62.4780980928918, 62.5262309524377]</t>
-  </si>
-  <si>
-    <t>[7.03444016980177, 7.79435683019823]</t>
-  </si>
-  <si>
-    <t>Ørskog trafostasjon – Grytten trafostasjon</t>
-  </si>
-  <si>
-    <t>[63.0357063153294, 63.061804, 63.22373, 63.2768185449166]</t>
-  </si>
-  <si>
-    <t>[11.7274675384392, 11.469727, 10.778961, 10.4580312550914]</t>
-  </si>
-  <si>
-    <t>Klæbu transformatorstasjon – Nea trafostasjon</t>
-  </si>
-  <si>
-    <t>transformer_id</t>
-  </si>
-  <si>
-    <t>ratio</t>
-  </si>
-  <si>
     <t>Klæbu transformatorstasjon – Klæbu transformatorstasjon</t>
   </si>
   <si>
@@ -690,16 +699,13 @@
     <t>Pinj</t>
   </si>
   <si>
-    <t>Qmax</t>
-  </si>
-  <si>
-    <t>Qmin</t>
-  </si>
-  <si>
-    <t>eic code</t>
-  </si>
-  <si>
-    <t>3rr4</t>
+    <t>R_per_m</t>
+  </si>
+  <si>
+    <t>X_per_m</t>
+  </si>
+  <si>
+    <t>B_per_m</t>
   </si>
 </sst>
 </file>
@@ -1085,43 +1091,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -1129,10 +1135,10 @@
         <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>300</v>
@@ -1156,7 +1162,7 @@
         <v>100</v>
       </c>
       <c r="K2">
-        <f>0.25*J2</f>
+        <f t="shared" ref="K2:K22" si="0">0.25*J2</f>
         <v>25</v>
       </c>
       <c r="L2">
@@ -1171,10 +1177,10 @@
         <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>300</v>
@@ -1198,7 +1204,7 @@
         <v>300</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K22" si="0">0.25*J3</f>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="L3">
@@ -1213,10 +1219,10 @@
         <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>132</v>
@@ -1255,10 +1261,10 @@
         <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>300</v>
@@ -1297,10 +1303,10 @@
         <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>380</v>
@@ -1339,10 +1345,10 @@
         <v>62</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>132</v>
@@ -1381,10 +1387,10 @@
         <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>300</v>
@@ -1423,10 +1429,10 @@
         <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <v>132</v>
@@ -1465,10 +1471,10 @@
         <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>380</v>
@@ -1507,10 +1513,10 @@
         <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>380</v>
@@ -1549,10 +1555,10 @@
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D12">
         <v>132</v>
@@ -1591,10 +1597,10 @@
         <v>105</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>300</v>
@@ -1633,10 +1639,10 @@
         <v>106</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D14">
         <v>300</v>
@@ -1675,10 +1681,10 @@
         <v>107</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D15">
         <v>132</v>
@@ -1717,10 +1723,10 @@
         <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <v>380</v>
@@ -1759,10 +1765,10 @@
         <v>109</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D17">
         <v>380</v>
@@ -1801,10 +1807,10 @@
         <v>138</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D18">
         <v>300</v>
@@ -1843,10 +1849,10 @@
         <v>139</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>300</v>
@@ -1885,10 +1891,10 @@
         <v>141</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>132</v>
@@ -1927,10 +1933,10 @@
         <v>161</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D21">
         <v>132</v>
@@ -1969,10 +1975,10 @@
         <v>176</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>300</v>
@@ -2018,48 +2024,48 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>217</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>218</v>
+        <v>95</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="D2">
         <v>143</v>
@@ -2082,13 +2088,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="D3">
         <v>60</v>
@@ -2111,13 +2117,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="D4">
         <v>251</v>
@@ -2140,13 +2146,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="D5">
         <v>160</v>
@@ -2169,13 +2175,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="D6">
         <v>92</v>
@@ -2198,13 +2204,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="D7">
         <v>14</v>
@@ -2227,13 +2233,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="D8">
         <v>140</v>
@@ -2256,13 +2262,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="D9">
         <v>157.30000000000001</v>
@@ -2285,13 +2291,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="D10">
         <v>259.8</v>
@@ -2314,13 +2320,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="D11">
         <v>46</v>
@@ -2343,13 +2349,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -2372,13 +2378,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -2401,13 +2407,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>5.4</v>
@@ -2430,13 +2436,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>109</v>
@@ -2459,13 +2465,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>117</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="D16">
         <v>253.2</v>
@@ -2488,13 +2494,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -2517,13 +2523,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>169.2</v>
@@ -2546,13 +2552,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>90</v>
@@ -2575,13 +2581,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>26</v>
@@ -2604,13 +2610,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>40.299999999999997</v>
@@ -2633,13 +2639,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -2662,13 +2668,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>6.2</v>
@@ -2691,13 +2697,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>14</v>
@@ -2720,13 +2726,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -2749,13 +2755,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>48.5</v>
@@ -2778,13 +2784,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>85</v>
@@ -2807,13 +2813,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>5.4</v>
@@ -2836,13 +2842,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -2865,13 +2871,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>45</v>
@@ -2894,13 +2900,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>86</v>
@@ -2923,13 +2929,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>64</v>
@@ -2952,13 +2958,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="D33">
         <v>319.2</v>
@@ -2981,13 +2987,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="D34">
         <v>23</v>
@@ -3010,13 +3016,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>60</v>
@@ -3039,13 +3045,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>36</v>
@@ -3068,13 +3074,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -3097,13 +3103,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>70</v>
@@ -3126,13 +3132,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>19.5</v>
@@ -3155,13 +3161,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D40">
         <v>7.8</v>
@@ -3184,13 +3190,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D41">
         <v>5.8</v>
@@ -3213,13 +3219,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>8</v>
@@ -3242,13 +3248,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D43">
         <v>17</v>
@@ -3271,13 +3277,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D44">
         <v>25.2</v>
@@ -3300,13 +3306,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D45">
         <v>4.0999999999999996</v>
@@ -3329,13 +3335,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -3358,13 +3364,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -3387,13 +3393,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D48">
         <v>10.4</v>
@@ -3416,13 +3422,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D49">
         <v>100</v>
@@ -3445,13 +3451,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C50" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D50">
         <v>21.7</v>
@@ -3474,13 +3480,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>92</v>
+        <v>154</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C51" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D51">
         <v>5.2</v>
@@ -3503,13 +3509,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="B52" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D52">
         <v>5.4</v>
@@ -3532,13 +3538,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D53">
         <v>9</v>
@@ -3561,13 +3567,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="B54" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D54">
         <v>5.5</v>
@@ -3590,13 +3596,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C55" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D55">
         <v>10.6</v>
@@ -3619,13 +3625,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="B56" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C56" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D56">
         <v>11.5</v>
@@ -3648,13 +3654,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C57" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D57">
         <v>40</v>
@@ -3677,13 +3683,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="B58" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C58" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D58">
         <v>35</v>
@@ -3706,13 +3712,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C59" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D59">
         <v>9</v>
@@ -3735,13 +3741,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C60" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D60">
         <v>16.3</v>
@@ -3764,13 +3770,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C61" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D61">
         <v>45</v>
@@ -3793,13 +3799,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C62" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D62">
         <v>8</v>
@@ -3822,13 +3828,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="B63" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C63" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D63">
         <v>4.5999999999999996</v>
@@ -3851,13 +3857,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="B64" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D64">
         <v>10</v>
@@ -3880,13 +3886,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="B65" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C65" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D65">
         <v>36.6</v>
@@ -3909,13 +3915,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="B66" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C66" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D66">
         <v>5</v>
@@ -3938,13 +3944,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="B67" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C67" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D67">
         <v>3.7</v>
@@ -3967,13 +3973,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="B68" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C68" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D68">
         <v>5.7</v>
@@ -3996,13 +4002,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>110</v>
+        <v>172</v>
       </c>
       <c r="B69" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D69">
         <v>5.6</v>
@@ -4025,13 +4031,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="B70" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C70" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -4054,13 +4060,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>112</v>
+        <v>174</v>
       </c>
       <c r="B71" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C71" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D71">
         <v>12</v>
@@ -4083,13 +4089,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="B72" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="C72" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="D72">
         <v>37.5</v>
@@ -4112,13 +4118,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="B73" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C73" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D73">
         <v>16</v>
@@ -4141,13 +4147,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="B74" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C74" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D74">
         <v>108</v>
@@ -4170,13 +4176,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="B75" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C75" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D75">
         <v>28</v>
@@ -4199,13 +4205,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="B76" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C76" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D76">
         <v>5</v>
@@ -4228,13 +4234,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>118</v>
+        <v>180</v>
       </c>
       <c r="B77" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D77">
         <v>9.5</v>
@@ -4257,13 +4263,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="B78" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C78" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="D78">
         <v>30</v>
@@ -4286,13 +4292,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="B79" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C79" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="D79">
         <v>130</v>
@@ -4315,13 +4321,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>121</v>
+        <v>183</v>
       </c>
       <c r="B80" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C80" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D80">
         <v>1.5</v>
@@ -4344,13 +4350,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="B81" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C81" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D81">
         <v>3.5</v>
@@ -4373,13 +4379,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="B82" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C82" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D82">
         <v>4.4000000000000004</v>
@@ -4402,13 +4408,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="B83" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C83" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D83">
         <v>0.3</v>
@@ -4431,13 +4437,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="B84" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C84" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D84">
         <v>8.1999999999999993</v>
@@ -4460,13 +4466,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="B85" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C85" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D85">
         <v>4.8</v>
@@ -4489,13 +4495,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>127</v>
+        <v>189</v>
       </c>
       <c r="B86" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C86" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D86">
         <v>8.1</v>
@@ -4518,13 +4524,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B87" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C87" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D87">
         <v>5.5</v>
@@ -4547,13 +4553,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D88">
         <v>40</v>
@@ -4576,13 +4582,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="B89" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C89" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D89">
         <v>0.4</v>
@@ -4605,13 +4611,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="B90" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C90" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -4634,13 +4640,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>132</v>
+        <v>194</v>
       </c>
       <c r="B91" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C91" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D91">
         <v>105</v>
@@ -4663,13 +4669,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="B92" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C92" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D92">
         <v>4.8</v>
@@ -4692,13 +4698,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C93" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D93">
         <v>2.4</v>
@@ -4721,13 +4727,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>135</v>
+        <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C94" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D94">
         <v>12.7</v>
@@ -4750,13 +4756,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="B95" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C95" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D95">
         <v>12.7</v>
@@ -4779,13 +4785,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="B96" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D96">
         <v>3</v>
@@ -4808,13 +4814,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>138</v>
+        <v>200</v>
       </c>
       <c r="B97" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C97" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D97">
         <v>13.7</v>
@@ -4837,13 +4843,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="B98" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C98" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D98">
         <v>41</v>
@@ -4866,13 +4872,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>140</v>
+        <v>202</v>
       </c>
       <c r="B99" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D99">
         <v>1.3</v>
@@ -4895,13 +4901,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="B100" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="C100" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="D100">
         <v>31</v>
@@ -4924,13 +4930,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="B101" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C101" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D101">
         <v>6.5</v>
@@ -4953,13 +4959,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="B102" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D102">
         <v>23.9</v>
@@ -4982,13 +4988,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="B103" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C103" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D103">
         <v>8.4</v>
@@ -5011,13 +5017,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="B104" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C104" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D104">
         <v>3.2</v>
@@ -5040,13 +5046,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="B105" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C105" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D105">
         <v>5.5</v>
@@ -5077,48 +5083,48 @@
   <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="12" max="12" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>149</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>151</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>219</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -5126,7 +5132,7 @@
         <v>1166</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>77</v>
@@ -5141,22 +5147,22 @@
         <v>132</v>
       </c>
       <c r="G2" t="s">
-        <v>155</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="I2">
-        <v>1.1461763862794841E-2</v>
+        <v>5.9999960132916883E-5</v>
       </c>
       <c r="J2">
-        <v>5.7499886917566988E-2</v>
+        <v>3.0100000000000011E-4</v>
       </c>
       <c r="K2">
-        <v>6.7677365007369585E-10</v>
+        <v>3E-9</v>
       </c>
       <c r="L2" t="s">
-        <v>157</v>
+        <v>13</v>
       </c>
       <c r="M2">
         <v>10943</v>
@@ -5167,7 +5173,7 @@
         <v>1334</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>46</v>
@@ -5182,25 +5188,25 @@
         <v>132</v>
       </c>
       <c r="G3" t="s">
-        <v>158</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="I3">
-        <v>3.2425557410300722E-3</v>
+        <v>5.9999960132916849E-5</v>
       </c>
       <c r="J3">
-        <v>1.626683210935333E-2</v>
+        <v>3.0099999999999989E-4</v>
       </c>
       <c r="K3">
-        <v>2.3922548709192738E-9</v>
+        <v>3E-9</v>
       </c>
       <c r="L3" t="s">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="M3" t="s">
-        <v>220</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -5208,7 +5214,7 @@
         <v>1335</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>62</v>
@@ -5223,22 +5229,22 @@
         <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="I4">
-        <v>4.6355900748739787E-3</v>
+        <v>5.9999960132916842E-5</v>
       </c>
       <c r="J4">
-        <v>2.325522566091805E-2</v>
+        <v>3.0100000000000011E-4</v>
       </c>
       <c r="K4">
-        <v>1.67336188929892E-9</v>
+        <v>3E-9</v>
       </c>
       <c r="L4" t="s">
-        <v>160</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -5246,7 +5252,7 @@
         <v>1336</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>107</v>
@@ -5261,22 +5267,22 @@
         <v>132</v>
       </c>
       <c r="G5" t="s">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="I5">
-        <v>1.262221308784686E-2</v>
+        <v>5.9999960132916842E-5</v>
       </c>
       <c r="J5">
-        <v>6.3321477731408726E-2</v>
+        <v>3.01E-4</v>
       </c>
       <c r="K5">
-        <v>6.1455306701922131E-10</v>
+        <v>3E-9</v>
       </c>
       <c r="L5" t="s">
-        <v>165</v>
+        <v>22</v>
       </c>
       <c r="M5">
         <v>3343</v>
@@ -5287,7 +5293,7 @@
         <v>1165</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>141</v>
@@ -5302,22 +5308,22 @@
         <v>132</v>
       </c>
       <c r="G6" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="I6">
-        <v>4.3382021687186828E-2</v>
+        <v>5.9999960132916849E-5</v>
       </c>
       <c r="J6">
-        <v>0.2176332867374596</v>
+        <v>3.0100000000000011E-4</v>
       </c>
       <c r="K6">
-        <v>1.7880724466092671E-10</v>
+        <v>3E-9</v>
       </c>
       <c r="L6" t="s">
-        <v>168</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -5325,7 +5331,7 @@
         <v>1289</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>138</v>
@@ -5340,22 +5346,22 @@
         <v>300</v>
       </c>
       <c r="G7" t="s">
-        <v>169</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>170</v>
+        <v>27</v>
       </c>
       <c r="I7">
-        <v>1.1395216266730269E-3</v>
+        <v>4.000000000000001E-5</v>
       </c>
       <c r="J7">
-        <v>7.5493307767088022E-3</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K7">
-        <v>1.796205325905698E-10</v>
+        <v>3.9000000000000002E-9</v>
       </c>
       <c r="L7" t="s">
-        <v>171</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -5363,7 +5369,7 @@
         <v>1290</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C8">
         <v>105</v>
@@ -5378,22 +5384,22 @@
         <v>300</v>
       </c>
       <c r="G8" t="s">
-        <v>172</v>
+        <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>173</v>
+        <v>30</v>
       </c>
       <c r="I8">
-        <v>1.8826852113204089E-3</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J8">
-        <v>1.247278952499771E-2</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K8">
-        <v>1.087178463243621E-10</v>
+        <v>3.9000000000000002E-9</v>
       </c>
       <c r="L8" t="s">
-        <v>174</v>
+        <v>31</v>
       </c>
       <c r="M8">
         <v>343321</v>
@@ -5404,7 +5410,7 @@
         <v>1291</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>139</v>
@@ -5419,22 +5425,22 @@
         <v>300</v>
       </c>
       <c r="G9" t="s">
-        <v>175</v>
+        <v>32</v>
       </c>
       <c r="H9" t="s">
-        <v>176</v>
+        <v>33</v>
       </c>
       <c r="I9">
-        <v>1.318316155233574E-3</v>
+        <v>4.0000000000000017E-5</v>
       </c>
       <c r="J9">
-        <v>8.7338445284224249E-3</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K9">
-        <v>1.5525978398195161E-10</v>
+        <v>3.9000000000000002E-9</v>
       </c>
       <c r="L9" t="s">
-        <v>177</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
@@ -5442,7 +5448,7 @@
         <v>1173</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <v>105</v>
@@ -5457,22 +5463,22 @@
         <v>300</v>
       </c>
       <c r="G10" t="s">
-        <v>178</v>
+        <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>179</v>
+        <v>36</v>
       </c>
       <c r="I10">
-        <v>3.7707866033381602E-3</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J10">
-        <v>2.4981461247115311E-2</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K10">
-        <v>5.4280844559138772E-11</v>
+        <v>3.9000000000000002E-9</v>
       </c>
       <c r="L10" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
@@ -5480,7 +5486,7 @@
         <v>1174</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11">
         <v>106</v>
@@ -5495,22 +5501,22 @@
         <v>300</v>
       </c>
       <c r="G11" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>182</v>
+        <v>39</v>
       </c>
       <c r="I11">
-        <v>6.1594118566375559E-4</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J11">
-        <v>4.0806103550223814E-3</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K11">
-        <v>3.323068602092437E-10</v>
+        <v>3.9000000000000002E-9</v>
       </c>
       <c r="L11" t="s">
-        <v>183</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -5518,7 +5524,7 @@
         <v>1292</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C12">
         <v>76</v>
@@ -5533,22 +5539,22 @@
         <v>300</v>
       </c>
       <c r="G12" t="s">
-        <v>184</v>
+        <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="I12">
-        <v>1.257594431190782E-3</v>
+        <v>3.999999999999999E-5</v>
       </c>
       <c r="J12">
-        <v>8.3315631066389322E-3</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K12">
-        <v>1.627563516543837E-10</v>
+        <v>3.9000000000000002E-9</v>
       </c>
       <c r="L12" t="s">
-        <v>186</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -5556,7 +5562,7 @@
         <v>1175</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>60</v>
@@ -5571,22 +5577,22 @@
         <v>300</v>
       </c>
       <c r="G13" t="s">
-        <v>187</v>
+        <v>44</v>
       </c>
       <c r="H13" t="s">
-        <v>188</v>
+        <v>45</v>
       </c>
       <c r="I13">
-        <v>4.6024119256294219E-3</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J13">
-        <v>3.049097900729492E-2</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K13">
-        <v>4.4472655813720863E-11</v>
+        <v>3.9000000000000002E-9</v>
       </c>
       <c r="L13" t="s">
-        <v>189</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -5594,7 +5600,7 @@
         <v>6798</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C14">
         <v>45</v>
@@ -5609,22 +5615,22 @@
         <v>300</v>
       </c>
       <c r="G14" t="s">
-        <v>190</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s">
-        <v>191</v>
+        <v>48</v>
       </c>
       <c r="I14">
-        <v>4.1544491960371997E-3</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J14">
-        <v>2.7523225923746449E-2</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K14">
-        <v>4.9268018893267679E-11</v>
+        <v>3.9000000000000002E-9</v>
       </c>
       <c r="L14" t="s">
-        <v>192</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -5632,7 +5638,7 @@
         <v>1288</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C15">
         <v>138</v>
@@ -5647,22 +5653,22 @@
         <v>300</v>
       </c>
       <c r="G15" t="s">
-        <v>193</v>
+        <v>50</v>
       </c>
       <c r="H15" t="s">
-        <v>194</v>
+        <v>51</v>
       </c>
       <c r="I15">
-        <v>2.3680741216752219E-3</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J15">
-        <v>1.5688491056098351E-2</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K15">
-        <v>8.6433730941109982E-11</v>
+        <v>3.9000000000000002E-9</v>
       </c>
       <c r="L15" t="s">
-        <v>195</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -5670,7 +5676,7 @@
         <v>6562</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C16">
         <v>61</v>
@@ -5685,22 +5691,22 @@
         <v>380</v>
       </c>
       <c r="G16" t="s">
-        <v>196</v>
+        <v>53</v>
       </c>
       <c r="H16" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="I16">
-        <v>8.1211485883719381E-4</v>
+        <v>2.9999999999999991E-5</v>
       </c>
       <c r="J16">
-        <v>6.6593418424649876E-3</v>
+        <v>2.4599999999999991E-4</v>
       </c>
       <c r="K16">
-        <v>7.6767632298032541E-11</v>
+        <v>4.1000000000000003E-9</v>
       </c>
       <c r="L16" t="s">
-        <v>198</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
@@ -5708,7 +5714,7 @@
         <v>1293</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C17">
         <v>78</v>
@@ -5723,22 +5729,22 @@
         <v>380</v>
       </c>
       <c r="G17" t="s">
-        <v>199</v>
+        <v>56</v>
       </c>
       <c r="H17" t="s">
-        <v>200</v>
+        <v>57</v>
       </c>
       <c r="I17">
-        <v>2.8902147532193349E-3</v>
+        <v>3.0000000000000001E-5</v>
       </c>
       <c r="J17">
-        <v>2.3699760976398549E-2</v>
+        <v>2.4600000000000012E-4</v>
       </c>
       <c r="K17">
-        <v>2.1570762102552679E-11</v>
+        <v>4.1000000000000003E-9</v>
       </c>
       <c r="L17" t="s">
-        <v>201</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -5746,7 +5752,7 @@
         <v>1176</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C18">
         <v>109</v>
@@ -5761,22 +5767,22 @@
         <v>380</v>
       </c>
       <c r="G18" t="s">
-        <v>202</v>
+        <v>59</v>
       </c>
       <c r="H18" t="s">
-        <v>203</v>
+        <v>60</v>
       </c>
       <c r="I18">
-        <v>8.211955428542142E-4</v>
+        <v>3.0000000000000001E-5</v>
       </c>
       <c r="J18">
-        <v>6.7338034514045561E-3</v>
+        <v>2.4600000000000002E-4</v>
       </c>
       <c r="K18">
-        <v>7.5918744822084579E-11</v>
+        <v>4.1000000000000003E-9</v>
       </c>
       <c r="L18" t="s">
-        <v>204</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
@@ -5784,7 +5790,7 @@
         <v>1317</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C19">
         <v>78</v>
@@ -5799,22 +5805,22 @@
         <v>380</v>
       </c>
       <c r="G19" t="s">
-        <v>205</v>
+        <v>62</v>
       </c>
       <c r="H19" t="s">
-        <v>206</v>
+        <v>63</v>
       </c>
       <c r="I19">
-        <v>1.4493920974281761E-3</v>
+        <v>3.0000000000000011E-5</v>
       </c>
       <c r="J19">
-        <v>1.1885015198911039E-2</v>
+        <v>2.4600000000000002E-4</v>
       </c>
       <c r="K19">
-        <v>4.3013988400796947E-11</v>
+        <v>4.1000000000000003E-9</v>
       </c>
       <c r="L19" t="s">
-        <v>207</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -5829,25 +5835,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>149</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>152</v>
+        <v>211</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>153</v>
+        <v>212</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -5870,7 +5876,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -5893,7 +5899,7 @@
         <v>0.04</v>
       </c>
       <c r="G3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -5916,7 +5922,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -5939,7 +5945,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -5948,37 +5954,37 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>149</v>
+        <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/Grid/test_trøndelagsnettet.xlsx
+++ b/Grid/test_trøndelagsnettet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0348cbc925570652/Master/Kraftsystemer/Kraftsystemer-2/Grid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_D66F0DED9A5C76CD19CE15FAE4E891D83F9B944B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68021297-1237-4FD7-B733-4D36A35FCEB3}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="11_D66F0DED9A5C76CD19CE15FAE4E891D83F9B944B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DEEC584-BFA7-4AA5-B31D-6DAC1B173902}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="224">
   <si>
     <t>line_id</t>
   </si>
@@ -330,12 +330,6 @@
     <t>bus</t>
   </si>
   <si>
-    <t>Unnamed: 9</t>
-  </si>
-  <si>
-    <t>Unnamed: 10</t>
-  </si>
-  <si>
     <t>Grytten</t>
   </si>
   <si>
@@ -706,6 +700,15 @@
   </si>
   <si>
     <t>B_per_m</t>
+  </si>
+  <si>
+    <t>S_max</t>
+  </si>
+  <si>
+    <t>V_max</t>
+  </si>
+  <si>
+    <t>V_min</t>
   </si>
 </sst>
 </file>
@@ -775,7 +778,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -784,6 +787,8 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -799,6 +804,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1086,10 +1095,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
@@ -1129,8 +1138,17 @@
       <c r="M1" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N1" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>30</v>
       </c>
@@ -1162,7 +1180,7 @@
         <v>100</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K22" si="0">0.25*J2</f>
+        <f>0.25*J2</f>
         <v>25</v>
       </c>
       <c r="L2">
@@ -1171,8 +1189,17 @@
       <c r="M2">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N2">
+        <v>1200</v>
+      </c>
+      <c r="O2" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>45</v>
       </c>
@@ -1201,20 +1228,29 @@
         <v>0</v>
       </c>
       <c r="J3" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K3">
-        <f t="shared" si="0"/>
-        <v>75</v>
+        <f t="shared" ref="K3:K22" si="0">0.25*J3</f>
+        <v>50</v>
       </c>
       <c r="L3">
-        <v>1150</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>90</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N3">
+        <v>1200</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>46</v>
       </c>
@@ -1255,8 +1291,17 @@
       <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N4">
+        <v>1200</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>60</v>
       </c>
@@ -1297,8 +1342,17 @@
       <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N5">
+        <v>1200</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P5">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>61</v>
       </c>
@@ -1339,8 +1393,17 @@
       <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N6">
+        <v>1200</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P6">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>62</v>
       </c>
@@ -1381,8 +1444,17 @@
       <c r="M7">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N7">
+        <v>1200</v>
+      </c>
+      <c r="O7" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>76</v>
       </c>
@@ -1423,8 +1495,17 @@
       <c r="M8">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N8">
+        <v>1200</v>
+      </c>
+      <c r="O8" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>77</v>
       </c>
@@ -1465,8 +1546,17 @@
       <c r="M9">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N9">
+        <v>1200</v>
+      </c>
+      <c r="O9" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P9">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>78</v>
       </c>
@@ -1507,8 +1597,17 @@
       <c r="M10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N10">
+        <v>1200</v>
+      </c>
+      <c r="O10" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P10">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>79</v>
       </c>
@@ -1549,8 +1648,17 @@
       <c r="M11">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N11">
+        <v>1200</v>
+      </c>
+      <c r="O11" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P11">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>80</v>
       </c>
@@ -1579,11 +1687,11 @@
         <v>0</v>
       </c>
       <c r="J12" s="3">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K12">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="L12">
         <v>40</v>
@@ -1591,8 +1699,17 @@
       <c r="M12">
         <v>45</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N12">
+        <v>1200</v>
+      </c>
+      <c r="O12" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P12">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>105</v>
       </c>
@@ -1621,11 +1738,11 @@
         <v>0</v>
       </c>
       <c r="J13" s="3">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="K13">
         <f t="shared" si="0"/>
-        <v>12.5</v>
+        <v>125</v>
       </c>
       <c r="L13">
         <v>330</v>
@@ -1633,8 +1750,17 @@
       <c r="M13">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N13">
+        <v>1200</v>
+      </c>
+      <c r="O13" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P13">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>106</v>
       </c>
@@ -1675,8 +1801,17 @@
       <c r="M14">
         <v>75</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N14">
+        <v>1200</v>
+      </c>
+      <c r="O14" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P14">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>107</v>
       </c>
@@ -1717,8 +1852,17 @@
       <c r="M15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N15">
+        <v>1200</v>
+      </c>
+      <c r="O15" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P15">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>108</v>
       </c>
@@ -1757,10 +1901,19 @@
         <v>70</v>
       </c>
       <c r="M16">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+        <v>400</v>
+      </c>
+      <c r="N16">
+        <v>1200</v>
+      </c>
+      <c r="O16" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P16">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>109</v>
       </c>
@@ -1801,8 +1954,17 @@
       <c r="M17">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N17">
+        <v>1200</v>
+      </c>
+      <c r="O17" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P17">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>138</v>
       </c>
@@ -1843,8 +2005,17 @@
       <c r="M18">
         <v>30</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N18">
+        <v>1200</v>
+      </c>
+      <c r="O18" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P18">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>139</v>
       </c>
@@ -1885,8 +2056,17 @@
       <c r="M19">
         <v>45</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N19">
+        <v>1200</v>
+      </c>
+      <c r="O19" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P19">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>141</v>
       </c>
@@ -1927,8 +2107,17 @@
       <c r="M20">
         <v>135</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N20">
+        <v>1200</v>
+      </c>
+      <c r="O20" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>161</v>
       </c>
@@ -1969,8 +2158,17 @@
       <c r="M21">
         <v>165</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N21">
+        <v>1200</v>
+      </c>
+      <c r="O21" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P21">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>176</v>
       </c>
@@ -2010,6 +2208,15 @@
       </c>
       <c r="M22">
         <v>30</v>
+      </c>
+      <c r="N22">
+        <v>1200</v>
+      </c>
+      <c r="O22" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P22">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -2019,10 +2226,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2050,22 +2257,16 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>97</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" t="s">
         <v>99</v>
-      </c>
-      <c r="B2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" t="s">
-        <v>101</v>
       </c>
       <c r="D2">
         <v>143</v>
@@ -2086,15 +2287,15 @@
         <v>8.8044759999999993</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D3">
         <v>60</v>
@@ -2115,15 +2316,15 @@
         <v>11.871930600000001</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D4">
         <v>251</v>
@@ -2144,15 +2345,15 @@
         <v>5.2955095999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D5">
         <v>160</v>
@@ -2173,15 +2374,15 @@
         <v>8.8866494000000031</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D6">
         <v>92</v>
@@ -2202,15 +2403,15 @@
         <v>10.0126685</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D7">
         <v>14</v>
@@ -2231,15 +2432,15 @@
         <v>11.08352</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D8">
         <v>140</v>
@@ -2260,15 +2461,15 @@
         <v>10.481959399999999</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D9">
         <v>157.30000000000001</v>
@@ -2289,15 +2490,15 @@
         <v>5.6666667000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D10">
         <v>259.8</v>
@@ -2318,15 +2519,15 @@
         <v>11.1900113</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D11">
         <v>46</v>
@@ -2347,15 +2548,15 @@
         <v>11.0058121</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -2376,15 +2577,15 @@
         <v>12.458487</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -2405,15 +2606,15 @@
         <v>5.9323598000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14">
         <v>5.4</v>
@@ -2434,15 +2635,15 @@
         <v>12.426399999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D15">
         <v>109</v>
@@ -2463,15 +2664,15 @@
         <v>8.0306999999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" t="s">
         <v>117</v>
-      </c>
-      <c r="B16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" t="s">
-        <v>119</v>
       </c>
       <c r="D16">
         <v>253.2</v>
@@ -2494,13 +2695,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -2523,13 +2724,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D18">
         <v>169.2</v>
@@ -2552,13 +2753,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D19">
         <v>90</v>
@@ -2581,13 +2782,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D20">
         <v>26</v>
@@ -2610,13 +2811,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D21">
         <v>40.299999999999997</v>
@@ -2639,13 +2840,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -2668,13 +2869,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D23">
         <v>6.2</v>
@@ -2697,13 +2898,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D24">
         <v>14</v>
@@ -2726,13 +2927,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -2755,13 +2956,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D26">
         <v>48.5</v>
@@ -2784,13 +2985,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D27">
         <v>85</v>
@@ -2813,13 +3014,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D28">
         <v>5.4</v>
@@ -2842,13 +3043,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -2871,13 +3072,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D30">
         <v>45</v>
@@ -2900,13 +3101,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D31">
         <v>86</v>
@@ -2929,13 +3130,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D32">
         <v>64</v>
@@ -2958,13 +3159,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D33">
         <v>319.2</v>
@@ -2987,13 +3188,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D34">
         <v>23</v>
@@ -3016,13 +3217,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D35">
         <v>60</v>
@@ -3045,13 +3246,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D36">
         <v>36</v>
@@ -3074,13 +3275,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -3103,13 +3304,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D38">
         <v>70</v>
@@ -3132,13 +3333,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D39">
         <v>19.5</v>
@@ -3161,13 +3362,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D40">
         <v>7.8</v>
@@ -3190,13 +3391,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D41">
         <v>5.8</v>
@@ -3219,13 +3420,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D42">
         <v>8</v>
@@ -3248,13 +3449,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D43">
         <v>17</v>
@@ -3277,13 +3478,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D44">
         <v>25.2</v>
@@ -3306,13 +3507,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D45">
         <v>4.0999999999999996</v>
@@ -3335,13 +3536,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -3364,13 +3565,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -3393,13 +3594,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D48">
         <v>10.4</v>
@@ -3422,13 +3623,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D49">
         <v>100</v>
@@ -3451,13 +3652,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C50" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D50">
         <v>21.7</v>
@@ -3480,13 +3681,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D51">
         <v>5.2</v>
@@ -3509,13 +3710,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D52">
         <v>5.4</v>
@@ -3538,13 +3739,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D53">
         <v>9</v>
@@ -3567,13 +3768,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B54" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C54" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D54">
         <v>5.5</v>
@@ -3596,13 +3797,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B55" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C55" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D55">
         <v>10.6</v>
@@ -3625,13 +3826,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B56" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C56" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D56">
         <v>11.5</v>
@@ -3654,13 +3855,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B57" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C57" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D57">
         <v>40</v>
@@ -3683,13 +3884,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B58" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C58" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D58">
         <v>35</v>
@@ -3712,13 +3913,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B59" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C59" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D59">
         <v>9</v>
@@ -3741,13 +3942,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B60" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D60">
         <v>16.3</v>
@@ -3770,13 +3971,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B61" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C61" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D61">
         <v>45</v>
@@ -3799,13 +4000,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B62" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C62" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D62">
         <v>8</v>
@@ -3828,13 +4029,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B63" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C63" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D63">
         <v>4.5999999999999996</v>
@@ -3857,13 +4058,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B64" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C64" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D64">
         <v>10</v>
@@ -3886,13 +4087,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B65" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C65" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D65">
         <v>36.6</v>
@@ -3915,13 +4116,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B66" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C66" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D66">
         <v>5</v>
@@ -3944,13 +4145,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B67" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C67" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D67">
         <v>3.7</v>
@@ -3973,13 +4174,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B68" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C68" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D68">
         <v>5.7</v>
@@ -4002,13 +4203,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B69" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C69" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D69">
         <v>5.6</v>
@@ -4031,13 +4232,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B70" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C70" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -4060,13 +4261,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B71" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C71" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D71">
         <v>12</v>
@@ -4089,13 +4290,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B72" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C72" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D72">
         <v>37.5</v>
@@ -4118,13 +4319,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B73" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C73" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D73">
         <v>16</v>
@@ -4147,13 +4348,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B74" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C74" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D74">
         <v>108</v>
@@ -4176,13 +4377,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B75" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D75">
         <v>28</v>
@@ -4205,13 +4406,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B76" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C76" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D76">
         <v>5</v>
@@ -4234,13 +4435,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B77" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C77" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D77">
         <v>9.5</v>
@@ -4263,13 +4464,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B78" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C78" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D78">
         <v>30</v>
@@ -4292,13 +4493,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C79" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D79">
         <v>130</v>
@@ -4321,13 +4522,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B80" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C80" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D80">
         <v>1.5</v>
@@ -4350,13 +4551,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B81" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C81" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D81">
         <v>3.5</v>
@@ -4379,13 +4580,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B82" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C82" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D82">
         <v>4.4000000000000004</v>
@@ -4408,13 +4609,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B83" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C83" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D83">
         <v>0.3</v>
@@ -4437,13 +4638,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B84" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C84" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D84">
         <v>8.1999999999999993</v>
@@ -4466,13 +4667,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C85" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D85">
         <v>4.8</v>
@@ -4495,13 +4696,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B86" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C86" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D86">
         <v>8.1</v>
@@ -4524,13 +4725,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C87" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D87">
         <v>5.5</v>
@@ -4553,13 +4754,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C88" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D88">
         <v>40</v>
@@ -4582,13 +4783,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C89" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D89">
         <v>0.4</v>
@@ -4611,13 +4812,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C90" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -4640,13 +4841,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B91" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C91" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D91">
         <v>105</v>
@@ -4669,13 +4870,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B92" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C92" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D92">
         <v>4.8</v>
@@ -4698,13 +4899,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B93" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C93" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D93">
         <v>2.4</v>
@@ -4727,13 +4928,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B94" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D94">
         <v>12.7</v>
@@ -4756,13 +4957,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B95" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C95" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D95">
         <v>12.7</v>
@@ -4785,13 +4986,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C96" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D96">
         <v>3</v>
@@ -4814,13 +5015,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B97" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C97" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D97">
         <v>13.7</v>
@@ -4843,13 +5044,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B98" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C98" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D98">
         <v>41</v>
@@ -4872,13 +5073,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B99" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C99" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D99">
         <v>1.3</v>
@@ -4901,13 +5102,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B100" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D100">
         <v>31</v>
@@ -4930,13 +5131,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B101" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C101" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D101">
         <v>6.5</v>
@@ -4959,13 +5160,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B102" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C102" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D102">
         <v>23.9</v>
@@ -4988,13 +5189,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B103" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C103" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D103">
         <v>8.4</v>
@@ -5017,13 +5218,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B104" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C104" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D104">
         <v>3.2</v>
@@ -5046,13 +5247,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B105" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C105" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D105">
         <v>5.5</v>
@@ -5080,13 +5281,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="12" max="12" width="13" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="1.36328125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5112,13 +5313,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>8</v>
@@ -5126,8 +5327,11 @@
       <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N1" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1166</v>
       </c>
@@ -5167,8 +5371,11 @@
       <c r="M2">
         <v>10943</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1334</v>
       </c>
@@ -5208,8 +5415,11 @@
       <c r="M3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1335</v>
       </c>
@@ -5246,8 +5456,11 @@
       <c r="L4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1336</v>
       </c>
@@ -5287,8 +5500,11 @@
       <c r="M5">
         <v>3343</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1165</v>
       </c>
@@ -5325,8 +5541,11 @@
       <c r="L6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N6">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1289</v>
       </c>
@@ -5363,8 +5582,11 @@
       <c r="L7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N7">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1290</v>
       </c>
@@ -5404,8 +5626,11 @@
       <c r="M8">
         <v>343321</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N8">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1291</v>
       </c>
@@ -5442,8 +5667,11 @@
       <c r="L9" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1173</v>
       </c>
@@ -5480,8 +5708,11 @@
       <c r="L10" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N10">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1174</v>
       </c>
@@ -5518,8 +5749,11 @@
       <c r="L11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N11">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1292</v>
       </c>
@@ -5556,8 +5790,11 @@
       <c r="L12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N12">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1175</v>
       </c>
@@ -5594,8 +5831,11 @@
       <c r="L13" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N13">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>6798</v>
       </c>
@@ -5632,8 +5872,11 @@
       <c r="L14" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N14">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1288</v>
       </c>
@@ -5670,8 +5913,11 @@
       <c r="L15" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N15">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>6562</v>
       </c>
@@ -5708,8 +5954,11 @@
       <c r="L16" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N16">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1293</v>
       </c>
@@ -5746,8 +5995,11 @@
       <c r="L17" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N17">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1176</v>
       </c>
@@ -5784,8 +6036,11 @@
       <c r="L18" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N18">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1317</v>
       </c>
@@ -5821,6 +6076,9 @@
       </c>
       <c r="L19" t="s">
         <v>64</v>
+      </c>
+      <c r="N19">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -5830,12 +6088,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -5844,19 +6105,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H1" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>43</v>
       </c>
@@ -5876,10 +6140,13 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+      <c r="H2" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>44</v>
       </c>
@@ -5899,10 +6166,13 @@
         <v>0.04</v>
       </c>
       <c r="G3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+      <c r="H3" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>45</v>
       </c>
@@ -5922,10 +6192,13 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+      <c r="H4" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>46</v>
       </c>
@@ -5945,7 +6218,10 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G5" t="s">
-        <v>216</v>
+        <v>214</v>
+      </c>
+      <c r="H5" s="4">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -5960,7 +6236,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -5969,7 +6245,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -5984,7 +6260,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/Grid/test_trøndelagsnettet.xlsx
+++ b/Grid/test_trøndelagsnettet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0348cbc925570652/Master/Kraftsystemer/Kraftsystemer-2/Grid/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2d06795444358214/Dokumenter/Kraftsystemer2/Kraftsystemer-2/Grid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_D66F0DED9A5C76CD19CE15FAE4E891D83F9B944B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DEEC584-BFA7-4AA5-B31D-6DAC1B173902}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="114_{602B95B0-7EC1-481A-A8A6-31C43E35FBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68F71763-46B0-485C-8C15-652DE338E48D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bus" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="239">
   <si>
     <t>line_id</t>
   </si>
@@ -709,6 +709,51 @@
   </si>
   <si>
     <t>V_min</t>
+  </si>
+  <si>
+    <t>[61.73283, 61.88593]</t>
+  </si>
+  <si>
+    <t>[5.218506, 9.063721]</t>
+  </si>
+  <si>
+    <t>[61.88593, 62.62872]</t>
+  </si>
+  <si>
+    <t>[9.063721, 10.26672]</t>
+  </si>
+  <si>
+    <t>[62.628719, 63.035662]</t>
+  </si>
+  <si>
+    <t>[10.26672, 11.72791]</t>
+  </si>
+  <si>
+    <t>[63.035662, 64.453849]</t>
+  </si>
+  <si>
+    <t>[11.72791, 11.62079]</t>
+  </si>
+  <si>
+    <t>Svelgen transformatorstasjon 132/300 kV</t>
+  </si>
+  <si>
+    <t>Brattset transformatorstasjon 132/300 kV</t>
+  </si>
+  <si>
+    <t>Brattset transformatorstasjon 132/380 kV</t>
+  </si>
+  <si>
+    <t>Namsos transformatorstasjon 300/380 kV</t>
+  </si>
+  <si>
+    <t>Svelgen 300 kV</t>
+  </si>
+  <si>
+    <t>Brattset 380 kV</t>
+  </si>
+  <si>
+    <t>Namsos 380 kV</t>
   </si>
 </sst>
 </file>
@@ -718,7 +763,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -730,6 +775,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -778,7 +828,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -789,6 +839,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -804,10 +860,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1095,10 +1147,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
@@ -1148,7 +1200,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>30</v>
       </c>
@@ -1199,7 +1251,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>45</v>
       </c>
@@ -1250,7 +1302,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>46</v>
       </c>
@@ -1301,7 +1353,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>60</v>
       </c>
@@ -1352,7 +1404,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>61</v>
       </c>
@@ -1403,7 +1455,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>62</v>
       </c>
@@ -1454,7 +1506,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>76</v>
       </c>
@@ -1505,7 +1557,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>77</v>
       </c>
@@ -1556,7 +1608,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>78</v>
       </c>
@@ -1607,7 +1659,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>79</v>
       </c>
@@ -1658,7 +1710,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>80</v>
       </c>
@@ -1709,7 +1761,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16">
       <c r="A13">
         <v>105</v>
       </c>
@@ -1760,7 +1812,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16">
       <c r="A14">
         <v>106</v>
       </c>
@@ -1811,7 +1863,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>107</v>
       </c>
@@ -1862,7 +1914,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>108</v>
       </c>
@@ -1913,7 +1965,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>109</v>
       </c>
@@ -1964,7 +2016,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>138</v>
       </c>
@@ -2015,7 +2067,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>139</v>
       </c>
@@ -2066,7 +2118,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>141</v>
       </c>
@@ -2117,7 +2169,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>161</v>
       </c>
@@ -2168,7 +2220,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>176</v>
       </c>
@@ -2216,6 +2268,206 @@
         <v>1.2</v>
       </c>
       <c r="P22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>177</v>
+      </c>
+      <c r="B23" t="s">
+        <v>236</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>300</v>
+      </c>
+      <c r="E23">
+        <v>61.73283</v>
+      </c>
+      <c r="F23">
+        <v>5.2185059999999996</v>
+      </c>
+      <c r="G23">
+        <v>100</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>1200</v>
+      </c>
+      <c r="O23" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P23">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>178</v>
+      </c>
+      <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24">
+        <v>300</v>
+      </c>
+      <c r="E24">
+        <v>62.628718999999997</v>
+      </c>
+      <c r="F24">
+        <v>10.266719999999999</v>
+      </c>
+      <c r="G24">
+        <v>100</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>1200</v>
+      </c>
+      <c r="O24" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P24">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>179</v>
+      </c>
+      <c r="B25" t="s">
+        <v>237</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25">
+        <v>380</v>
+      </c>
+      <c r="E25">
+        <v>62.628718999999997</v>
+      </c>
+      <c r="F25">
+        <v>10.266719999999999</v>
+      </c>
+      <c r="G25">
+        <v>100</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>1200</v>
+      </c>
+      <c r="O25" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>180</v>
+      </c>
+      <c r="B26" t="s">
+        <v>238</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>380</v>
+      </c>
+      <c r="E26">
+        <v>64.453849000000005</v>
+      </c>
+      <c r="F26">
+        <v>11.62079</v>
+      </c>
+      <c r="G26">
+        <v>100</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>1200</v>
+      </c>
+      <c r="O26" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P26">
         <v>0.7</v>
       </c>
     </row>
@@ -2227,9 +2479,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2258,7 +2510,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>97</v>
       </c>
@@ -2287,7 +2539,7 @@
         <v>8.8044759999999993</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -2316,7 +2568,7 @@
         <v>11.871930600000001</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -2345,7 +2597,7 @@
         <v>5.2955095999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -2374,7 +2626,7 @@
         <v>8.8866494000000031</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>105</v>
       </c>
@@ -2403,7 +2655,7 @@
         <v>10.0126685</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>106</v>
       </c>
@@ -2432,7 +2684,7 @@
         <v>11.08352</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>107</v>
       </c>
@@ -2461,7 +2713,7 @@
         <v>10.481959399999999</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>108</v>
       </c>
@@ -2490,7 +2742,7 @@
         <v>5.6666667000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>109</v>
       </c>
@@ -2519,7 +2771,7 @@
         <v>11.1900113</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -2548,7 +2800,7 @@
         <v>11.0058121</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>111</v>
       </c>
@@ -2577,7 +2829,7 @@
         <v>12.458487</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -2606,7 +2858,7 @@
         <v>5.9323598000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>113</v>
       </c>
@@ -2635,7 +2887,7 @@
         <v>12.426399999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -2664,7 +2916,7 @@
         <v>8.0306999999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -2693,7 +2945,7 @@
         <v>6.9432999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -2722,7 +2974,7 @@
         <v>8.9611000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>119</v>
       </c>
@@ -2751,7 +3003,7 @@
         <v>10.3950528</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>120</v>
       </c>
@@ -2780,7 +3032,7 @@
         <v>9.7151951999999984</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>121</v>
       </c>
@@ -2809,7 +3061,7 @@
         <v>11.439399999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>122</v>
       </c>
@@ -2838,7 +3090,7 @@
         <v>11.230700000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>123</v>
       </c>
@@ -2867,7 +3119,7 @@
         <v>7.2199947</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>124</v>
       </c>
@@ -2896,7 +3148,7 @@
         <v>5.5803419999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -2925,7 +3177,7 @@
         <v>9.3017813999999994</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>126</v>
       </c>
@@ -2954,7 +3206,7 @@
         <v>6.8948</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -2983,7 +3235,7 @@
         <v>11.1072278</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>128</v>
       </c>
@@ -3012,7 +3264,7 @@
         <v>7.8511770000000034</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
         <v>129</v>
       </c>
@@ -3041,7 +3293,7 @@
         <v>6.8848000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
         <v>130</v>
       </c>
@@ -3070,7 +3322,7 @@
         <v>7.2545709999999994</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
         <v>131</v>
       </c>
@@ -3099,7 +3351,7 @@
         <v>11.8285</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
         <v>132</v>
       </c>
@@ -3128,7 +3380,7 @@
         <v>9.7574403499999995</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
         <v>133</v>
       </c>
@@ -3157,7 +3409,7 @@
         <v>6.0833482000000014</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
         <v>134</v>
       </c>
@@ -3186,7 +3438,7 @@
         <v>7.4153287000000017</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
         <v>135</v>
       </c>
@@ -3215,7 +3467,7 @@
         <v>10.436579999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
         <v>136</v>
       </c>
@@ -3244,7 +3496,7 @@
         <v>12.036899999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
         <v>137</v>
       </c>
@@ -3273,7 +3525,7 @@
         <v>11.520841900000001</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
         <v>138</v>
       </c>
@@ -3302,7 +3554,7 @@
         <v>11.6968</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
         <v>139</v>
       </c>
@@ -3331,7 +3583,7 @@
         <v>11.239599999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
         <v>140</v>
       </c>
@@ -3360,7 +3612,7 @@
         <v>7.5333332999999989</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
         <v>141</v>
       </c>
@@ -3389,7 +3641,7 @@
         <v>8.9330416999999969</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
         <v>142</v>
       </c>
@@ -3418,7 +3670,7 @@
         <v>8.157</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
         <v>143</v>
       </c>
@@ -3447,7 +3699,7 @@
         <v>10.9664</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
         <v>144</v>
       </c>
@@ -3476,7 +3728,7 @@
         <v>6.6169454999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
         <v>145</v>
       </c>
@@ -3505,7 +3757,7 @@
         <v>6.5069116999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
         <v>146</v>
       </c>
@@ -3534,7 +3786,7 @@
         <v>11.5484121</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
         <v>147</v>
       </c>
@@ -3563,7 +3815,7 @@
         <v>6.5741103000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
         <v>148</v>
       </c>
@@ -3592,7 +3844,7 @@
         <v>5.8376893999999986</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -3621,7 +3873,7 @@
         <v>11.051768900000001</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
         <v>150</v>
       </c>
@@ -3650,7 +3902,7 @@
         <v>8.1743355999999991</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
         <v>151</v>
       </c>
@@ -3679,7 +3931,7 @@
         <v>11.763260900000001</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
         <v>152</v>
       </c>
@@ -3708,7 +3960,7 @@
         <v>5.8235750999999993</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
         <v>153</v>
       </c>
@@ -3737,7 +3989,7 @@
         <v>6.8139132</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
         <v>154</v>
       </c>
@@ -3766,7 +4018,7 @@
         <v>8.5725324999999994</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
         <v>155</v>
       </c>
@@ -3795,7 +4047,7 @@
         <v>6.9097999999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
         <v>156</v>
       </c>
@@ -3824,7 +4076,7 @@
         <v>6.0118764999999996</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
         <v>157</v>
       </c>
@@ -3853,7 +4105,7 @@
         <v>10.4582701</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
         <v>158</v>
       </c>
@@ -3882,7 +4134,7 @@
         <v>5.8372717999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
         <v>159</v>
       </c>
@@ -3911,7 +4163,7 @@
         <v>7.828136999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
         <v>160</v>
       </c>
@@ -3940,7 +4192,7 @@
         <v>6.15</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
         <v>161</v>
       </c>
@@ -3969,7 +4221,7 @@
         <v>11.04129</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
         <v>162</v>
       </c>
@@ -3998,7 +4250,7 @@
         <v>9.0890899999999988</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
         <v>163</v>
       </c>
@@ -4027,7 +4279,7 @@
         <v>5.5608660999999966</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
         <v>164</v>
       </c>
@@ -4056,7 +4308,7 @@
         <v>6.9358199999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
         <v>165</v>
       </c>
@@ -4085,7 +4337,7 @@
         <v>5.8543174000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
         <v>166</v>
       </c>
@@ -4114,7 +4366,7 @@
         <v>6.9920547000000024</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
         <v>167</v>
       </c>
@@ -4143,7 +4395,7 @@
         <v>9.8333333000000014</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
         <v>168</v>
       </c>
@@ -4172,7 +4424,7 @@
         <v>6.2766851000000008</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
         <v>169</v>
       </c>
@@ -4201,7 +4453,7 @@
         <v>6.5668392999999998</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
         <v>170</v>
       </c>
@@ -4230,7 +4482,7 @@
         <v>6.5005457999999994</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
         <v>171</v>
       </c>
@@ -4259,7 +4511,7 @@
         <v>6.5980089000000008</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
         <v>172</v>
       </c>
@@ -4288,7 +4540,7 @@
         <v>9.6333333000000021</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
         <v>173</v>
       </c>
@@ -4317,7 +4569,7 @@
         <v>8.6937046000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
         <v>174</v>
       </c>
@@ -4346,7 +4598,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
         <v>175</v>
       </c>
@@ -4375,7 +4627,7 @@
         <v>11.7372151</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
         <v>176</v>
       </c>
@@ -4404,7 +4656,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
         <v>177</v>
       </c>
@@ -4433,7 +4685,7 @@
         <v>10.0377767</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
         <v>178</v>
       </c>
@@ -4462,7 +4714,7 @@
         <v>6.5719160000000008</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
         <v>179</v>
       </c>
@@ -4491,7 +4743,7 @@
         <v>5.8013399999999997</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
         <v>180</v>
       </c>
@@ -4520,7 +4772,7 @@
         <v>9.0191520000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
         <v>181</v>
       </c>
@@ -4549,7 +4801,7 @@
         <v>9.6812501999999991</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9">
       <c r="A81" t="s">
         <v>182</v>
       </c>
@@ -4578,7 +4830,7 @@
         <v>9.7131293000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9">
       <c r="A82" t="s">
         <v>183</v>
       </c>
@@ -4607,7 +4859,7 @@
         <v>9.1879674999999992</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9">
       <c r="A83" t="s">
         <v>184</v>
       </c>
@@ -4636,7 +4888,7 @@
         <v>5.4489538999999994</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9">
       <c r="A84" t="s">
         <v>185</v>
       </c>
@@ -4665,7 +4917,7 @@
         <v>6.2465699999999984</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9">
       <c r="A85" t="s">
         <v>186</v>
       </c>
@@ -4694,7 +4946,7 @@
         <v>10.981521600000001</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
         <v>187</v>
       </c>
@@ -4723,7 +4975,7 @@
         <v>11.006936400000001</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9">
       <c r="A87" t="s">
         <v>188</v>
       </c>
@@ -4752,7 +5004,7 @@
         <v>5.1708737999999999</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9">
       <c r="A88" t="s">
         <v>189</v>
       </c>
@@ -4781,7 +5033,7 @@
         <v>8.7299540000000011</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9">
       <c r="A89" t="s">
         <v>190</v>
       </c>
@@ -4810,7 +5062,7 @@
         <v>9.1423079999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9">
       <c r="A90" t="s">
         <v>191</v>
       </c>
@@ -4839,7 +5091,7 @@
         <v>8.0138783</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9">
       <c r="A91" t="s">
         <v>192</v>
       </c>
@@ -4868,7 +5120,7 @@
         <v>10.0280798</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9">
       <c r="A92" t="s">
         <v>193</v>
       </c>
@@ -4897,7 +5149,7 @@
         <v>6.2347906999999996</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9">
       <c r="A93" t="s">
         <v>194</v>
       </c>
@@ -4926,7 +5178,7 @@
         <v>11.188310299999999</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9">
       <c r="A94" t="s">
         <v>195</v>
       </c>
@@ -4955,7 +5207,7 @@
         <v>11.4618021</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9">
       <c r="A95" t="s">
         <v>196</v>
       </c>
@@ -4984,7 +5236,7 @@
         <v>11.510163</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9">
       <c r="A96" t="s">
         <v>197</v>
       </c>
@@ -5013,7 +5265,7 @@
         <v>8.8672097000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9">
       <c r="A97" t="s">
         <v>198</v>
       </c>
@@ -5042,7 +5294,7 @@
         <v>11.4952627</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
         <v>199</v>
       </c>
@@ -5071,7 +5323,7 @@
         <v>9.8477710999999992</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
         <v>200</v>
       </c>
@@ -5100,7 +5352,7 @@
         <v>11.04129</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
         <v>201</v>
       </c>
@@ -5129,7 +5381,7 @@
         <v>9.8825433</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
         <v>202</v>
       </c>
@@ -5158,7 +5410,7 @@
         <v>9.0966266000000005</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9">
       <c r="A102" t="s">
         <v>203</v>
       </c>
@@ -5187,7 +5439,7 @@
         <v>11.916895</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9">
       <c r="A103" t="s">
         <v>204</v>
       </c>
@@ -5216,7 +5468,7 @@
         <v>8.0588759000000003</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9">
       <c r="A104" t="s">
         <v>205</v>
       </c>
@@ -5245,7 +5497,7 @@
         <v>6.8477066000000004</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
         <v>206</v>
       </c>
@@ -5281,13 +5533,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="12" max="12" width="1.36328125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="1.3671875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5331,7 +5583,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>1166</v>
       </c>
@@ -5375,7 +5627,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>1334</v>
       </c>
@@ -5419,7 +5671,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>1335</v>
       </c>
@@ -5460,7 +5712,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>1336</v>
       </c>
@@ -5504,7 +5756,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>1165</v>
       </c>
@@ -5545,7 +5797,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>1289</v>
       </c>
@@ -5586,7 +5838,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>1290</v>
       </c>
@@ -5630,7 +5882,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>1291</v>
       </c>
@@ -5671,7 +5923,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>1173</v>
       </c>
@@ -5712,7 +5964,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>1174</v>
       </c>
@@ -5753,7 +6005,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>1292</v>
       </c>
@@ -5794,7 +6046,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>1175</v>
       </c>
@@ -5835,7 +6087,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>6798</v>
       </c>
@@ -5876,7 +6128,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>1288</v>
       </c>
@@ -5917,7 +6169,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>6562</v>
       </c>
@@ -5958,7 +6210,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>1293</v>
       </c>
@@ -5999,7 +6251,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18">
         <v>1176</v>
       </c>
@@ -6040,7 +6292,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>1317</v>
       </c>
@@ -6078,6 +6330,158 @@
         <v>64</v>
       </c>
       <c r="N19">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20">
+        <v>6799</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <v>177</v>
+      </c>
+      <c r="D20">
+        <v>30</v>
+      </c>
+      <c r="E20">
+        <v>232400</v>
+      </c>
+      <c r="F20">
+        <v>300</v>
+      </c>
+      <c r="G20" t="s">
+        <v>224</v>
+      </c>
+      <c r="H20" t="s">
+        <v>225</v>
+      </c>
+      <c r="I20">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="J20">
+        <v>2.6499999999999999E-4</v>
+      </c>
+      <c r="K20">
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="N20">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21">
+        <v>6800</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>30</v>
+      </c>
+      <c r="D21">
+        <v>178</v>
+      </c>
+      <c r="E21">
+        <v>60340</v>
+      </c>
+      <c r="F21">
+        <v>300</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I21">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="J21">
+        <v>2.6499999999999999E-4</v>
+      </c>
+      <c r="K21">
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="N21">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22">
+        <v>6801</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>179</v>
+      </c>
+      <c r="D22">
+        <v>108</v>
+      </c>
+      <c r="E22">
+        <v>86520</v>
+      </c>
+      <c r="F22">
+        <v>380</v>
+      </c>
+      <c r="G22" t="s">
+        <v>228</v>
+      </c>
+      <c r="H22" t="s">
+        <v>229</v>
+      </c>
+      <c r="I22">
+        <v>3.0000000000000011E-5</v>
+      </c>
+      <c r="J22">
+        <v>2.4600000000000002E-4</v>
+      </c>
+      <c r="K22">
+        <v>4.1000000000000003E-9</v>
+      </c>
+      <c r="N22">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23">
+        <v>6802</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>108</v>
+      </c>
+      <c r="D23">
+        <v>180</v>
+      </c>
+      <c r="E23">
+        <v>157000</v>
+      </c>
+      <c r="F23">
+        <v>380</v>
+      </c>
+      <c r="G23" t="s">
+        <v>230</v>
+      </c>
+      <c r="H23" t="s">
+        <v>231</v>
+      </c>
+      <c r="I23">
+        <v>3.0000000000000011E-5</v>
+      </c>
+      <c r="J23">
+        <v>2.4600000000000002E-4</v>
+      </c>
+      <c r="K23">
+        <v>4.1000000000000003E-9</v>
+      </c>
+      <c r="N23">
         <v>600</v>
       </c>
     </row>
@@ -6088,13 +6492,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>207</v>
       </c>
@@ -6120,7 +6524,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>43</v>
       </c>
@@ -6146,7 +6550,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>44</v>
       </c>
@@ -6172,7 +6576,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>45</v>
       </c>
@@ -6198,7 +6602,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>46</v>
       </c>
@@ -6221,6 +6625,110 @@
         <v>214</v>
       </c>
       <c r="H5" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>47</v>
+      </c>
+      <c r="B6">
+        <v>161</v>
+      </c>
+      <c r="C6">
+        <v>177</v>
+      </c>
+      <c r="D6">
+        <v>0.44</v>
+      </c>
+      <c r="E6">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="F6">
+        <v>0.04</v>
+      </c>
+      <c r="G6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H6" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>48</v>
+      </c>
+      <c r="B7">
+        <v>46</v>
+      </c>
+      <c r="C7">
+        <v>178</v>
+      </c>
+      <c r="D7">
+        <v>0.44</v>
+      </c>
+      <c r="E7">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="F7">
+        <v>0.04</v>
+      </c>
+      <c r="G7" t="s">
+        <v>233</v>
+      </c>
+      <c r="H7" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>49</v>
+      </c>
+      <c r="B8">
+        <v>46</v>
+      </c>
+      <c r="C8">
+        <v>179</v>
+      </c>
+      <c r="D8">
+        <v>0.34736800000000001</v>
+      </c>
+      <c r="E8">
+        <v>5.5999999999999995E-4</v>
+      </c>
+      <c r="F8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>234</v>
+      </c>
+      <c r="H8" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17.399999999999999" customHeight="1">
+      <c r="A9">
+        <v>50</v>
+      </c>
+      <c r="B9">
+        <v>176</v>
+      </c>
+      <c r="C9">
+        <v>180</v>
+      </c>
+      <c r="D9">
+        <v>0.78947400000000001</v>
+      </c>
+      <c r="E9">
+        <v>5.5999999999999995E-4</v>
+      </c>
+      <c r="F9">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="H9" s="4">
         <v>300</v>
       </c>
     </row>
@@ -6232,9 +6740,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>215</v>
       </c>

--- a/Grid/test_trøndelagsnettet.xlsx
+++ b/Grid/test_trøndelagsnettet.xlsx
@@ -1,17 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2d06795444358214/Dokumenter/Kraftsystemer2/Kraftsystemer-2/Grid/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="114_{602B95B0-7EC1-481A-A8A6-31C43E35FBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68F71763-46B0-485C-8C15-652DE338E48D}"/>
-  <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="bus" sheetId="1" r:id="rId1"/>
     <sheet name="gen" sheetId="2" r:id="rId2"/>
@@ -19,767 +9,44 @@
     <sheet name="trafo" sheetId="4" r:id="rId4"/>
     <sheet name="link" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="239">
-  <si>
-    <t>line_id</t>
-  </si>
-  <si>
-    <t>area0</t>
-  </si>
-  <si>
-    <t>bus0</t>
-  </si>
-  <si>
-    <t>bus1</t>
-  </si>
-  <si>
-    <t>length</t>
-  </si>
-  <si>
-    <t>Vbase</t>
-  </si>
-  <si>
-    <t>lat</t>
-  </si>
-  <si>
-    <t>lon</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>eic code</t>
-  </si>
-  <si>
-    <t>NO3</t>
-  </si>
-  <si>
-    <t>[63.0581865391036, 63.169235, 63.271747122419]</t>
-  </si>
-  <si>
-    <t>[9.6024199750926, 9.95773300000001, 9.93306218856054]</t>
-  </si>
-  <si>
-    <t>Thamshavn trafostasjon – Grana koblingsstasjon</t>
-  </si>
-  <si>
-    <t>[62.6815788399503, 62.6288473888959]</t>
-  </si>
-  <si>
-    <t>[10.1228770726635, 10.2663749273365]</t>
-  </si>
-  <si>
-    <t>Brattset trafostasjon – Brattset trafostasjon</t>
-  </si>
-  <si>
-    <t>3rr4</t>
-  </si>
-  <si>
-    <t>[62.764642333228, 62.6818480622148]</t>
-  </si>
-  <si>
-    <t>[9.93059299951052, 10.1222020004895]</t>
-  </si>
-  <si>
-    <t>[63.0578905163084, 62.7649652979347]</t>
-  </si>
-  <si>
-    <t>[9.60225399160166, 9.93006400839835]</t>
-  </si>
-  <si>
-    <t>Grana koblingsstasjon – Brattset trafostasjon</t>
-  </si>
-  <si>
-    <t>[62.4779336946648, 61.7329656956376]</t>
-  </si>
-  <si>
-    <t>[7.03366082879706, 5.21884217120294]</t>
-  </si>
-  <si>
-    <t>Ørskog trafostasjon – Svelgen trafostasjon</t>
-  </si>
-  <si>
-    <t>[63.979469495752, 63.951246, 63.7796426966659]</t>
-  </si>
-  <si>
-    <t>[11.4783430752882, 11.578217, 11.4725900216729]</t>
-  </si>
-  <si>
-    <t>Ogndal trafostasjon – Verdal trafostasjon</t>
-  </si>
-  <si>
-    <t>[63.7792842667966, 63.4574296446683]</t>
-  </si>
-  <si>
-    <t>[11.4722350100571, 11.0181519899429]</t>
-  </si>
-  <si>
-    <t>Verdal trafostasjon – Eidum trafostasjon</t>
-  </si>
-  <si>
-    <t>[63.4013872743893, 63.423488, 63.4571907093831]</t>
-  </si>
-  <si>
-    <t>[10.4402013779148, 10.813293, 11.0174939283141]</t>
-  </si>
-  <si>
-    <t>Eidum trafostasjon – Strinda koblingsstasjon</t>
-  </si>
-  <si>
-    <t>[63.779267150403, 63.703506, 63.409354, 63.2769667913878]</t>
-  </si>
-  <si>
-    <t>[11.4726336570695, 11.538391, 11.15387, 10.4580241866236]</t>
-  </si>
-  <si>
-    <t>Verdal trafostasjon – Klæbu transformatorstasjon</t>
-  </si>
-  <si>
-    <t>[63.2770887040084, 63.4011611611364]</t>
-  </si>
-  <si>
-    <t>[10.4575822753626, 10.4397867246374]</t>
-  </si>
-  <si>
-    <t>Strinda koblingsstasjon – Klæbu transformatorstasjon</t>
-  </si>
-  <si>
-    <t>[63.2719119610727, 63.268241, 63.23672, 63.2768450273625]</t>
-  </si>
-  <si>
-    <t>[9.93345548452976, 9.979706, 10.04837, 10.4571728802973]</t>
-  </si>
-  <si>
-    <t>Klæbu transformatorstasjon – Orkdal transformatorstasjon</t>
-  </si>
-  <si>
-    <t>[62.6799952696754, 63.021959, 63.202068, 63.2717982207385]</t>
-  </si>
-  <si>
-    <t>[8.48028947595439, 8.897552, 9.79156500000001, 9.93271247746952]</t>
-  </si>
-  <si>
-    <t>Orkdal transformatorstasjon – Aura trafostasjon</t>
-  </si>
-  <si>
-    <t>[61.8861304294624, 62.6796217603448]</t>
-  </si>
-  <si>
-    <t>[9.06357629708208, 8.48021670291793]</t>
-  </si>
-  <si>
-    <t>Aura trafostasjon – Vågåmo trafo stasjon</t>
-  </si>
-  <si>
-    <t>[63.9797705313635, 64.4536577724636]</t>
-  </si>
-  <si>
-    <t>[11.4780240828036, 11.6207309171964]</t>
-  </si>
-  <si>
-    <t>Ogndal trafostasjon – Namsos (Statnett) trafostasjon</t>
-  </si>
-  <si>
-    <t>[62.5263493502315, 62.6797261154976]</t>
-  </si>
-  <si>
-    <t>[7.79520216211446, 8.47966983788554]</t>
-  </si>
-  <si>
-    <t>Viklandet trafostasjon – Grytten trafostasjon</t>
-  </si>
-  <si>
-    <t>[63.2769332188306, 63.325632, 63.085435, 62.6800121989769]</t>
-  </si>
-  <si>
-    <t>[10.4571743955897, 9.986572, 8.751984, 8.480202620587]</t>
-  </si>
-  <si>
-    <t>Klæbu transformatorstasjon – Viklandet trafostasjon</t>
-  </si>
-  <si>
-    <t>[62.4780980928918, 62.5262309524377]</t>
-  </si>
-  <si>
-    <t>[7.03444016980177, 7.79435683019823]</t>
-  </si>
-  <si>
-    <t>Ørskog trafostasjon – Grytten trafostasjon</t>
-  </si>
-  <si>
-    <t>[63.0357063153294, 63.061804, 63.22373, 63.2768185449166]</t>
-  </si>
-  <si>
-    <t>[11.7274675384392, 11.469727, 10.778961, 10.4580312550914]</t>
-  </si>
-  <si>
-    <t>Klæbu transformatorstasjon – Nea trafostasjon</t>
-  </si>
-  <si>
-    <t>bus_id</t>
-  </si>
-  <si>
-    <t>bidz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S_base [MVA] </t>
-  </si>
-  <si>
-    <t>V [P.U]</t>
-  </si>
-  <si>
-    <t>Angle [rad]</t>
-  </si>
-  <si>
-    <t>P_gen</t>
-  </si>
-  <si>
-    <t>Q_gen</t>
-  </si>
-  <si>
-    <t>P_load</t>
-  </si>
-  <si>
-    <t>Q_load</t>
-  </si>
-  <si>
-    <t>Vågåmo trafo stasjon</t>
-  </si>
-  <si>
-    <t>Aura trafostasjon</t>
-  </si>
-  <si>
-    <t>Brattset trafostasjon</t>
-  </si>
-  <si>
-    <t>Orkdal transformatorstasjon</t>
-  </si>
-  <si>
-    <t>Viklandet trafostasjon</t>
-  </si>
-  <si>
-    <t>Klæbu transformatorstasjon</t>
-  </si>
-  <si>
-    <t>Thamshavn trafostasjon</t>
-  </si>
-  <si>
-    <t>Grytten trafostasjon</t>
-  </si>
-  <si>
-    <t>Verdal trafostasjon</t>
-  </si>
-  <si>
-    <t>Strinda koblingsstasjon</t>
-  </si>
-  <si>
-    <t>Grana koblingsstasjon</t>
-  </si>
-  <si>
-    <t>Nea trafostasjon</t>
-  </si>
-  <si>
-    <t>Ørskog trafostasjon</t>
-  </si>
-  <si>
-    <t>Ogndal trafostasjon</t>
-  </si>
-  <si>
-    <t>Eidum trafostasjon</t>
-  </si>
-  <si>
-    <t>Svelgen trafostasjon</t>
-  </si>
-  <si>
-    <t>Namsos (Statnett) trafostasjon</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>type2</t>
-  </si>
-  <si>
-    <t>Pmax</t>
-  </si>
-  <si>
-    <t>Qmax</t>
-  </si>
-  <si>
-    <t>Qmin</t>
-  </si>
-  <si>
-    <t>bus</t>
-  </si>
-  <si>
-    <t>Grytten</t>
-  </si>
-  <si>
-    <t>Hydro</t>
-  </si>
-  <si>
-    <t>Reservoir</t>
-  </si>
-  <si>
-    <t>Tevla</t>
-  </si>
-  <si>
-    <t>Pumped Storage</t>
-  </si>
-  <si>
-    <t>Svelgfoss</t>
-  </si>
-  <si>
-    <t>Run-Of-River</t>
-  </si>
-  <si>
-    <t>Driva</t>
-  </si>
-  <si>
-    <t>Brattset</t>
-  </si>
-  <si>
-    <t>Brattingfoss</t>
-  </si>
-  <si>
-    <t>Bratsberg</t>
-  </si>
-  <si>
-    <t>Askara</t>
-  </si>
-  <si>
-    <t>Nea</t>
-  </si>
-  <si>
-    <t>Mosvik</t>
-  </si>
-  <si>
-    <t>Ovre fiskumfoss</t>
-  </si>
-  <si>
-    <t>Harpefossen</t>
-  </si>
-  <si>
-    <t>Knutfoss</t>
-  </si>
-  <si>
-    <t>Oyberget</t>
-  </si>
-  <si>
-    <t>Rka nyhamna</t>
-  </si>
-  <si>
-    <t>Thermal</t>
-  </si>
-  <si>
-    <t>OCGT</t>
-  </si>
-  <si>
-    <t>Midtre tessa</t>
-  </si>
-  <si>
-    <t>Trolheim</t>
-  </si>
-  <si>
-    <t>Grana</t>
-  </si>
-  <si>
-    <t>Gresslifoss</t>
-  </si>
-  <si>
-    <t>Hegsetfoss</t>
-  </si>
-  <si>
-    <t>Istad</t>
-  </si>
-  <si>
-    <t>Gjerdsvik</t>
-  </si>
-  <si>
-    <t>Eidefossen</t>
-  </si>
-  <si>
-    <t>Fausa</t>
-  </si>
-  <si>
-    <t>Follafoss</t>
-  </si>
-  <si>
-    <t>Framruste</t>
-  </si>
-  <si>
-    <t>Furset</t>
-  </si>
-  <si>
-    <t>Norddalen</t>
-  </si>
-  <si>
-    <t>Vessingfoss</t>
-  </si>
-  <si>
-    <t>Svorkmo</t>
-  </si>
-  <si>
-    <t>Tussa</t>
-  </si>
-  <si>
-    <t>Tafjord</t>
-  </si>
-  <si>
-    <t>Fjaremsfossen</t>
-  </si>
-  <si>
-    <t>Bogna</t>
-  </si>
-  <si>
-    <t>Aunfoss</t>
-  </si>
-  <si>
-    <t>Fossan</t>
-  </si>
-  <si>
-    <t>Nedrenea</t>
-  </si>
-  <si>
-    <t>Litledalen</t>
-  </si>
-  <si>
-    <t>Kvitfossen</t>
-  </si>
-  <si>
-    <t>Kanstadbotn</t>
-  </si>
-  <si>
-    <t>Julskaret</t>
-  </si>
-  <si>
-    <t>Innvik</t>
-  </si>
-  <si>
-    <t>Byrkjelo</t>
-  </si>
-  <si>
-    <t>Byafossen</t>
-  </si>
-  <si>
-    <t>Brunstad</t>
-  </si>
-  <si>
-    <t>Brekkefoss</t>
-  </si>
-  <si>
-    <t>Asen</t>
-  </si>
-  <si>
-    <t>Eiriksdal</t>
-  </si>
-  <si>
-    <t>Funna</t>
-  </si>
-  <si>
-    <t>Hopselva</t>
-  </si>
-  <si>
-    <t>Giskemo</t>
-  </si>
-  <si>
-    <t>Fossheim</t>
-  </si>
-  <si>
-    <t>Embla</t>
-  </si>
-  <si>
-    <t>Eid</t>
-  </si>
-  <si>
-    <t>Lokaunet</t>
-  </si>
-  <si>
-    <t>Amela</t>
-  </si>
-  <si>
-    <t>Skjak</t>
-  </si>
-  <si>
-    <t>Skogheim</t>
-  </si>
-  <si>
-    <t>Usma selbu</t>
-  </si>
-  <si>
-    <t>Soa</t>
-  </si>
-  <si>
-    <t>Sorbrandal</t>
-  </si>
-  <si>
-    <t>Stadheim</t>
-  </si>
-  <si>
-    <t>Steinsvik</t>
-  </si>
-  <si>
-    <t>Stordal</t>
-  </si>
-  <si>
-    <t>Skulafossen</t>
-  </si>
-  <si>
-    <t>Trysilfossen</t>
-  </si>
-  <si>
-    <t>Urke</t>
-  </si>
-  <si>
-    <t>Trandal</t>
-  </si>
-  <si>
-    <t>Sykkylven</t>
-  </si>
-  <si>
-    <t>Vassli</t>
-  </si>
-  <si>
-    <t>Tjeldbergodden</t>
-  </si>
-  <si>
-    <t>Morre</t>
-  </si>
-  <si>
-    <t>Meraker</t>
-  </si>
-  <si>
-    <t>Osbu</t>
-  </si>
-  <si>
-    <t>Osen</t>
-  </si>
-  <si>
-    <t>Riksheimdal</t>
-  </si>
-  <si>
-    <t>Oksenelvane</t>
-  </si>
-  <si>
-    <t>Trollheim</t>
-  </si>
-  <si>
-    <t>Agdenes</t>
-  </si>
-  <si>
-    <t>Aselva</t>
-  </si>
-  <si>
-    <t>Brandaa</t>
-  </si>
-  <si>
-    <t>Bryggja</t>
-  </si>
-  <si>
-    <t>Eidsfossen sfe</t>
-  </si>
-  <si>
-    <t>Eidum</t>
-  </si>
-  <si>
-    <t>Fossan halogalan</t>
-  </si>
-  <si>
-    <t>Fr.stad bioel</t>
-  </si>
-  <si>
-    <t>Groa</t>
-  </si>
-  <si>
-    <t>Holla</t>
-  </si>
-  <si>
-    <t>Hopen</t>
-  </si>
-  <si>
-    <t>Innset</t>
-  </si>
-  <si>
-    <t>Jardola</t>
-  </si>
-  <si>
-    <t>Kassdalen</t>
-  </si>
-  <si>
-    <t>Kurasfossen</t>
-  </si>
-  <si>
-    <t>Namsos</t>
-  </si>
-  <si>
-    <t>Nordsvorka</t>
-  </si>
-  <si>
-    <t>Ogndal</t>
-  </si>
-  <si>
-    <t>Orkdal</t>
-  </si>
-  <si>
-    <t>Selbu</t>
-  </si>
-  <si>
-    <t>Thamshavn</t>
-  </si>
-  <si>
-    <t>Vagamo</t>
-  </si>
-  <si>
-    <t>Verdal</t>
-  </si>
-  <si>
-    <t>Verma</t>
-  </si>
-  <si>
-    <t>Via</t>
-  </si>
-  <si>
-    <t>Viddal</t>
-  </si>
-  <si>
-    <t>transformer_id</t>
-  </si>
-  <si>
-    <t>ratio</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Klæbu transformatorstasjon – Klæbu transformatorstasjon</t>
-  </si>
-  <si>
-    <t>Thamshavn trafostasjon – Orkdal transformatorstasjon</t>
-  </si>
-  <si>
-    <t>Ørskog trafostasjon – Ørskog trafostasjon</t>
-  </si>
-  <si>
-    <t>Aura trafostasjon – Viklandet trafostasjon</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>area1</t>
-  </si>
-  <si>
-    <t>Pinj</t>
-  </si>
-  <si>
-    <t>R_per_m</t>
-  </si>
-  <si>
-    <t>X_per_m</t>
-  </si>
-  <si>
-    <t>B_per_m</t>
-  </si>
-  <si>
-    <t>S_max</t>
-  </si>
-  <si>
-    <t>V_max</t>
-  </si>
-  <si>
-    <t>V_min</t>
-  </si>
-  <si>
-    <t>[61.73283, 61.88593]</t>
-  </si>
-  <si>
-    <t>[5.218506, 9.063721]</t>
-  </si>
-  <si>
-    <t>[61.88593, 62.62872]</t>
-  </si>
-  <si>
-    <t>[9.063721, 10.26672]</t>
-  </si>
-  <si>
-    <t>[62.628719, 63.035662]</t>
-  </si>
-  <si>
-    <t>[10.26672, 11.72791]</t>
-  </si>
-  <si>
-    <t>[63.035662, 64.453849]</t>
-  </si>
-  <si>
-    <t>[11.72791, 11.62079]</t>
-  </si>
-  <si>
-    <t>Svelgen transformatorstasjon 132/300 kV</t>
-  </si>
-  <si>
-    <t>Brattset transformatorstasjon 132/300 kV</t>
-  </si>
-  <si>
-    <t>Brattset transformatorstasjon 132/380 kV</t>
-  </si>
-  <si>
-    <t>Namsos transformatorstasjon 300/380 kV</t>
-  </si>
-  <si>
-    <t>Svelgen 300 kV</t>
-  </si>
-  <si>
-    <t>Brattset 380 kV</t>
-  </si>
-  <si>
-    <t>Namsos 380 kV</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="2">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -790,36 +57,10 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -828,37 +69,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -937,6 +155,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -971,6 +190,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1005,20 +225,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1140,81 +356,119 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P26"/>
-  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>bus_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>bidz</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Vbase</v>
+      </c>
+      <c r="E1" t="str">
+        <v>lat</v>
+      </c>
+      <c r="F1" t="str">
+        <v>lon</v>
+      </c>
+      <c r="G1" t="str">
+        <v xml:space="preserve">S_base [MVA] </v>
+      </c>
+      <c r="H1" t="str">
+        <v>V [P.U]</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Angle [rad]</v>
+      </c>
+      <c r="J1" t="str">
+        <v>P_gen</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Q_gen</v>
+      </c>
+      <c r="L1" t="str">
+        <v>P_load</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Q_load</v>
+      </c>
+      <c r="N1" t="str">
+        <v>S_max</v>
+      </c>
+      <c r="O1" t="str">
+        <v>V_max</v>
+      </c>
+      <c r="P1" t="str">
+        <v>V_min</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
+      <c r="B2" t="str">
+        <v>Vågåmo trafo stasjon</v>
+      </c>
+      <c r="C2" t="str">
+        <v>NO3</v>
       </c>
       <c r="D2">
         <v>300</v>
       </c>
       <c r="E2">
-        <v>61.885931000000006</v>
+        <v>61.88593100000001</v>
       </c>
       <c r="F2">
         <v>9.063721000000001</v>
@@ -1228,11 +482,10 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2">
         <v>100</v>
       </c>
       <c r="K2">
-        <f>0.25*J2</f>
         <v>25</v>
       </c>
       <c r="L2">
@@ -1244,31 +497,31 @@
       <c r="N2">
         <v>1200</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2">
         <v>1.2</v>
       </c>
       <c r="P2">
         <v>0.7</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3">
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
+      <c r="B3" t="str">
+        <v>Aura trafostasjon</v>
+      </c>
+      <c r="C3" t="str">
+        <v>NO3</v>
       </c>
       <c r="D3">
         <v>300</v>
       </c>
       <c r="E3">
-        <v>62.679816000000002</v>
+        <v>62.679816</v>
       </c>
       <c r="F3">
-        <v>8.4800720000000087</v>
+        <v>8.480072000000009</v>
       </c>
       <c r="G3">
         <v>100</v>
@@ -1279,11 +532,10 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3">
         <v>200</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K22" si="0">0.25*J3</f>
         <v>50</v>
       </c>
       <c r="L3">
@@ -1295,28 +547,28 @@
       <c r="N3">
         <v>1200</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3">
         <v>1.2</v>
       </c>
       <c r="P3">
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4">
       <c r="A4">
         <v>46</v>
       </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
+      <c r="B4" t="str">
+        <v>Brattset trafostasjon</v>
+      </c>
+      <c r="C4" t="str">
+        <v>NO3</v>
       </c>
       <c r="D4">
         <v>132</v>
       </c>
       <c r="E4">
-        <v>62.628718999999997</v>
+        <v>62.628719</v>
       </c>
       <c r="F4">
         <v>10.266724</v>
@@ -1330,11 +582,10 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L4">
@@ -1346,28 +597,28 @@
       <c r="N4">
         <v>1200</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O4">
         <v>1.2</v>
       </c>
       <c r="P4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5">
       <c r="A5">
         <v>60</v>
       </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
+      <c r="B5" t="str">
+        <v>Orkdal transformatorstasjon</v>
+      </c>
+      <c r="C5" t="str">
+        <v>NO3</v>
       </c>
       <c r="D5">
         <v>300</v>
       </c>
       <c r="E5">
-        <v>63.271946999999997</v>
+        <v>63.271947</v>
       </c>
       <c r="F5">
         <v>9.933014</v>
@@ -1381,11 +632,10 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L5">
@@ -1397,31 +647,31 @@
       <c r="N5">
         <v>1200</v>
       </c>
-      <c r="O5" s="5">
+      <c r="O5">
         <v>1.2</v>
       </c>
       <c r="P5">
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6">
       <c r="A6">
         <v>61</v>
       </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
+      <c r="B6" t="str">
+        <v>Viklandet trafostasjon</v>
+      </c>
+      <c r="C6" t="str">
+        <v>NO3</v>
       </c>
       <c r="D6">
         <v>380</v>
       </c>
       <c r="E6">
-        <v>62.679816000000002</v>
+        <v>62.679816</v>
       </c>
       <c r="F6">
-        <v>8.4800720000000087</v>
+        <v>8.480072000000009</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -1432,11 +682,10 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L6">
@@ -1448,31 +697,31 @@
       <c r="N6">
         <v>1200</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6">
         <v>1.2</v>
       </c>
       <c r="P6">
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7">
       <c r="A7">
         <v>62</v>
       </c>
-      <c r="B7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
+      <c r="B7" t="str">
+        <v>Brattset trafostasjon</v>
+      </c>
+      <c r="C7" t="str">
+        <v>NO3</v>
       </c>
       <c r="D7">
         <v>132</v>
       </c>
       <c r="E7">
-        <v>62.681707000000003</v>
+        <v>62.681707</v>
       </c>
       <c r="F7">
-        <v>10.122528000000001</v>
+        <v>10.122528</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -1483,11 +732,10 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="L7">
@@ -1499,22 +747,22 @@
       <c r="N7">
         <v>1200</v>
       </c>
-      <c r="O7" s="5">
+      <c r="O7">
         <v>1.2</v>
       </c>
       <c r="P7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8">
       <c r="A8">
         <v>76</v>
       </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
+      <c r="B8" t="str">
+        <v>Klæbu transformatorstasjon</v>
+      </c>
+      <c r="C8" t="str">
+        <v>NO3</v>
       </c>
       <c r="D8">
         <v>300</v>
@@ -1534,11 +782,10 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8">
         <v>50</v>
       </c>
       <c r="K8">
-        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
       <c r="L8">
@@ -1550,28 +797,28 @@
       <c r="N8">
         <v>1200</v>
       </c>
-      <c r="O8" s="5">
+      <c r="O8">
         <v>1.2</v>
       </c>
       <c r="P8">
         <v>0.7</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9">
       <c r="A9">
         <v>77</v>
       </c>
-      <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
+      <c r="B9" t="str">
+        <v>Thamshavn trafostasjon</v>
+      </c>
+      <c r="C9" t="str">
+        <v>NO3</v>
       </c>
       <c r="D9">
         <v>132</v>
       </c>
       <c r="E9">
-        <v>63.271946999999997</v>
+        <v>63.271947</v>
       </c>
       <c r="F9">
         <v>9.933014</v>
@@ -1585,11 +832,10 @@
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9">
         <v>50</v>
       </c>
       <c r="K9">
-        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
       <c r="L9">
@@ -1601,22 +847,22 @@
       <c r="N9">
         <v>1200</v>
       </c>
-      <c r="O9" s="5">
+      <c r="O9">
         <v>1.2</v>
       </c>
       <c r="P9">
         <v>0.7</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10">
       <c r="A10">
         <v>78</v>
       </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
+      <c r="B10" t="str">
+        <v>Klæbu transformatorstasjon</v>
+      </c>
+      <c r="C10" t="str">
+        <v>NO3</v>
       </c>
       <c r="D10">
         <v>380</v>
@@ -1636,11 +882,10 @@
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L10">
@@ -1652,31 +897,31 @@
       <c r="N10">
         <v>1200</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O10">
         <v>1.2</v>
       </c>
       <c r="P10">
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11">
       <c r="A11">
         <v>79</v>
       </c>
-      <c r="B11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
+      <c r="B11" t="str">
+        <v>Grytten trafostasjon</v>
+      </c>
+      <c r="C11" t="str">
+        <v>NO3</v>
       </c>
       <c r="D11">
         <v>380</v>
       </c>
       <c r="E11">
-        <v>62.526259000000003</v>
+        <v>62.526259</v>
       </c>
       <c r="F11">
-        <v>7.7948000000000004</v>
+        <v>7.7948</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -1687,11 +932,10 @@
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11">
         <v>200</v>
       </c>
       <c r="K11">
-        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="L11">
@@ -1703,31 +947,31 @@
       <c r="N11">
         <v>1200</v>
       </c>
-      <c r="O11" s="5">
+      <c r="O11">
         <v>1.2</v>
       </c>
       <c r="P11">
         <v>0.7</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12">
       <c r="A12">
         <v>80</v>
       </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
+      <c r="B12" t="str">
+        <v>Brattset trafostasjon</v>
+      </c>
+      <c r="C12" t="str">
+        <v>NO3</v>
       </c>
       <c r="D12">
         <v>132</v>
       </c>
       <c r="E12">
-        <v>62.764782999999987</v>
+        <v>62.76478299999999</v>
       </c>
       <c r="F12">
-        <v>9.9302670000000095</v>
+        <v>9.93026700000001</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -1738,11 +982,10 @@
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12">
         <v>200</v>
       </c>
       <c r="K12">
-        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="L12">
@@ -1754,31 +997,31 @@
       <c r="N12">
         <v>1200</v>
       </c>
-      <c r="O12" s="5">
+      <c r="O12">
         <v>1.2</v>
       </c>
       <c r="P12">
         <v>0.7</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13">
       <c r="A13">
         <v>105</v>
       </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
+      <c r="B13" t="str">
+        <v>Verdal trafostasjon</v>
+      </c>
+      <c r="C13" t="str">
+        <v>NO3</v>
       </c>
       <c r="D13">
         <v>300</v>
       </c>
       <c r="E13">
-        <v>63.779451999999999</v>
+        <v>63.779452</v>
       </c>
       <c r="F13">
-        <v>11.472473000000001</v>
+        <v>11.472473</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -1789,11 +1032,10 @@
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13">
         <v>500</v>
       </c>
       <c r="K13">
-        <f t="shared" si="0"/>
         <v>125</v>
       </c>
       <c r="L13">
@@ -1805,31 +1047,31 @@
       <c r="N13">
         <v>1200</v>
       </c>
-      <c r="O13" s="5">
+      <c r="O13">
         <v>1.2</v>
       </c>
       <c r="P13">
         <v>0.7</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14">
       <c r="A14">
         <v>106</v>
       </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
+      <c r="B14" t="str">
+        <v>Strinda koblingsstasjon</v>
+      </c>
+      <c r="C14" t="str">
+        <v>NO3</v>
       </c>
       <c r="D14">
         <v>300</v>
       </c>
       <c r="E14">
-        <v>63.401361000000001</v>
+        <v>63.401361</v>
       </c>
       <c r="F14">
-        <v>10.439757999999999</v>
+        <v>10.439758</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -1840,11 +1082,10 @@
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14">
         <v>250</v>
       </c>
       <c r="K14">
-        <f t="shared" si="0"/>
         <v>62.5</v>
       </c>
       <c r="L14">
@@ -1856,31 +1097,31 @@
       <c r="N14">
         <v>1200</v>
       </c>
-      <c r="O14" s="5">
+      <c r="O14">
         <v>1.2</v>
       </c>
       <c r="P14">
         <v>0.7</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15">
       <c r="A15">
         <v>107</v>
       </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
+      <c r="B15" t="str">
+        <v>Grana koblingsstasjon</v>
+      </c>
+      <c r="C15" t="str">
+        <v>NO3</v>
       </c>
       <c r="D15">
         <v>132</v>
       </c>
       <c r="E15">
-        <v>63.058070999999998</v>
+        <v>63.058071</v>
       </c>
       <c r="F15">
-        <v>9.6020509999999994</v>
+        <v>9.602051</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -1891,11 +1132,10 @@
       <c r="I15">
         <v>0</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15">
         <v>250</v>
       </c>
       <c r="K15">
-        <f t="shared" si="0"/>
         <v>62.5</v>
       </c>
       <c r="L15">
@@ -1907,28 +1147,28 @@
       <c r="N15">
         <v>1200</v>
       </c>
-      <c r="O15" s="5">
+      <c r="O15">
         <v>1.2</v>
       </c>
       <c r="P15">
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16">
       <c r="A16">
         <v>108</v>
       </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>10</v>
+      <c r="B16" t="str">
+        <v>Nea trafostasjon</v>
+      </c>
+      <c r="C16" t="str">
+        <v>NO3</v>
       </c>
       <c r="D16">
         <v>380</v>
       </c>
       <c r="E16">
-        <v>63.035662000000002</v>
+        <v>63.035662</v>
       </c>
       <c r="F16">
         <v>11.727905</v>
@@ -1942,11 +1182,10 @@
       <c r="I16">
         <v>0</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16">
         <v>450</v>
       </c>
       <c r="K16">
-        <f t="shared" si="0"/>
         <v>112.5</v>
       </c>
       <c r="L16">
@@ -1958,31 +1197,31 @@
       <c r="N16">
         <v>1200</v>
       </c>
-      <c r="O16" s="5">
+      <c r="O16">
         <v>1.2</v>
       </c>
       <c r="P16">
         <v>0.7</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17">
       <c r="A17">
         <v>109</v>
       </c>
-      <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" t="s">
-        <v>10</v>
+      <c r="B17" t="str">
+        <v>Ørskog trafostasjon</v>
+      </c>
+      <c r="C17" t="str">
+        <v>NO3</v>
       </c>
       <c r="D17">
         <v>380</v>
       </c>
       <c r="E17">
-        <v>62.478070000000002</v>
+        <v>62.47807</v>
       </c>
       <c r="F17">
-        <v>7.0339970000000003</v>
+        <v>7.033997</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -1993,11 +1232,10 @@
       <c r="I17">
         <v>0</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17">
         <v>50</v>
       </c>
       <c r="K17">
-        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
       <c r="L17">
@@ -2009,28 +1247,28 @@
       <c r="N17">
         <v>1200</v>
       </c>
-      <c r="O17" s="5">
+      <c r="O17">
         <v>1.2</v>
       </c>
       <c r="P17">
         <v>0.7</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18">
       <c r="A18">
         <v>138</v>
       </c>
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>10</v>
+      <c r="B18" t="str">
+        <v>Ogndal trafostasjon</v>
+      </c>
+      <c r="C18" t="str">
+        <v>NO3</v>
       </c>
       <c r="D18">
         <v>300</v>
       </c>
       <c r="E18">
-        <v>63.979576000000002</v>
+        <v>63.979576</v>
       </c>
       <c r="F18">
         <v>11.477966</v>
@@ -2044,11 +1282,10 @@
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="L18">
@@ -2060,31 +1297,31 @@
       <c r="N18">
         <v>1200</v>
       </c>
-      <c r="O18" s="5">
+      <c r="O18">
         <v>1.2</v>
       </c>
       <c r="P18">
         <v>0.7</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19">
       <c r="A19">
         <v>139</v>
       </c>
-      <c r="B19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" t="s">
-        <v>10</v>
+      <c r="B19" t="str">
+        <v>Eidum trafostasjon</v>
+      </c>
+      <c r="C19" t="str">
+        <v>NO3</v>
       </c>
       <c r="D19">
         <v>300</v>
       </c>
       <c r="E19">
-        <v>63.457259999999998</v>
+        <v>63.45726</v>
       </c>
       <c r="F19">
-        <v>11.017913999999999</v>
+        <v>11.017914</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -2095,11 +1332,10 @@
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19">
         <v>150</v>
       </c>
       <c r="K19">
-        <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
       <c r="L19">
@@ -2111,31 +1347,31 @@
       <c r="N19">
         <v>1200</v>
       </c>
-      <c r="O19" s="5">
+      <c r="O19">
         <v>1.2</v>
       </c>
       <c r="P19">
         <v>0.7</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20">
       <c r="A20">
         <v>141</v>
       </c>
-      <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>10</v>
+      <c r="B20" t="str">
+        <v>Ørskog trafostasjon</v>
+      </c>
+      <c r="C20" t="str">
+        <v>NO3</v>
       </c>
       <c r="D20">
         <v>132</v>
       </c>
       <c r="E20">
-        <v>62.478070000000002</v>
+        <v>62.47807</v>
       </c>
       <c r="F20">
-        <v>7.0339970000000003</v>
+        <v>7.033997</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -2146,11 +1382,10 @@
       <c r="I20">
         <v>0</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20">
         <v>450</v>
       </c>
       <c r="K20">
-        <f t="shared" si="0"/>
         <v>112.5</v>
       </c>
       <c r="L20">
@@ -2162,31 +1397,31 @@
       <c r="N20">
         <v>1200</v>
       </c>
-      <c r="O20" s="5">
+      <c r="O20">
         <v>1.2</v>
       </c>
       <c r="P20">
         <v>0.7</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21">
       <c r="A21">
         <v>161</v>
       </c>
-      <c r="B21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" t="s">
-        <v>10</v>
+      <c r="B21" t="str">
+        <v>Svelgen trafostasjon</v>
+      </c>
+      <c r="C21" t="str">
+        <v>NO3</v>
       </c>
       <c r="D21">
         <v>132</v>
       </c>
       <c r="E21">
-        <v>61.732826000000003</v>
+        <v>61.732826</v>
       </c>
       <c r="F21">
-        <v>5.2185059999999996</v>
+        <v>5.218506</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -2197,11 +1432,10 @@
       <c r="I21">
         <v>0</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21">
         <v>550</v>
       </c>
       <c r="K21">
-        <f t="shared" si="0"/>
         <v>137.5</v>
       </c>
       <c r="L21">
@@ -2213,28 +1447,28 @@
       <c r="N21">
         <v>1200</v>
       </c>
-      <c r="O21" s="5">
+      <c r="O21">
         <v>1.2</v>
       </c>
       <c r="P21">
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22">
       <c r="A22">
         <v>176</v>
       </c>
-      <c r="B22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" t="s">
-        <v>10</v>
+      <c r="B22" t="str">
+        <v>Namsos (Statnett) trafostasjon</v>
+      </c>
+      <c r="C22" t="str">
+        <v>NO3</v>
       </c>
       <c r="D22">
         <v>300</v>
       </c>
       <c r="E22">
-        <v>64.453849000000005</v>
+        <v>64.453849</v>
       </c>
       <c r="F22">
         <v>11.620789</v>
@@ -2248,11 +1482,10 @@
       <c r="I22">
         <v>0</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="L22">
@@ -2264,22 +1497,22 @@
       <c r="N22">
         <v>1200</v>
       </c>
-      <c r="O22" s="5">
+      <c r="O22">
         <v>1.2</v>
       </c>
       <c r="P22">
         <v>0.7</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23">
       <c r="A23">
         <v>177</v>
       </c>
-      <c r="B23" t="s">
-        <v>236</v>
-      </c>
-      <c r="C23" t="s">
-        <v>10</v>
+      <c r="B23" t="str">
+        <v>Svelgen 300 kV</v>
+      </c>
+      <c r="C23" t="str">
+        <v>NO3</v>
       </c>
       <c r="D23">
         <v>300</v>
@@ -2288,7 +1521,7 @@
         <v>61.73283</v>
       </c>
       <c r="F23">
-        <v>5.2185059999999996</v>
+        <v>5.218506</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -2299,7 +1532,7 @@
       <c r="I23">
         <v>0</v>
       </c>
-      <c r="J23" s="3">
+      <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
@@ -2314,31 +1547,31 @@
       <c r="N23">
         <v>1200</v>
       </c>
-      <c r="O23" s="5">
+      <c r="O23">
         <v>1.2</v>
       </c>
       <c r="P23">
         <v>0.7</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24">
       <c r="A24">
         <v>178</v>
       </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>10</v>
+      <c r="B24" t="str">
+        <v>Brattset trafostasjon</v>
+      </c>
+      <c r="C24" t="str">
+        <v>NO3</v>
       </c>
       <c r="D24">
         <v>300</v>
       </c>
       <c r="E24">
-        <v>62.628718999999997</v>
+        <v>62.628719</v>
       </c>
       <c r="F24">
-        <v>10.266719999999999</v>
+        <v>10.26672</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -2349,7 +1582,7 @@
       <c r="I24">
         <v>0</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
@@ -2364,31 +1597,31 @@
       <c r="N24">
         <v>1200</v>
       </c>
-      <c r="O24" s="5">
+      <c r="O24">
         <v>1.2</v>
       </c>
       <c r="P24">
         <v>0.7</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25">
       <c r="A25">
         <v>179</v>
       </c>
-      <c r="B25" t="s">
-        <v>237</v>
-      </c>
-      <c r="C25" t="s">
-        <v>10</v>
+      <c r="B25" t="str">
+        <v>Brattset 380 kV</v>
+      </c>
+      <c r="C25" t="str">
+        <v>NO3</v>
       </c>
       <c r="D25">
         <v>380</v>
       </c>
       <c r="E25">
-        <v>62.628718999999997</v>
+        <v>62.628719</v>
       </c>
       <c r="F25">
-        <v>10.266719999999999</v>
+        <v>10.26672</v>
       </c>
       <c r="G25">
         <v>100</v>
@@ -2399,7 +1632,7 @@
       <c r="I25">
         <v>0</v>
       </c>
-      <c r="J25" s="3">
+      <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
@@ -2414,28 +1647,28 @@
       <c r="N25">
         <v>1200</v>
       </c>
-      <c r="O25" s="5">
+      <c r="O25">
         <v>1.2</v>
       </c>
       <c r="P25">
         <v>0.7</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26">
       <c r="A26">
         <v>180</v>
       </c>
-      <c r="B26" t="s">
-        <v>238</v>
-      </c>
-      <c r="C26" t="s">
-        <v>10</v>
+      <c r="B26" t="str">
+        <v>Namsos 380 kV</v>
+      </c>
+      <c r="C26" t="str">
+        <v>NO3</v>
       </c>
       <c r="D26">
         <v>380</v>
       </c>
       <c r="E26">
-        <v>64.453849000000005</v>
+        <v>64.453849</v>
       </c>
       <c r="F26">
         <v>11.62079</v>
@@ -2449,7 +1682,7 @@
       <c r="I26">
         <v>0</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
@@ -2464,7 +1697,7 @@
       <c r="N26">
         <v>1200</v>
       </c>
-      <c r="O26" s="5">
+      <c r="O26">
         <v>1.2</v>
       </c>
       <c r="P26">
@@ -2472,53 +1705,54 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:P26"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I105"/>
-  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" t="s">
-        <v>99</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>type2</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Pmax</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Qmax</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Qmin</v>
+      </c>
+      <c r="G1" t="str">
+        <v>bus</v>
+      </c>
+      <c r="H1" t="str">
+        <v>lat</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lon</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Grytten</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Reservoir</v>
       </c>
       <c r="D2">
         <v>143</v>
@@ -2533,21 +1767,21 @@
         <v>45</v>
       </c>
       <c r="H2">
-        <v>62.492536000000001</v>
+        <v>62.492536</v>
       </c>
       <c r="I2">
-        <v>8.8044759999999993</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" t="s">
-        <v>101</v>
+        <v>8.804476</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Tevla</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Pumped Storage</v>
       </c>
       <c r="D3">
         <v>60</v>
@@ -2562,21 +1796,21 @@
         <v>108</v>
       </c>
       <c r="H3">
-        <v>63.385137599999993</v>
+        <v>63.38513759999999</v>
       </c>
       <c r="I3">
-        <v>11.871930600000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" t="s">
-        <v>103</v>
+        <v>11.8719306</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Svelgfoss</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Run-Of-River</v>
       </c>
       <c r="D4">
         <v>251</v>
@@ -2591,21 +1825,21 @@
         <v>161</v>
       </c>
       <c r="H4">
-        <v>61.768523600000002</v>
+        <v>61.7685236</v>
       </c>
       <c r="I4">
-        <v>5.2955095999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" t="s">
-        <v>103</v>
+        <v>5.2955096</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Driva</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Run-Of-River</v>
       </c>
       <c r="D5">
         <v>160</v>
@@ -2620,21 +1854,21 @@
         <v>45</v>
       </c>
       <c r="H5">
-        <v>62.594488099999992</v>
+        <v>62.59448809999999</v>
       </c>
       <c r="I5">
-        <v>8.8866494000000031</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" t="s">
-        <v>103</v>
+        <v>8.886649400000003</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Brattset</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Run-Of-River</v>
       </c>
       <c r="D6">
         <v>92</v>
@@ -2649,21 +1883,21 @@
         <v>80</v>
       </c>
       <c r="H6">
-        <v>62.802273999999997</v>
+        <v>62.802274</v>
       </c>
       <c r="I6">
         <v>10.0126685</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" t="s">
-        <v>101</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Brattingfoss</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Pumped Storage</v>
       </c>
       <c r="D7">
         <v>14</v>
@@ -2678,21 +1912,21 @@
         <v>138</v>
       </c>
       <c r="H7">
-        <v>64.043305000000004</v>
+        <v>64.043305</v>
       </c>
       <c r="I7">
         <v>11.08352</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" t="s">
-        <v>103</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Bratsberg</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Run-Of-River</v>
       </c>
       <c r="D8">
         <v>140</v>
@@ -2707,27 +1941,27 @@
         <v>106</v>
       </c>
       <c r="H8">
-        <v>63.349364199999997</v>
+        <v>63.3493642</v>
       </c>
       <c r="I8">
-        <v>10.481959399999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
+        <v>10.4819594</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Askara</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Run-Of-River</v>
       </c>
       <c r="D9">
-        <v>157.30000000000001</v>
+        <v>157.3</v>
       </c>
       <c r="E9">
-        <v>157.30000000000001</v>
+        <v>157.3</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2736,21 +1970,21 @@
         <v>161</v>
       </c>
       <c r="H9">
-        <v>61.783333299999988</v>
+        <v>61.78333329999999</v>
       </c>
       <c r="I9">
-        <v>5.6666667000000004</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" t="s">
-        <v>99</v>
+        <v>5.6666667</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Nea</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Reservoir</v>
       </c>
       <c r="D10">
         <v>259.8</v>
@@ -2765,21 +1999,21 @@
         <v>108</v>
       </c>
       <c r="H10">
-        <v>63.161791600000001</v>
+        <v>63.1617916</v>
       </c>
       <c r="I10">
         <v>11.1900113</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Mosvik</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Run-Of-River</v>
       </c>
       <c r="D11">
         <v>46</v>
@@ -2800,15 +2034,15 @@
         <v>11.0058121</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" t="s">
-        <v>103</v>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Ovre fiskumfoss</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Run-Of-River</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -2829,15 +2063,15 @@
         <v>12.458487</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" t="s">
-        <v>99</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Harpefossen</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Reservoir</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -2852,21 +2086,21 @@
         <v>161</v>
       </c>
       <c r="H13">
-        <v>61.957961500000003</v>
+        <v>61.9579615</v>
       </c>
       <c r="I13">
-        <v>5.9323598000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" t="s">
-        <v>98</v>
+        <v>5.9323598</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Knutfoss</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D14">
         <v>5.4</v>
@@ -2881,21 +2115,21 @@
         <v>176</v>
       </c>
       <c r="H14">
-        <v>64.522800000000004</v>
+        <v>64.5228</v>
       </c>
       <c r="I14">
-        <v>12.426399999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
+        <v>12.4264</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Oyberget</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D15">
         <v>109</v>
@@ -2910,21 +2144,21 @@
         <v>30</v>
       </c>
       <c r="H15">
-        <v>61.934199999999997</v>
+        <v>61.9342</v>
       </c>
       <c r="I15">
-        <v>8.0306999999999995</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" t="s">
-        <v>117</v>
+        <v>8.0307</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Rka nyhamna</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Thermal</v>
+      </c>
+      <c r="C16" t="str">
+        <v>OCGT</v>
       </c>
       <c r="D16">
         <v>253.2</v>
@@ -2942,18 +2176,18 @@
         <v>62.8489</v>
       </c>
       <c r="I16">
-        <v>6.9432999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
+        <v>6.9433</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Midtre tessa</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -2968,21 +2202,21 @@
         <v>30</v>
       </c>
       <c r="H17">
-        <v>61.845999999999997</v>
+        <v>61.846</v>
       </c>
       <c r="I17">
-        <v>8.9611000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>119</v>
-      </c>
-      <c r="B18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
+        <v>8.9611</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Trolheim</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D18">
         <v>169.2</v>
@@ -2997,21 +2231,21 @@
         <v>106</v>
       </c>
       <c r="H18">
-        <v>63.430514899999999</v>
+        <v>63.4305149</v>
       </c>
       <c r="I18">
         <v>10.3950528</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>120</v>
-      </c>
-      <c r="B19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" t="s">
-        <v>98</v>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Grana</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D19">
         <v>90</v>
@@ -3029,18 +2263,18 @@
         <v>62.8776461</v>
       </c>
       <c r="I19">
-        <v>9.7151951999999984</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>121</v>
-      </c>
-      <c r="B20" t="s">
-        <v>98</v>
-      </c>
-      <c r="C20" t="s">
-        <v>98</v>
+        <v>9.715195199999998</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Gresslifoss</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D20">
         <v>26</v>
@@ -3055,27 +2289,27 @@
         <v>108</v>
       </c>
       <c r="H20">
-        <v>63.057699999999997</v>
+        <v>63.0577</v>
       </c>
       <c r="I20">
-        <v>11.439399999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" t="s">
-        <v>98</v>
+        <v>11.4394</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Hegsetfoss</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D21">
-        <v>40.299999999999997</v>
+        <v>40.3</v>
       </c>
       <c r="E21">
-        <v>40.299999999999997</v>
+        <v>40.3</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -3084,21 +2318,21 @@
         <v>108</v>
       </c>
       <c r="H21">
-        <v>63.165300000000002</v>
+        <v>63.1653</v>
       </c>
       <c r="I21">
-        <v>11.230700000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>123</v>
-      </c>
-      <c r="B22" t="s">
-        <v>98</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
+        <v>11.2307</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Istad</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -3113,21 +2347,21 @@
         <v>141</v>
       </c>
       <c r="H22">
-        <v>62.746369999999999</v>
+        <v>62.74637</v>
       </c>
       <c r="I22">
         <v>7.2199947</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>124</v>
-      </c>
-      <c r="B23" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Gjerdsvik</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D23">
         <v>6.2</v>
@@ -3142,21 +2376,21 @@
         <v>161</v>
       </c>
       <c r="H23">
-        <v>62.264245999999993</v>
+        <v>62.26424599999999</v>
       </c>
       <c r="I23">
-        <v>5.5803419999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>125</v>
-      </c>
-      <c r="B24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
+        <v>5.580342</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Eidefossen</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D24">
         <v>14</v>
@@ -3174,18 +2408,18 @@
         <v>61.80454379999999</v>
       </c>
       <c r="I24">
-        <v>9.3017813999999994</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>126</v>
-      </c>
-      <c r="B25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" t="s">
-        <v>98</v>
+        <v>9.3017814</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Fausa</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -3200,21 +2434,21 @@
         <v>141</v>
       </c>
       <c r="H25">
-        <v>62.357500000000002</v>
+        <v>62.3575</v>
       </c>
       <c r="I25">
         <v>6.8948</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>127</v>
-      </c>
-      <c r="B26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" t="s">
-        <v>98</v>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Follafoss</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D26">
         <v>48.5</v>
@@ -3229,21 +2463,21 @@
         <v>138</v>
       </c>
       <c r="H26">
-        <v>63.985557500000013</v>
+        <v>63.98555750000001</v>
       </c>
       <c r="I26">
         <v>11.1072278</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
-      <c r="A27" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" t="s">
-        <v>98</v>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Framruste</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D27">
         <v>85</v>
@@ -3258,21 +2492,21 @@
         <v>79</v>
       </c>
       <c r="H27">
-        <v>61.960009399999997</v>
+        <v>61.9600094</v>
       </c>
       <c r="I27">
-        <v>7.8511770000000034</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>129</v>
-      </c>
-      <c r="B28" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" t="s">
-        <v>98</v>
+        <v>7.851177000000003</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Furset</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D28">
         <v>5.4</v>
@@ -3287,21 +2521,21 @@
         <v>141</v>
       </c>
       <c r="H28">
-        <v>62.282800000000002</v>
+        <v>62.2828</v>
       </c>
       <c r="I28">
-        <v>6.8848000000000003</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" t="s">
-        <v>130</v>
-      </c>
-      <c r="B29" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" t="s">
-        <v>99</v>
+        <v>6.8848</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Norddalen</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Reservoir</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -3316,21 +2550,21 @@
         <v>141</v>
       </c>
       <c r="H29">
-        <v>62.299768399999998</v>
+        <v>62.2997684</v>
       </c>
       <c r="I29">
-        <v>7.2545709999999994</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>131</v>
-      </c>
-      <c r="B30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
+        <v>7.254570999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Vessingfoss</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D30">
         <v>45</v>
@@ -3345,21 +2579,21 @@
         <v>108</v>
       </c>
       <c r="H30">
-        <v>62.995699999999999</v>
+        <v>62.9957</v>
       </c>
       <c r="I30">
         <v>11.8285</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
-      <c r="A31" t="s">
-        <v>132</v>
-      </c>
-      <c r="B31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" t="s">
-        <v>98</v>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Svorkmo</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D31">
         <v>86</v>
@@ -3374,21 +2608,21 @@
         <v>107</v>
       </c>
       <c r="H31">
-        <v>63.163664850000004</v>
+        <v>63.16366485</v>
       </c>
       <c r="I31">
-        <v>9.7574403499999995</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" t="s">
-        <v>133</v>
-      </c>
-      <c r="B32" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" t="s">
-        <v>98</v>
+        <v>9.75744035</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Tussa</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D32">
         <v>64</v>
@@ -3403,21 +2637,21 @@
         <v>141</v>
       </c>
       <c r="H32">
-        <v>62.178645300000007</v>
+        <v>62.17864530000001</v>
       </c>
       <c r="I32">
-        <v>6.0833482000000014</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" t="s">
-        <v>134</v>
-      </c>
-      <c r="B33" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" t="s">
-        <v>103</v>
+        <v>6.083348200000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Tafjord</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Run-Of-River</v>
       </c>
       <c r="D33">
         <v>319.2</v>
@@ -3432,21 +2666,21 @@
         <v>141</v>
       </c>
       <c r="H33">
-        <v>62.231151299999979</v>
+        <v>62.23115129999998</v>
       </c>
       <c r="I33">
-        <v>7.4153287000000017</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" t="s">
-        <v>135</v>
-      </c>
-      <c r="B34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" t="s">
-        <v>103</v>
+        <v>7.415328700000002</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Fjaremsfossen</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Run-Of-River</v>
       </c>
       <c r="D34">
         <v>23</v>
@@ -3461,21 +2695,21 @@
         <v>76</v>
       </c>
       <c r="H34">
-        <v>63.322110000000002</v>
+        <v>63.32211</v>
       </c>
       <c r="I34">
-        <v>10.436579999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" t="s">
-        <v>136</v>
-      </c>
-      <c r="B35" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" t="s">
-        <v>98</v>
+        <v>10.43658</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Bogna</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D35">
         <v>60</v>
@@ -3490,21 +2724,21 @@
         <v>176</v>
       </c>
       <c r="H35">
-        <v>64.221500000000006</v>
+        <v>64.2215</v>
       </c>
       <c r="I35">
-        <v>12.036899999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" t="s">
-        <v>137</v>
-      </c>
-      <c r="B36" t="s">
-        <v>98</v>
-      </c>
-      <c r="C36" t="s">
-        <v>98</v>
+        <v>12.0369</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Aunfoss</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D36">
         <v>36</v>
@@ -3522,18 +2756,18 @@
         <v>64.31045300000001</v>
       </c>
       <c r="I36">
-        <v>11.520841900000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" t="s">
-        <v>138</v>
-      </c>
-      <c r="B37" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" t="s">
-        <v>98</v>
+        <v>11.5208419</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Fossan</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -3548,21 +2782,21 @@
         <v>108</v>
       </c>
       <c r="H37">
-        <v>63.027299999999997</v>
+        <v>63.0273</v>
       </c>
       <c r="I37">
         <v>11.6968</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
-      <c r="A38" t="s">
-        <v>139</v>
-      </c>
-      <c r="B38" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" t="s">
-        <v>98</v>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Nedrenea</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D38">
         <v>70</v>
@@ -3577,21 +2811,21 @@
         <v>108</v>
       </c>
       <c r="H38">
-        <v>63.151699999999998</v>
+        <v>63.1517</v>
       </c>
       <c r="I38">
-        <v>11.239599999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" t="s">
-        <v>140</v>
-      </c>
-      <c r="B39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" t="s">
-        <v>98</v>
+        <v>11.2396</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Litledalen</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D39">
         <v>19.5</v>
@@ -3609,18 +2843,18 @@
         <v>62.6666667</v>
       </c>
       <c r="I39">
-        <v>7.5333332999999989</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" t="s">
-        <v>141</v>
-      </c>
-      <c r="B40" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" t="s">
-        <v>98</v>
+        <v>7.533333299999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Kvitfossen</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D40">
         <v>7.8</v>
@@ -3635,21 +2869,21 @@
         <v>30</v>
       </c>
       <c r="H40">
-        <v>62.210242699999988</v>
+        <v>62.21024269999999</v>
       </c>
       <c r="I40">
-        <v>8.9330416999999969</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" t="s">
-        <v>142</v>
-      </c>
-      <c r="B41" t="s">
-        <v>98</v>
-      </c>
-      <c r="C41" t="s">
-        <v>98</v>
+        <v>8.933041699999997</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Kanstadbotn</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D41">
         <v>5.8</v>
@@ -3664,21 +2898,21 @@
         <v>45</v>
       </c>
       <c r="H41">
-        <v>62.676000000000002</v>
+        <v>62.676</v>
       </c>
       <c r="I41">
         <v>8.157</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
-      <c r="A42" t="s">
-        <v>143</v>
-      </c>
-      <c r="B42" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" t="s">
-        <v>98</v>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Julskaret</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D42">
         <v>8</v>
@@ -3693,21 +2927,21 @@
         <v>76</v>
       </c>
       <c r="H42">
-        <v>63.140300000000003</v>
+        <v>63.1403</v>
       </c>
       <c r="I42">
         <v>10.9664</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
-      <c r="A43" t="s">
-        <v>144</v>
-      </c>
-      <c r="B43" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" t="s">
-        <v>98</v>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Innvik</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D43">
         <v>17</v>
@@ -3722,21 +2956,21 @@
         <v>109</v>
       </c>
       <c r="H43">
-        <v>61.851740700000001</v>
+        <v>61.8517407</v>
       </c>
       <c r="I43">
-        <v>6.6169454999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" t="s">
-        <v>145</v>
-      </c>
-      <c r="B44" t="s">
-        <v>98</v>
-      </c>
-      <c r="C44" t="s">
-        <v>98</v>
+        <v>6.6169455</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Byrkjelo</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D44">
         <v>25.2</v>
@@ -3751,27 +2985,27 @@
         <v>161</v>
       </c>
       <c r="H44">
-        <v>61.733299000000002</v>
+        <v>61.733299</v>
       </c>
       <c r="I44">
-        <v>6.5069116999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" t="s">
-        <v>146</v>
-      </c>
-      <c r="B45" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" t="s">
-        <v>98</v>
+        <v>6.5069117</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Byafossen</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D45">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="E45">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -3780,21 +3014,21 @@
         <v>138</v>
       </c>
       <c r="H45">
-        <v>64.031990399999998</v>
+        <v>64.0319904</v>
       </c>
       <c r="I45">
         <v>11.5484121</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
-      <c r="A46" t="s">
-        <v>147</v>
-      </c>
-      <c r="B46" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" t="s">
-        <v>98</v>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Brunstad</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -3809,21 +3043,21 @@
         <v>141</v>
       </c>
       <c r="H46">
-        <v>62.381633899999997</v>
+        <v>62.3816339</v>
       </c>
       <c r="I46">
-        <v>6.5741103000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" t="s">
-        <v>148</v>
-      </c>
-      <c r="B47" t="s">
-        <v>98</v>
-      </c>
-      <c r="C47" t="s">
-        <v>98</v>
+        <v>6.5741103</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Brekkefoss</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -3838,21 +3072,21 @@
         <v>161</v>
       </c>
       <c r="H47">
-        <v>61.723153799999992</v>
+        <v>61.72315379999999</v>
       </c>
       <c r="I47">
-        <v>5.8376893999999986</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" t="s">
-        <v>149</v>
-      </c>
-      <c r="B48" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" t="s">
-        <v>98</v>
+        <v>5.837689399999999</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Asen</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D48">
         <v>10.4</v>
@@ -3867,21 +3101,21 @@
         <v>139</v>
       </c>
       <c r="H48">
-        <v>63.608235299999997</v>
+        <v>63.6082353</v>
       </c>
       <c r="I48">
-        <v>11.051768900000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" t="s">
-        <v>150</v>
-      </c>
-      <c r="B49" t="s">
-        <v>98</v>
-      </c>
-      <c r="C49" t="s">
-        <v>98</v>
+        <v>11.0517689</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Eiriksdal</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D49">
         <v>100</v>
@@ -3896,21 +3130,21 @@
         <v>79</v>
       </c>
       <c r="H49">
-        <v>62.476147400000002</v>
+        <v>62.4761474</v>
       </c>
       <c r="I49">
-        <v>8.1743355999999991</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" t="s">
-        <v>151</v>
-      </c>
-      <c r="B50" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" t="s">
-        <v>98</v>
+        <v>8.1743356</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Funna</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D50">
         <v>21.7</v>
@@ -3925,21 +3159,21 @@
         <v>139</v>
       </c>
       <c r="H50">
-        <v>63.451559799999998</v>
+        <v>63.4515598</v>
       </c>
       <c r="I50">
-        <v>11.763260900000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" t="s">
-        <v>152</v>
-      </c>
-      <c r="B51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51" t="s">
-        <v>98</v>
+        <v>11.7632609</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Hopselva</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D51">
         <v>5.2</v>
@@ -3954,21 +3188,21 @@
         <v>161</v>
       </c>
       <c r="H51">
-        <v>61.714849000000001</v>
+        <v>61.714849</v>
       </c>
       <c r="I51">
-        <v>5.8235750999999993</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" t="s">
-        <v>153</v>
-      </c>
-      <c r="B52" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" t="s">
-        <v>98</v>
+        <v>5.823575099999999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Giskemo</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D52">
         <v>5.4</v>
@@ -3983,21 +3217,21 @@
         <v>141</v>
       </c>
       <c r="H52">
-        <v>62.481357499999987</v>
+        <v>62.48135749999999</v>
       </c>
       <c r="I52">
         <v>6.8139132</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
-      <c r="A53" t="s">
-        <v>154</v>
-      </c>
-      <c r="B53" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" t="s">
-        <v>98</v>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Fossheim</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D53">
         <v>9</v>
@@ -4012,21 +3246,21 @@
         <v>30</v>
       </c>
       <c r="H53">
-        <v>61.838385399999993</v>
+        <v>61.83838539999999</v>
       </c>
       <c r="I53">
-        <v>8.5725324999999994</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" t="s">
-        <v>155</v>
-      </c>
-      <c r="B54" t="s">
-        <v>98</v>
-      </c>
-      <c r="C54" t="s">
-        <v>98</v>
+        <v>8.5725325</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Embla</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D54">
         <v>5.5</v>
@@ -4041,21 +3275,21 @@
         <v>141</v>
       </c>
       <c r="H54">
-        <v>62.217100000000002</v>
+        <v>62.2171</v>
       </c>
       <c r="I54">
-        <v>6.9097999999999997</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" t="s">
-        <v>156</v>
-      </c>
-      <c r="B55" t="s">
-        <v>98</v>
-      </c>
-      <c r="C55" t="s">
-        <v>98</v>
+        <v>6.9098</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Eid</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D55">
         <v>10.6</v>
@@ -4070,21 +3304,21 @@
         <v>161</v>
       </c>
       <c r="H55">
-        <v>61.920644099999997</v>
+        <v>61.9206441</v>
       </c>
       <c r="I55">
-        <v>6.0118764999999996</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" t="s">
-        <v>157</v>
-      </c>
-      <c r="B56" t="s">
-        <v>98</v>
-      </c>
-      <c r="C56" t="s">
-        <v>98</v>
+        <v>6.0118765</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Lokaunet</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D56">
         <v>11.5</v>
@@ -4099,21 +3333,21 @@
         <v>76</v>
       </c>
       <c r="H56">
-        <v>63.268192799999987</v>
+        <v>63.26819279999999</v>
       </c>
       <c r="I56">
         <v>10.4582701</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
-      <c r="A57" t="s">
-        <v>158</v>
-      </c>
-      <c r="B57" t="s">
-        <v>98</v>
-      </c>
-      <c r="C57" t="s">
-        <v>98</v>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Amela</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D57">
         <v>40</v>
@@ -4128,21 +3362,21 @@
         <v>161</v>
       </c>
       <c r="H57">
-        <v>62.009125699999998</v>
+        <v>62.0091257</v>
       </c>
       <c r="I57">
-        <v>5.8372717999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" t="s">
-        <v>159</v>
-      </c>
-      <c r="B58" t="s">
-        <v>98</v>
-      </c>
-      <c r="C58" t="s">
-        <v>98</v>
+        <v>5.8372718</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Skjak</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D58">
         <v>35</v>
@@ -4157,21 +3391,21 @@
         <v>79</v>
       </c>
       <c r="H58">
-        <v>61.946797599999996</v>
+        <v>61.9467976</v>
       </c>
       <c r="I58">
         <v>7.828136999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
-      <c r="A59" t="s">
-        <v>160</v>
-      </c>
-      <c r="B59" t="s">
-        <v>98</v>
-      </c>
-      <c r="C59" t="s">
-        <v>98</v>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Skogheim</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D59">
         <v>9</v>
@@ -4186,21 +3420,21 @@
         <v>161</v>
       </c>
       <c r="H59">
-        <v>61.816666699999999</v>
+        <v>61.8166667</v>
       </c>
       <c r="I59">
         <v>6.15</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
-      <c r="A60" t="s">
-        <v>161</v>
-      </c>
-      <c r="B60" t="s">
-        <v>98</v>
-      </c>
-      <c r="C60" t="s">
-        <v>98</v>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Usma selbu</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D60">
         <v>16.3</v>
@@ -4215,21 +3449,21 @@
         <v>139</v>
       </c>
       <c r="H60">
-        <v>63.219245399999991</v>
+        <v>63.21924539999999</v>
       </c>
       <c r="I60">
         <v>11.04129</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
-      <c r="A61" t="s">
-        <v>162</v>
-      </c>
-      <c r="B61" t="s">
-        <v>98</v>
-      </c>
-      <c r="C61" t="s">
-        <v>98</v>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Soa</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D61">
         <v>45</v>
@@ -4244,21 +3478,21 @@
         <v>107</v>
       </c>
       <c r="H61">
-        <v>63.290570000000002</v>
+        <v>63.29057</v>
       </c>
       <c r="I61">
-        <v>9.0890899999999988</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62" t="s">
-        <v>163</v>
-      </c>
-      <c r="B62" t="s">
-        <v>98</v>
-      </c>
-      <c r="C62" t="s">
-        <v>98</v>
+        <v>9.089089999999999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Sorbrandal</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D62">
         <v>8</v>
@@ -4273,27 +3507,27 @@
         <v>161</v>
       </c>
       <c r="H62">
-        <v>62.167462600000007</v>
+        <v>62.16746260000001</v>
       </c>
       <c r="I62">
-        <v>5.5608660999999966</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" t="s">
-        <v>164</v>
-      </c>
-      <c r="B63" t="s">
-        <v>98</v>
-      </c>
-      <c r="C63" t="s">
-        <v>98</v>
+        <v>5.560866099999997</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Stadheim</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D63">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="E63">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -4302,21 +3536,21 @@
         <v>141</v>
       </c>
       <c r="H63">
-        <v>62.309640000000002</v>
+        <v>62.30964</v>
       </c>
       <c r="I63">
-        <v>6.9358199999999997</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64" t="s">
-        <v>165</v>
-      </c>
-      <c r="B64" t="s">
-        <v>98</v>
-      </c>
-      <c r="C64" t="s">
-        <v>98</v>
+        <v>6.93582</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Steinsvik</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D64">
         <v>10</v>
@@ -4331,21 +3565,21 @@
         <v>161</v>
       </c>
       <c r="H64">
-        <v>62.004661499999997</v>
+        <v>62.0046615</v>
       </c>
       <c r="I64">
-        <v>5.8543174000000002</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65" t="s">
-        <v>166</v>
-      </c>
-      <c r="B65" t="s">
-        <v>98</v>
-      </c>
-      <c r="C65" t="s">
-        <v>98</v>
+        <v>5.8543174</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Stordal</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D65">
         <v>36.6</v>
@@ -4360,21 +3594,21 @@
         <v>141</v>
       </c>
       <c r="H65">
-        <v>62.381817899999987</v>
+        <v>62.38181789999999</v>
       </c>
       <c r="I65">
-        <v>6.9920547000000024</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
-      <c r="A66" t="s">
-        <v>167</v>
-      </c>
-      <c r="B66" t="s">
-        <v>98</v>
-      </c>
-      <c r="C66" t="s">
-        <v>98</v>
+        <v>6.992054700000002</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Skulafossen</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D66">
         <v>5</v>
@@ -4389,21 +3623,21 @@
         <v>77</v>
       </c>
       <c r="H66">
-        <v>63.266666700000002</v>
+        <v>63.2666667</v>
       </c>
       <c r="I66">
-        <v>9.8333333000000014</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
-      <c r="A67" t="s">
-        <v>168</v>
-      </c>
-      <c r="B67" t="s">
-        <v>98</v>
-      </c>
-      <c r="C67" t="s">
-        <v>98</v>
+        <v>9.833333300000001</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Trysilfossen</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D67">
         <v>3.7</v>
@@ -4421,18 +3655,18 @@
         <v>61.74977719999999</v>
       </c>
       <c r="I67">
-        <v>6.2766851000000008</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
-      <c r="A68" t="s">
-        <v>169</v>
-      </c>
-      <c r="B68" t="s">
-        <v>98</v>
-      </c>
-      <c r="C68" t="s">
-        <v>98</v>
+        <v>6.276685100000001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Urke</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D68">
         <v>5.7</v>
@@ -4447,21 +3681,21 @@
         <v>141</v>
       </c>
       <c r="H68">
-        <v>62.212875399999987</v>
+        <v>62.21287539999999</v>
       </c>
       <c r="I68">
-        <v>6.5668392999999998</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
-      <c r="A69" t="s">
-        <v>170</v>
-      </c>
-      <c r="B69" t="s">
-        <v>98</v>
-      </c>
-      <c r="C69" t="s">
-        <v>98</v>
+        <v>6.5668393</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Trandal</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D69">
         <v>5.6</v>
@@ -4476,21 +3710,21 @@
         <v>141</v>
       </c>
       <c r="H69">
-        <v>62.260845699999997</v>
+        <v>62.2608457</v>
       </c>
       <c r="I69">
-        <v>6.5005457999999994</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
-      <c r="A70" t="s">
-        <v>171</v>
-      </c>
-      <c r="B70" t="s">
-        <v>98</v>
-      </c>
-      <c r="C70" t="s">
-        <v>98</v>
+        <v>6.500545799999999</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Sykkylven</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -4505,21 +3739,21 @@
         <v>141</v>
       </c>
       <c r="H70">
-        <v>62.391900300000003</v>
+        <v>62.3919003</v>
       </c>
       <c r="I70">
-        <v>6.5980089000000008</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
-      <c r="A71" t="s">
-        <v>172</v>
-      </c>
-      <c r="B71" t="s">
-        <v>98</v>
-      </c>
-      <c r="C71" t="s">
-        <v>98</v>
+        <v>6.598008900000001</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Vassli</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D71">
         <v>12</v>
@@ -4534,21 +3768,21 @@
         <v>77</v>
       </c>
       <c r="H71">
-        <v>63.216666700000012</v>
+        <v>63.21666670000001</v>
       </c>
       <c r="I71">
-        <v>9.6333333000000021</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
-      <c r="A72" t="s">
-        <v>173</v>
-      </c>
-      <c r="B72" t="s">
-        <v>116</v>
-      </c>
-      <c r="C72" t="s">
-        <v>117</v>
+        <v>9.633333300000002</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Tjeldbergodden</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Thermal</v>
+      </c>
+      <c r="C72" t="str">
+        <v>OCGT</v>
       </c>
       <c r="D72">
         <v>37.5</v>
@@ -4563,21 +3797,21 @@
         <v>107</v>
       </c>
       <c r="H72">
-        <v>63.408431600000007</v>
+        <v>63.40843160000001</v>
       </c>
       <c r="I72">
-        <v>8.6937046000000002</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9">
-      <c r="A73" t="s">
-        <v>174</v>
-      </c>
-      <c r="B73" t="s">
-        <v>98</v>
-      </c>
-      <c r="C73" t="s">
-        <v>98</v>
+        <v>8.6937046</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Morre</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D73">
         <v>16</v>
@@ -4592,21 +3826,21 @@
         <v>138</v>
       </c>
       <c r="H73">
-        <v>63.966667000000001</v>
+        <v>63.966667</v>
       </c>
       <c r="I73">
-        <v>10.199999999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
-      <c r="A74" t="s">
-        <v>175</v>
-      </c>
-      <c r="B74" t="s">
-        <v>98</v>
-      </c>
-      <c r="C74" t="s">
-        <v>98</v>
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Meraker</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D74">
         <v>108</v>
@@ -4621,21 +3855,21 @@
         <v>139</v>
       </c>
       <c r="H74">
-        <v>63.416168900000002</v>
+        <v>63.4161689</v>
       </c>
       <c r="I74">
         <v>11.7372151</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
-      <c r="A75" t="s">
-        <v>176</v>
-      </c>
-      <c r="B75" t="s">
-        <v>98</v>
-      </c>
-      <c r="C75" t="s">
-        <v>98</v>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Osbu</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D75">
         <v>28</v>
@@ -4650,21 +3884,21 @@
         <v>45</v>
       </c>
       <c r="H75">
-        <v>62.516666700000002</v>
+        <v>62.5166667</v>
       </c>
       <c r="I75">
         <v>8.5</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
-      <c r="A76" t="s">
-        <v>177</v>
-      </c>
-      <c r="B76" t="s">
-        <v>98</v>
-      </c>
-      <c r="C76" t="s">
-        <v>98</v>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Osen</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D76">
         <v>5</v>
@@ -4679,21 +3913,21 @@
         <v>176</v>
       </c>
       <c r="H76">
-        <v>64.421139799999992</v>
+        <v>64.42113979999999</v>
       </c>
       <c r="I76">
         <v>10.0377767</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
-      <c r="A77" t="s">
-        <v>178</v>
-      </c>
-      <c r="B77" t="s">
-        <v>98</v>
-      </c>
-      <c r="C77" t="s">
-        <v>98</v>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Riksheimdal</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D77">
         <v>9.5</v>
@@ -4708,21 +3942,21 @@
         <v>141</v>
       </c>
       <c r="H77">
-        <v>62.357509999999998</v>
+        <v>62.35751</v>
       </c>
       <c r="I77">
-        <v>6.5719160000000008</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9">
-      <c r="A78" t="s">
-        <v>179</v>
-      </c>
-      <c r="B78" t="s">
-        <v>98</v>
-      </c>
-      <c r="C78" t="s">
-        <v>103</v>
+        <v>6.571916000000001</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Oksenelvane</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Run-Of-River</v>
       </c>
       <c r="D78">
         <v>30</v>
@@ -4737,21 +3971,21 @@
         <v>161</v>
       </c>
       <c r="H78">
-        <v>61.841830000000002</v>
+        <v>61.84183</v>
       </c>
       <c r="I78">
-        <v>5.8013399999999997</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9">
-      <c r="A79" t="s">
-        <v>180</v>
-      </c>
-      <c r="B79" t="s">
-        <v>98</v>
-      </c>
-      <c r="C79" t="s">
-        <v>99</v>
+        <v>5.80134</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Trollheim</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Reservoir</v>
       </c>
       <c r="D79">
         <v>130</v>
@@ -4769,18 +4003,18 @@
         <v>63.002761</v>
       </c>
       <c r="I79">
-        <v>9.0191520000000001</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
-      <c r="A80" t="s">
-        <v>181</v>
-      </c>
-      <c r="B80" t="s">
-        <v>98</v>
-      </c>
-      <c r="C80" t="s">
-        <v>98</v>
+        <v>9.019152</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Agdenes</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D80">
         <v>1.5</v>
@@ -4795,21 +4029,21 @@
         <v>77</v>
       </c>
       <c r="H80">
-        <v>63.513787200000003</v>
+        <v>63.5137872</v>
       </c>
       <c r="I80">
-        <v>9.6812501999999991</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9">
-      <c r="A81" t="s">
-        <v>182</v>
-      </c>
-      <c r="B81" t="s">
-        <v>98</v>
-      </c>
-      <c r="C81" t="s">
-        <v>98</v>
+        <v>9.6812502</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Aselva</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D81">
         <v>3.5</v>
@@ -4824,27 +4058,27 @@
         <v>77</v>
       </c>
       <c r="H81">
-        <v>63.615011700000011</v>
+        <v>63.61501170000001</v>
       </c>
       <c r="I81">
-        <v>9.7131293000000003</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
-      <c r="A82" t="s">
-        <v>183</v>
-      </c>
-      <c r="B82" t="s">
-        <v>98</v>
-      </c>
-      <c r="C82" t="s">
-        <v>98</v>
+        <v>9.7131293</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Brandaa</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D82">
-        <v>4.4000000000000004</v>
+        <v>4.4</v>
       </c>
       <c r="E82">
-        <v>4.4000000000000004</v>
+        <v>4.4</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4853,21 +4087,21 @@
         <v>107</v>
       </c>
       <c r="H82">
-        <v>63.095562100000002</v>
+        <v>63.0955621</v>
       </c>
       <c r="I82">
-        <v>9.1879674999999992</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9">
-      <c r="A83" t="s">
-        <v>184</v>
-      </c>
-      <c r="B83" t="s">
-        <v>98</v>
-      </c>
-      <c r="C83" t="s">
-        <v>98</v>
+        <v>9.1879675</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Bryggja</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D83">
         <v>0.3</v>
@@ -4882,27 +4116,27 @@
         <v>161</v>
       </c>
       <c r="H83">
-        <v>61.940724699999997</v>
+        <v>61.9407247</v>
       </c>
       <c r="I83">
-        <v>5.4489538999999994</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
-      <c r="A84" t="s">
-        <v>185</v>
-      </c>
-      <c r="B84" t="s">
-        <v>98</v>
-      </c>
-      <c r="C84" t="s">
-        <v>98</v>
+        <v>5.448953899999999</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Eidsfossen sfe</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D84">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="E84">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4914,18 +4148,18 @@
         <v>61.7557051</v>
       </c>
       <c r="I84">
-        <v>6.2465699999999984</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
-      <c r="A85" t="s">
-        <v>186</v>
-      </c>
-      <c r="B85" t="s">
-        <v>98</v>
-      </c>
-      <c r="C85" t="s">
-        <v>98</v>
+        <v>6.246569999999998</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Eidum</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D85">
         <v>4.8</v>
@@ -4940,21 +4174,21 @@
         <v>139</v>
       </c>
       <c r="H85">
-        <v>63.443506999999997</v>
+        <v>63.443507</v>
       </c>
       <c r="I85">
-        <v>10.981521600000001</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
-      <c r="A86" t="s">
-        <v>187</v>
-      </c>
-      <c r="B86" t="s">
-        <v>98</v>
-      </c>
-      <c r="C86" t="s">
-        <v>98</v>
+        <v>10.9815216</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Fossan halogalan</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D86">
         <v>8.1</v>
@@ -4969,21 +4203,21 @@
         <v>139</v>
       </c>
       <c r="H86">
-        <v>63.269995499999993</v>
+        <v>63.26999549999999</v>
       </c>
       <c r="I86">
-        <v>11.006936400000001</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9">
-      <c r="A87" t="s">
-        <v>188</v>
-      </c>
-      <c r="B87" t="s">
-        <v>98</v>
-      </c>
-      <c r="C87" t="s">
-        <v>98</v>
+        <v>11.0069364</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Fr.stad bioel</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D87">
         <v>5.5</v>
@@ -5001,18 +4235,18 @@
         <v>62.2034454</v>
       </c>
       <c r="I87">
-        <v>5.1708737999999999</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
-      <c r="A88" t="s">
-        <v>189</v>
-      </c>
-      <c r="B88" t="s">
-        <v>98</v>
-      </c>
-      <c r="C88" t="s">
-        <v>98</v>
+        <v>5.1708738</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Groa</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D88">
         <v>40</v>
@@ -5027,21 +4261,21 @@
         <v>45</v>
       </c>
       <c r="H88">
-        <v>62.643983700000007</v>
+        <v>62.64398370000001</v>
       </c>
       <c r="I88">
-        <v>8.7299540000000011</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9">
-      <c r="A89" t="s">
-        <v>190</v>
-      </c>
-      <c r="B89" t="s">
-        <v>98</v>
-      </c>
-      <c r="C89" t="s">
-        <v>98</v>
+        <v>8.729954000000001</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Holla</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D89">
         <v>0.4</v>
@@ -5059,18 +4293,18 @@
         <v>63.313609</v>
       </c>
       <c r="I89">
-        <v>9.1423079999999999</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9">
-      <c r="A90" t="s">
-        <v>191</v>
-      </c>
-      <c r="B90" t="s">
-        <v>98</v>
-      </c>
-      <c r="C90" t="s">
-        <v>98</v>
+        <v>9.142308</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Hopen</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -5085,21 +4319,21 @@
         <v>45</v>
       </c>
       <c r="H90">
-        <v>63.463441699999997</v>
+        <v>63.4634417</v>
       </c>
       <c r="I90">
         <v>8.0138783</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
-      <c r="A91" t="s">
-        <v>192</v>
-      </c>
-      <c r="B91" t="s">
-        <v>98</v>
-      </c>
-      <c r="C91" t="s">
-        <v>98</v>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Innset</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D91">
         <v>105</v>
@@ -5114,21 +4348,21 @@
         <v>62</v>
       </c>
       <c r="H91">
-        <v>62.719549000000001</v>
+        <v>62.719549</v>
       </c>
       <c r="I91">
         <v>10.0280798</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
-      <c r="A92" t="s">
-        <v>193</v>
-      </c>
-      <c r="B92" t="s">
-        <v>98</v>
-      </c>
-      <c r="C92" t="s">
-        <v>98</v>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Jardola</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D92">
         <v>4.8</v>
@@ -5146,18 +4380,18 @@
         <v>61.7171059</v>
       </c>
       <c r="I92">
-        <v>6.2347906999999996</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9">
-      <c r="A93" t="s">
-        <v>194</v>
-      </c>
-      <c r="B93" t="s">
-        <v>98</v>
-      </c>
-      <c r="C93" t="s">
-        <v>98</v>
+        <v>6.2347907</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Kassdalen</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D93">
         <v>2.4</v>
@@ -5172,21 +4406,21 @@
         <v>108</v>
       </c>
       <c r="H93">
-        <v>62.793325099999997</v>
+        <v>62.7933251</v>
       </c>
       <c r="I93">
-        <v>11.188310299999999</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9">
-      <c r="A94" t="s">
-        <v>195</v>
-      </c>
-      <c r="B94" t="s">
-        <v>98</v>
-      </c>
-      <c r="C94" t="s">
-        <v>98</v>
+        <v>11.1883103</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Kurasfossen</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D94">
         <v>12.7</v>
@@ -5201,21 +4435,21 @@
         <v>108</v>
       </c>
       <c r="H94">
-        <v>62.678901799999991</v>
+        <v>62.67890179999999</v>
       </c>
       <c r="I94">
         <v>11.4618021</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
-      <c r="A95" t="s">
-        <v>196</v>
-      </c>
-      <c r="B95" t="s">
-        <v>98</v>
-      </c>
-      <c r="C95" t="s">
-        <v>98</v>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Namsos</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D95">
         <v>12.7</v>
@@ -5230,21 +4464,21 @@
         <v>176</v>
       </c>
       <c r="H95">
-        <v>64.504051100000012</v>
+        <v>64.50405110000001</v>
       </c>
       <c r="I95">
         <v>11.510163</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
-      <c r="A96" t="s">
-        <v>197</v>
-      </c>
-      <c r="B96" t="s">
-        <v>98</v>
-      </c>
-      <c r="C96" t="s">
-        <v>98</v>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Nordsvorka</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D96">
         <v>3</v>
@@ -5259,21 +4493,21 @@
         <v>107</v>
       </c>
       <c r="H96">
-        <v>63.045076500000008</v>
+        <v>63.04507650000001</v>
       </c>
       <c r="I96">
-        <v>8.8672097000000001</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9">
-      <c r="A97" t="s">
-        <v>198</v>
-      </c>
-      <c r="B97" t="s">
-        <v>98</v>
-      </c>
-      <c r="C97" t="s">
-        <v>98</v>
+        <v>8.8672097</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Ogndal</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D97">
         <v>13.7</v>
@@ -5288,21 +4522,21 @@
         <v>138</v>
       </c>
       <c r="H97">
-        <v>64.015019299999992</v>
+        <v>64.01501929999999</v>
       </c>
       <c r="I97">
         <v>11.4952627</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
-      <c r="A98" t="s">
-        <v>199</v>
-      </c>
-      <c r="B98" t="s">
-        <v>98</v>
-      </c>
-      <c r="C98" t="s">
-        <v>98</v>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Orkdal</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D98">
         <v>41</v>
@@ -5317,21 +4551,21 @@
         <v>77</v>
       </c>
       <c r="H98">
-        <v>63.302412999999987</v>
+        <v>63.30241299999999</v>
       </c>
       <c r="I98">
-        <v>9.8477710999999992</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
-      <c r="A99" t="s">
-        <v>200</v>
-      </c>
-      <c r="B99" t="s">
-        <v>98</v>
-      </c>
-      <c r="C99" t="s">
-        <v>98</v>
+        <v>9.8477711</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Selbu</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D99">
         <v>1.3</v>
@@ -5346,21 +4580,21 @@
         <v>139</v>
       </c>
       <c r="H99">
-        <v>63.219245399999991</v>
+        <v>63.21924539999999</v>
       </c>
       <c r="I99">
         <v>11.04129</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
-      <c r="A100" t="s">
-        <v>201</v>
-      </c>
-      <c r="B100" t="s">
-        <v>116</v>
-      </c>
-      <c r="C100" t="s">
-        <v>117</v>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Thamshavn</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Thermal</v>
+      </c>
+      <c r="C100" t="str">
+        <v>OCGT</v>
       </c>
       <c r="D100">
         <v>31</v>
@@ -5375,21 +4609,21 @@
         <v>77</v>
       </c>
       <c r="H100">
-        <v>63.320584900000007</v>
+        <v>63.32058490000001</v>
       </c>
       <c r="I100">
         <v>9.8825433</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
-      <c r="A101" t="s">
-        <v>202</v>
-      </c>
-      <c r="B101" t="s">
-        <v>98</v>
-      </c>
-      <c r="C101" t="s">
-        <v>98</v>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Vagamo</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D101">
         <v>6.5</v>
@@ -5404,21 +4638,21 @@
         <v>30</v>
       </c>
       <c r="H101">
-        <v>61.875170100000012</v>
+        <v>61.87517010000001</v>
       </c>
       <c r="I101">
-        <v>9.0966266000000005</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9">
-      <c r="A102" t="s">
-        <v>203</v>
-      </c>
-      <c r="B102" t="s">
-        <v>98</v>
-      </c>
-      <c r="C102" t="s">
-        <v>98</v>
+        <v>9.0966266</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Verdal</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D102">
         <v>23.9</v>
@@ -5433,21 +4667,21 @@
         <v>105</v>
       </c>
       <c r="H102">
-        <v>63.750598100000012</v>
+        <v>63.75059810000001</v>
       </c>
       <c r="I102">
         <v>11.916895</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
-      <c r="A103" t="s">
-        <v>204</v>
-      </c>
-      <c r="B103" t="s">
-        <v>98</v>
-      </c>
-      <c r="C103" t="s">
-        <v>98</v>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Verma</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D103">
         <v>8.4</v>
@@ -5462,21 +4696,21 @@
         <v>79</v>
       </c>
       <c r="H103">
-        <v>62.343329700000012</v>
+        <v>62.34332970000001</v>
       </c>
       <c r="I103">
-        <v>8.0588759000000003</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9">
-      <c r="A104" t="s">
-        <v>205</v>
-      </c>
-      <c r="B104" t="s">
-        <v>98</v>
-      </c>
-      <c r="C104" t="s">
-        <v>98</v>
+        <v>8.0588759</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Via</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D104">
         <v>3.2</v>
@@ -5491,21 +4725,21 @@
         <v>109</v>
       </c>
       <c r="H104">
-        <v>61.871614100000009</v>
+        <v>61.87161410000001</v>
       </c>
       <c r="I104">
-        <v>6.8477066000000004</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
-      <c r="A105" t="s">
-        <v>206</v>
-      </c>
-      <c r="B105" t="s">
-        <v>98</v>
-      </c>
-      <c r="C105" t="s">
-        <v>98</v>
+        <v>6.8477066</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Viddal</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Hydro</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Hydro</v>
       </c>
       <c r="D105">
         <v>5.5</v>
@@ -5520,75 +4754,74 @@
         <v>141</v>
       </c>
       <c r="H105">
-        <v>62.139749200000011</v>
+        <v>62.13974920000001</v>
       </c>
       <c r="I105">
-        <v>6.6117854999999999</v>
+        <v>6.6117855</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I105"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="12" max="12" width="1.3671875" hidden="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>line_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>area0</v>
+      </c>
+      <c r="C1" t="str">
+        <v>bus0</v>
+      </c>
+      <c r="D1" t="str">
+        <v>bus1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>length</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Vbase</v>
+      </c>
+      <c r="G1" t="str">
+        <v>lat</v>
+      </c>
+      <c r="H1" t="str">
+        <v>lon</v>
+      </c>
+      <c r="I1" t="str">
+        <v>R_per_m</v>
+      </c>
+      <c r="J1" t="str">
+        <v>X_per_m</v>
+      </c>
+      <c r="K1" t="str">
+        <v>B_per_m</v>
+      </c>
+      <c r="L1" t="str">
+        <v>name</v>
+      </c>
+      <c r="M1" t="str">
+        <v>eic code</v>
+      </c>
+      <c r="N1" t="str">
+        <v>S_max</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1166</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
+      <c r="B2" t="str">
+        <v>NO3</v>
       </c>
       <c r="C2">
         <v>77</v>
@@ -5597,42 +4830,42 @@
         <v>107</v>
       </c>
       <c r="E2">
-        <v>33284.984373810199</v>
+        <v>33284.9843738102</v>
       </c>
       <c r="F2">
         <v>132</v>
       </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
+      <c r="G2" t="str">
+        <v>[63.0581865391036, 63.169235, 63.271747122419]</v>
+      </c>
+      <c r="H2" t="str">
+        <v>[9.6024199750926, 9.95773300000001, 9.93306218856054]</v>
       </c>
       <c r="I2">
-        <v>5.9999960132916883E-5</v>
+        <v>0.00005999996013291688</v>
       </c>
       <c r="J2">
-        <v>3.0100000000000011E-4</v>
+        <v>0.0003010000000000001</v>
       </c>
       <c r="K2">
-        <v>3E-9</v>
-      </c>
-      <c r="L2" t="s">
-        <v>13</v>
+        <v>3e-9</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Thamshavn trafostasjon – Grana koblingsstasjon</v>
       </c>
       <c r="M2">
         <v>10943</v>
       </c>
-      <c r="N2">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="N2" t="str">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>1334</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
+      <c r="B3" t="str">
+        <v>NO3</v>
       </c>
       <c r="C3">
         <v>46</v>
@@ -5641,42 +4874,42 @@
         <v>62</v>
       </c>
       <c r="E3">
-        <v>9416.3881286834712</v>
-      </c>
-      <c r="F3">
+        <v>9416.388128683471</v>
+      </c>
+      <c r="F3" t="str">
         <v>132</v>
       </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
+      <c r="G3" t="str">
+        <v>[62.6815788399503, 62.6288473888959]</v>
+      </c>
+      <c r="H3" t="str">
+        <v>[10.1228770726635, 10.2663749273365]</v>
       </c>
       <c r="I3">
-        <v>5.9999960132916849E-5</v>
+        <v>0.00005999996013291685</v>
       </c>
       <c r="J3">
-        <v>3.0099999999999989E-4</v>
+        <v>0.0003009999999999999</v>
       </c>
       <c r="K3">
-        <v>3E-9</v>
-      </c>
-      <c r="L3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" t="s">
-        <v>17</v>
-      </c>
-      <c r="N3">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>3e-9</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Brattset trafostasjon – Brattset trafostasjon</v>
+      </c>
+      <c r="M3" t="str">
+        <v>3rr4</v>
+      </c>
+      <c r="N3" t="str">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>1335</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
+      <c r="B4" t="str">
+        <v>NO3</v>
       </c>
       <c r="C4">
         <v>62</v>
@@ -5690,34 +4923,37 @@
       <c r="F4">
         <v>132</v>
       </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
+      <c r="G4" t="str">
+        <v>[62.764642333228, 62.6818480622148]</v>
+      </c>
+      <c r="H4" t="str">
+        <v>[9.93059299951052, 10.1222020004895]</v>
       </c>
       <c r="I4">
-        <v>5.9999960132916842E-5</v>
+        <v>0.00005999996013291684</v>
       </c>
       <c r="J4">
-        <v>3.0100000000000011E-4</v>
+        <v>0.0003010000000000001</v>
       </c>
       <c r="K4">
-        <v>3E-9</v>
-      </c>
-      <c r="L4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N4">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>3e-9</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Brattset trafostasjon – Brattset trafostasjon</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>1336</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
+      <c r="B5" t="str">
+        <v>NO3</v>
       </c>
       <c r="C5">
         <v>107</v>
@@ -5731,37 +4967,37 @@
       <c r="F5">
         <v>132</v>
       </c>
-      <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
+      <c r="G5" t="str">
+        <v>[63.0578905163084, 62.7649652979347]</v>
+      </c>
+      <c r="H5" t="str">
+        <v>[9.60225399160166, 9.93006400839835]</v>
       </c>
       <c r="I5">
-        <v>5.9999960132916842E-5</v>
+        <v>0.00005999996013291684</v>
       </c>
       <c r="J5">
-        <v>3.01E-4</v>
+        <v>0.000301</v>
       </c>
       <c r="K5">
-        <v>3E-9</v>
-      </c>
-      <c r="L5" t="s">
-        <v>22</v>
+        <v>3e-9</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Grana koblingsstasjon – Brattset trafostasjon</v>
       </c>
       <c r="M5">
         <v>3343</v>
       </c>
-      <c r="N5">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="N5" t="str">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>1165</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
+      <c r="B6" t="str">
+        <v>NO3</v>
       </c>
       <c r="C6">
         <v>141</v>
@@ -5775,34 +5011,37 @@
       <c r="F6">
         <v>132</v>
       </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
+      <c r="G6" t="str">
+        <v>[62.4779336946648, 61.7329656956376]</v>
+      </c>
+      <c r="H6" t="str">
+        <v>[7.03366082879706, 5.21884217120294]</v>
       </c>
       <c r="I6">
-        <v>5.9999960132916849E-5</v>
+        <v>0.00005999996013291685</v>
       </c>
       <c r="J6">
-        <v>3.0100000000000011E-4</v>
+        <v>0.0003010000000000001</v>
       </c>
       <c r="K6">
-        <v>3E-9</v>
-      </c>
-      <c r="L6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>3e-9</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Ørskog trafostasjon – Svelgen trafostasjon</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>1289</v>
       </c>
-      <c r="B7" t="s">
-        <v>10</v>
+      <c r="B7" t="str">
+        <v>NO3</v>
       </c>
       <c r="C7">
         <v>138</v>
@@ -5816,34 +5055,37 @@
       <c r="F7">
         <v>300</v>
       </c>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
+      <c r="G7" t="str">
+        <v>[63.979469495752, 63.951246, 63.7796426966659]</v>
+      </c>
+      <c r="H7" t="str">
+        <v>[11.4783430752882, 11.578217, 11.4725900216729]</v>
       </c>
       <c r="I7">
-        <v>4.000000000000001E-5</v>
+        <v>0.00004000000000000001</v>
       </c>
       <c r="J7">
-        <v>2.6499999999999999E-4</v>
+        <v>0.000265</v>
       </c>
       <c r="K7">
-        <v>3.9000000000000002E-9</v>
-      </c>
-      <c r="L7" t="s">
-        <v>28</v>
+        <v>3.9e-9</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Ogndal trafostasjon – Verdal trafostasjon</v>
+      </c>
+      <c r="M7" t="str">
+        <v/>
       </c>
       <c r="N7">
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8">
       <c r="A8">
         <v>1290</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
+      <c r="B8" t="str">
+        <v>NO3</v>
       </c>
       <c r="C8">
         <v>105</v>
@@ -5852,28 +5094,28 @@
         <v>139</v>
       </c>
       <c r="E8">
-        <v>42360.417254709202</v>
+        <v>42360.4172547092</v>
       </c>
       <c r="F8">
         <v>300</v>
       </c>
-      <c r="G8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" t="s">
-        <v>30</v>
+      <c r="G8" t="str">
+        <v>[63.7792842667966, 63.4574296446683]</v>
+      </c>
+      <c r="H8" t="str">
+        <v>[11.4722350100571, 11.0181519899429]</v>
       </c>
       <c r="I8">
-        <v>4.0000000000000003E-5</v>
+        <v>0.00004</v>
       </c>
       <c r="J8">
-        <v>2.6499999999999999E-4</v>
+        <v>0.000265</v>
       </c>
       <c r="K8">
-        <v>3.9000000000000002E-9</v>
-      </c>
-      <c r="L8" t="s">
-        <v>31</v>
+        <v>3.9e-9</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Verdal trafostasjon – Eidum trafostasjon</v>
       </c>
       <c r="M8">
         <v>343321</v>
@@ -5882,12 +5124,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9">
       <c r="A9">
         <v>1291</v>
       </c>
-      <c r="B9" t="s">
-        <v>10</v>
+      <c r="B9" t="str">
+        <v>NO3</v>
       </c>
       <c r="C9">
         <v>139</v>
@@ -5896,39 +5138,42 @@
         <v>106</v>
       </c>
       <c r="E9">
-        <v>29662.113492755401</v>
+        <v>29662.1134927554</v>
       </c>
       <c r="F9">
         <v>300</v>
       </c>
-      <c r="G9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" t="s">
-        <v>33</v>
+      <c r="G9" t="str">
+        <v>[63.4013872743893, 63.423488, 63.4571907093831]</v>
+      </c>
+      <c r="H9" t="str">
+        <v>[10.4402013779148, 10.813293, 11.0174939283141]</v>
       </c>
       <c r="I9">
-        <v>4.0000000000000017E-5</v>
+        <v>0.00004000000000000002</v>
       </c>
       <c r="J9">
-        <v>2.6499999999999999E-4</v>
+        <v>0.000265</v>
       </c>
       <c r="K9">
-        <v>3.9000000000000002E-9</v>
-      </c>
-      <c r="L9" t="s">
-        <v>34</v>
+        <v>3.9e-9</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Eidum trafostasjon – Strinda koblingsstasjon</v>
+      </c>
+      <c r="M9" t="str">
+        <v/>
       </c>
       <c r="N9">
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10">
       <c r="A10">
         <v>1173</v>
       </c>
-      <c r="B10" t="s">
-        <v>10</v>
+      <c r="B10" t="str">
+        <v>NO3</v>
       </c>
       <c r="C10">
         <v>105</v>
@@ -5937,39 +5182,42 @@
         <v>76</v>
       </c>
       <c r="E10">
-        <v>84842.698575108603</v>
+        <v>84842.6985751086</v>
       </c>
       <c r="F10">
         <v>300</v>
       </c>
-      <c r="G10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" t="s">
-        <v>36</v>
+      <c r="G10" t="str">
+        <v>[63.779267150403, 63.703506, 63.409354, 63.2769667913878]</v>
+      </c>
+      <c r="H10" t="str">
+        <v>[11.4726336570695, 11.538391, 11.15387, 10.4580241866236]</v>
       </c>
       <c r="I10">
-        <v>4.0000000000000003E-5</v>
+        <v>0.00004</v>
       </c>
       <c r="J10">
-        <v>2.6499999999999999E-4</v>
+        <v>0.000265</v>
       </c>
       <c r="K10">
-        <v>3.9000000000000002E-9</v>
-      </c>
-      <c r="L10" t="s">
-        <v>37</v>
+        <v>3.9e-9</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Verdal trafostasjon – Klæbu transformatorstasjon</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
       </c>
       <c r="N10">
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11">
       <c r="A11">
         <v>1174</v>
       </c>
-      <c r="B11" t="s">
-        <v>10</v>
+      <c r="B11" t="str">
+        <v>NO3</v>
       </c>
       <c r="C11">
         <v>106</v>
@@ -5983,34 +5231,37 @@
       <c r="F11">
         <v>300</v>
       </c>
-      <c r="G11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" t="s">
-        <v>39</v>
+      <c r="G11" t="str">
+        <v>[63.2770887040084, 63.4011611611364]</v>
+      </c>
+      <c r="H11" t="str">
+        <v>[10.4575822753626, 10.4397867246374]</v>
       </c>
       <c r="I11">
-        <v>4.0000000000000003E-5</v>
+        <v>0.00004</v>
       </c>
       <c r="J11">
-        <v>2.6499999999999999E-4</v>
+        <v>0.000265</v>
       </c>
       <c r="K11">
-        <v>3.9000000000000002E-9</v>
-      </c>
-      <c r="L11" t="s">
-        <v>40</v>
+        <v>3.9e-9</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Strinda koblingsstasjon – Klæbu transformatorstasjon</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
       </c>
       <c r="N11">
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12">
       <c r="A12">
         <v>1292</v>
       </c>
-      <c r="B12" t="s">
-        <v>10</v>
+      <c r="B12" t="str">
+        <v>NO3</v>
       </c>
       <c r="C12">
         <v>76</v>
@@ -6024,34 +5275,37 @@
       <c r="F12">
         <v>300</v>
       </c>
-      <c r="G12" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" t="s">
-        <v>42</v>
+      <c r="G12" t="str">
+        <v>[63.2719119610727, 63.268241, 63.23672, 63.2768450273625]</v>
+      </c>
+      <c r="H12" t="str">
+        <v>[9.93345548452976, 9.979706, 10.04837, 10.4571728802973]</v>
       </c>
       <c r="I12">
-        <v>3.999999999999999E-5</v>
+        <v>0.00003999999999999999</v>
       </c>
       <c r="J12">
-        <v>2.6499999999999999E-4</v>
+        <v>0.000265</v>
       </c>
       <c r="K12">
-        <v>3.9000000000000002E-9</v>
-      </c>
-      <c r="L12" t="s">
-        <v>43</v>
+        <v>3.9e-9</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Klæbu transformatorstasjon – Orkdal transformatorstasjon</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
       </c>
       <c r="N12">
         <v>500</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13">
       <c r="A13">
         <v>1175</v>
       </c>
-      <c r="B13" t="s">
-        <v>10</v>
+      <c r="B13" t="str">
+        <v>NO3</v>
       </c>
       <c r="C13">
         <v>60</v>
@@ -6065,34 +5319,37 @@
       <c r="F13">
         <v>300</v>
       </c>
-      <c r="G13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" t="s">
-        <v>45</v>
+      <c r="G13" t="str">
+        <v>[62.6799952696754, 63.021959, 63.202068, 63.2717982207385]</v>
+      </c>
+      <c r="H13" t="str">
+        <v>[8.48028947595439, 8.897552, 9.79156500000001, 9.93271247746952]</v>
       </c>
       <c r="I13">
-        <v>4.0000000000000003E-5</v>
+        <v>0.00004</v>
       </c>
       <c r="J13">
-        <v>2.6499999999999999E-4</v>
+        <v>0.000265</v>
       </c>
       <c r="K13">
-        <v>3.9000000000000002E-9</v>
-      </c>
-      <c r="L13" t="s">
-        <v>46</v>
+        <v>3.9e-9</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Orkdal transformatorstasjon – Aura trafostasjon</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
       </c>
       <c r="N13">
         <v>500</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14">
       <c r="A14">
         <v>6798</v>
       </c>
-      <c r="B14" t="s">
-        <v>10</v>
+      <c r="B14" t="str">
+        <v>NO3</v>
       </c>
       <c r="C14">
         <v>45</v>
@@ -6101,39 +5358,42 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>93475.106910836999</v>
+        <v>93475.106910837</v>
       </c>
       <c r="F14">
         <v>300</v>
       </c>
-      <c r="G14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" t="s">
-        <v>48</v>
+      <c r="G14" t="str">
+        <v>[61.8861304294624, 62.6796217603448]</v>
+      </c>
+      <c r="H14" t="str">
+        <v>[9.06357629708208, 8.48021670291793]</v>
       </c>
       <c r="I14">
-        <v>4.0000000000000003E-5</v>
+        <v>0.00004</v>
       </c>
       <c r="J14">
-        <v>2.6499999999999999E-4</v>
+        <v>0.000265</v>
       </c>
       <c r="K14">
-        <v>3.9000000000000002E-9</v>
-      </c>
-      <c r="L14" t="s">
-        <v>49</v>
+        <v>3.9e-9</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Aura trafostasjon – Vågåmo trafo stasjon</v>
+      </c>
+      <c r="M14" t="str">
+        <v/>
       </c>
       <c r="N14">
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15">
       <c r="A15">
         <v>1288</v>
       </c>
-      <c r="B15" t="s">
-        <v>10</v>
+      <c r="B15" t="str">
+        <v>NO3</v>
       </c>
       <c r="C15">
         <v>138</v>
@@ -6147,34 +5407,37 @@
       <c r="F15">
         <v>300</v>
       </c>
-      <c r="G15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" t="s">
-        <v>51</v>
+      <c r="G15" t="str">
+        <v>[63.9797705313635, 64.4536577724636]</v>
+      </c>
+      <c r="H15" t="str">
+        <v>[11.4780240828036, 11.6207309171964]</v>
       </c>
       <c r="I15">
-        <v>4.0000000000000003E-5</v>
+        <v>0.00004</v>
       </c>
       <c r="J15">
-        <v>2.6499999999999999E-4</v>
+        <v>0.000265</v>
       </c>
       <c r="K15">
-        <v>3.9000000000000002E-9</v>
-      </c>
-      <c r="L15" t="s">
-        <v>52</v>
+        <v>3.9e-9</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Ogndal trafostasjon – Namsos (Statnett) trafostasjon</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
       </c>
       <c r="N15">
         <v>500</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16">
       <c r="A16">
         <v>6562</v>
       </c>
-      <c r="B16" t="s">
-        <v>10</v>
+      <c r="B16" t="str">
+        <v>NO3</v>
       </c>
       <c r="C16">
         <v>61</v>
@@ -6183,39 +5446,42 @@
         <v>79</v>
       </c>
       <c r="E16">
-        <v>39089.795205363604</v>
+        <v>39089.7952053636</v>
       </c>
       <c r="F16">
         <v>380</v>
       </c>
-      <c r="G16" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" t="s">
-        <v>54</v>
+      <c r="G16" t="str">
+        <v>[62.5263493502315, 62.6797261154976]</v>
+      </c>
+      <c r="H16" t="str">
+        <v>[7.79520216211446, 8.47966983788554]</v>
       </c>
       <c r="I16">
-        <v>2.9999999999999991E-5</v>
+        <v>0.00002999999999999999</v>
       </c>
       <c r="J16">
-        <v>2.4599999999999991E-4</v>
+        <v>0.0002459999999999999</v>
       </c>
       <c r="K16">
-        <v>4.1000000000000003E-9</v>
-      </c>
-      <c r="L16" t="s">
-        <v>55</v>
+        <v>4.1e-9</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Viklandet trafostasjon – Grytten trafostasjon</v>
+      </c>
+      <c r="M16" t="str">
+        <v/>
       </c>
       <c r="N16">
         <v>600</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17">
       <c r="A17">
         <v>1293</v>
       </c>
-      <c r="B17" t="s">
-        <v>10</v>
+      <c r="B17" t="str">
+        <v>NO3</v>
       </c>
       <c r="C17">
         <v>78</v>
@@ -6224,39 +5490,42 @@
         <v>61</v>
       </c>
       <c r="E17">
-        <v>139115.67012162399</v>
+        <v>139115.670121624</v>
       </c>
       <c r="F17">
         <v>380</v>
       </c>
-      <c r="G17" t="s">
-        <v>56</v>
-      </c>
-      <c r="H17" t="s">
-        <v>57</v>
+      <c r="G17" t="str">
+        <v>[63.2769332188306, 63.325632, 63.085435, 62.6800121989769]</v>
+      </c>
+      <c r="H17" t="str">
+        <v>[10.4571743955897, 9.986572, 8.751984, 8.480202620587]</v>
       </c>
       <c r="I17">
-        <v>3.0000000000000001E-5</v>
+        <v>0.00003</v>
       </c>
       <c r="J17">
-        <v>2.4600000000000012E-4</v>
+        <v>0.0002460000000000001</v>
       </c>
       <c r="K17">
-        <v>4.1000000000000003E-9</v>
-      </c>
-      <c r="L17" t="s">
-        <v>58</v>
+        <v>4.1e-9</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Klæbu transformatorstasjon – Viklandet trafostasjon</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
       </c>
       <c r="N17">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18">
       <c r="A18">
         <v>1176</v>
       </c>
-      <c r="B18" t="s">
-        <v>10</v>
+      <c r="B18" t="str">
+        <v>NO3</v>
       </c>
       <c r="C18">
         <v>109</v>
@@ -6265,39 +5534,42 @@
         <v>79</v>
       </c>
       <c r="E18">
-        <v>39526.878796049503</v>
+        <v>39526.8787960495</v>
       </c>
       <c r="F18">
         <v>380</v>
       </c>
-      <c r="G18" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" t="s">
-        <v>60</v>
+      <c r="G18" t="str">
+        <v>[62.4780980928918, 62.5262309524377]</v>
+      </c>
+      <c r="H18" t="str">
+        <v>[7.03444016980177, 7.79435683019823]</v>
       </c>
       <c r="I18">
-        <v>3.0000000000000001E-5</v>
+        <v>0.00003</v>
       </c>
       <c r="J18">
-        <v>2.4600000000000002E-4</v>
+        <v>0.000246</v>
       </c>
       <c r="K18">
-        <v>4.1000000000000003E-9</v>
-      </c>
-      <c r="L18" t="s">
-        <v>61</v>
+        <v>4.1e-9</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Ørskog trafostasjon – Grytten trafostasjon</v>
+      </c>
+      <c r="M18" t="str">
+        <v/>
       </c>
       <c r="N18">
         <v>600</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19">
       <c r="A19">
         <v>1317</v>
       </c>
-      <c r="B19" t="s">
-        <v>10</v>
+      <c r="B19" t="str">
+        <v>NO3</v>
       </c>
       <c r="C19">
         <v>78</v>
@@ -6306,39 +5578,42 @@
         <v>108</v>
       </c>
       <c r="E19">
-        <v>69764.072956209508</v>
+        <v>69764.07295620951</v>
       </c>
       <c r="F19">
         <v>380</v>
       </c>
-      <c r="G19" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" t="s">
-        <v>63</v>
+      <c r="G19" t="str">
+        <v>[63.0357063153294, 63.061804, 63.22373, 63.2768185449166]</v>
+      </c>
+      <c r="H19" t="str">
+        <v>[11.7274675384392, 11.469727, 10.778961, 10.4580312550914]</v>
       </c>
       <c r="I19">
-        <v>3.0000000000000011E-5</v>
+        <v>0.00003000000000000001</v>
       </c>
       <c r="J19">
-        <v>2.4600000000000002E-4</v>
+        <v>0.000246</v>
       </c>
       <c r="K19">
-        <v>4.1000000000000003E-9</v>
-      </c>
-      <c r="L19" t="s">
-        <v>64</v>
+        <v>4.1e-9</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Klæbu transformatorstasjon – Nea trafostasjon</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
       </c>
       <c r="N19">
         <v>600</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20">
       <c r="A20">
         <v>6799</v>
       </c>
-      <c r="B20" t="s">
-        <v>10</v>
+      <c r="B20" t="str">
+        <v>NO3</v>
       </c>
       <c r="C20">
         <v>177</v>
@@ -6352,31 +5627,37 @@
       <c r="F20">
         <v>300</v>
       </c>
-      <c r="G20" t="s">
-        <v>224</v>
-      </c>
-      <c r="H20" t="s">
-        <v>225</v>
+      <c r="G20" t="str">
+        <v>[61.73283, 61.88593]</v>
+      </c>
+      <c r="H20" t="str">
+        <v>[5.218506, 9.063721]</v>
       </c>
       <c r="I20">
-        <v>4.0000000000000003E-5</v>
+        <v>0.00004</v>
       </c>
       <c r="J20">
-        <v>2.6499999999999999E-4</v>
+        <v>0.000265</v>
       </c>
       <c r="K20">
-        <v>3.9000000000000002E-9</v>
+        <v>3.9e-9</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v/>
       </c>
       <c r="N20">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21">
       <c r="A21">
         <v>6800</v>
       </c>
-      <c r="B21" t="s">
-        <v>10</v>
+      <c r="B21" t="str">
+        <v>NO3</v>
       </c>
       <c r="C21">
         <v>30</v>
@@ -6390,31 +5671,37 @@
       <c r="F21">
         <v>300</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>227</v>
+      <c r="G21" t="str">
+        <v>[61.88593, 62.62872]</v>
+      </c>
+      <c r="H21" t="str">
+        <v>[9.063721, 10.26672]</v>
       </c>
       <c r="I21">
-        <v>4.0000000000000003E-5</v>
+        <v>0.00004</v>
       </c>
       <c r="J21">
-        <v>2.6499999999999999E-4</v>
+        <v>0.000265</v>
       </c>
       <c r="K21">
-        <v>3.9000000000000002E-9</v>
+        <v>3.9e-9</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
       </c>
       <c r="N21">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22">
       <c r="A22">
         <v>6801</v>
       </c>
-      <c r="B22" t="s">
-        <v>10</v>
+      <c r="B22" t="str">
+        <v>NO3</v>
       </c>
       <c r="C22">
         <v>179</v>
@@ -6428,31 +5715,37 @@
       <c r="F22">
         <v>380</v>
       </c>
-      <c r="G22" t="s">
-        <v>228</v>
-      </c>
-      <c r="H22" t="s">
-        <v>229</v>
+      <c r="G22" t="str">
+        <v>[62.628719, 63.035662]</v>
+      </c>
+      <c r="H22" t="str">
+        <v>[10.26672, 11.72791]</v>
       </c>
       <c r="I22">
-        <v>3.0000000000000011E-5</v>
+        <v>0.00003000000000000001</v>
       </c>
       <c r="J22">
-        <v>2.4600000000000002E-4</v>
+        <v>0.000246</v>
       </c>
       <c r="K22">
-        <v>4.1000000000000003E-9</v>
+        <v>4.1e-9</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
       </c>
       <c r="N22">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23">
       <c r="A23">
         <v>6802</v>
       </c>
-      <c r="B23" t="s">
-        <v>10</v>
+      <c r="B23" t="str">
+        <v>NO3</v>
       </c>
       <c r="C23">
         <v>108</v>
@@ -6466,65 +5759,69 @@
       <c r="F23">
         <v>380</v>
       </c>
-      <c r="G23" t="s">
-        <v>230</v>
-      </c>
-      <c r="H23" t="s">
-        <v>231</v>
+      <c r="G23" t="str">
+        <v>[63.035662, 64.453849]</v>
+      </c>
+      <c r="H23" t="str">
+        <v>[11.72791, 11.62079]</v>
       </c>
       <c r="I23">
-        <v>3.0000000000000011E-5</v>
+        <v>0.00003000000000000001</v>
       </c>
       <c r="J23">
-        <v>2.4600000000000002E-4</v>
+        <v>0.000246</v>
       </c>
       <c r="K23">
-        <v>4.1000000000000003E-9</v>
+        <v>4.1e-9</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
       </c>
       <c r="N23">
         <v>600</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N23"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>transformer_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>bus0</v>
+      </c>
+      <c r="C1" t="str">
+        <v>bus1</v>
+      </c>
+      <c r="D1" t="str">
+        <v>ratio</v>
+      </c>
+      <c r="E1" t="str">
+        <v>R</v>
+      </c>
+      <c r="F1" t="str">
+        <v>X</v>
+      </c>
+      <c r="G1" t="str">
+        <v>name</v>
+      </c>
+      <c r="H1" t="str">
+        <v>S_max</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>43</v>
       </c>
@@ -6535,22 +5832,22 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>0.78947368421052633</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="E2">
-        <v>5.6000000000000006E-4</v>
+        <v>0.0005600000000000001</v>
       </c>
       <c r="F2">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="G2" t="s">
-        <v>211</v>
-      </c>
-      <c r="H2" s="4">
+        <v>0.028</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Klæbu transformatorstasjon – Klæbu transformatorstasjon</v>
+      </c>
+      <c r="H2">
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3">
       <c r="A3">
         <v>44</v>
       </c>
@@ -6564,19 +5861,19 @@
         <v>0.44</v>
       </c>
       <c r="E3">
-        <v>8.0000000000000004E-4</v>
+        <v>0.0008</v>
       </c>
       <c r="F3">
         <v>0.04</v>
       </c>
-      <c r="G3" t="s">
-        <v>212</v>
-      </c>
-      <c r="H3" s="4">
+      <c r="G3" t="str">
+        <v>Thamshavn trafostasjon – Orkdal transformatorstasjon</v>
+      </c>
+      <c r="H3">
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4">
       <c r="A4">
         <v>45</v>
       </c>
@@ -6590,19 +5887,19 @@
         <v>0.3473684210526316</v>
       </c>
       <c r="E4">
-        <v>5.6000000000000006E-4</v>
+        <v>0.0005600000000000001</v>
       </c>
       <c r="F4">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="G4" t="s">
-        <v>213</v>
-      </c>
-      <c r="H4" s="4">
+        <v>0.028</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Ørskog trafostasjon – Ørskog trafostasjon</v>
+      </c>
+      <c r="H4">
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5">
       <c r="A5">
         <v>46</v>
       </c>
@@ -6613,22 +5910,22 @@
         <v>61</v>
       </c>
       <c r="D5">
-        <v>0.78947368421052633</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="E5">
-        <v>5.6000000000000006E-4</v>
+        <v>0.0005600000000000001</v>
       </c>
       <c r="F5">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="G5" t="s">
-        <v>214</v>
-      </c>
-      <c r="H5" s="4">
+        <v>0.028</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Aura trafostasjon – Viklandet trafostasjon</v>
+      </c>
+      <c r="H5">
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6">
       <c r="A6">
         <v>47</v>
       </c>
@@ -6642,19 +5939,19 @@
         <v>0.44</v>
       </c>
       <c r="E6">
-        <v>8.0000000000000004E-4</v>
+        <v>0.0008</v>
       </c>
       <c r="F6">
         <v>0.04</v>
       </c>
-      <c r="G6" t="s">
-        <v>232</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="G6" t="str">
+        <v>Svelgen transformatorstasjon 132/300 kV</v>
+      </c>
+      <c r="H6">
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7">
       <c r="A7">
         <v>48</v>
       </c>
@@ -6668,19 +5965,19 @@
         <v>0.44</v>
       </c>
       <c r="E7">
-        <v>8.0000000000000004E-4</v>
+        <v>0.0008</v>
       </c>
       <c r="F7">
         <v>0.04</v>
       </c>
-      <c r="G7" t="s">
-        <v>233</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="G7" t="str">
+        <v>Brattset transformatorstasjon 132/300 kV</v>
+      </c>
+      <c r="H7">
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8">
       <c r="A8">
         <v>49</v>
       </c>
@@ -6691,22 +5988,22 @@
         <v>179</v>
       </c>
       <c r="D8">
-        <v>0.34736800000000001</v>
+        <v>0.347368</v>
       </c>
       <c r="E8">
-        <v>5.5999999999999995E-4</v>
+        <v>0.00056</v>
       </c>
       <c r="F8">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>234</v>
-      </c>
-      <c r="H8" s="4">
+        <v>0.028</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Brattset transformatorstasjon 132/380 kV</v>
+      </c>
+      <c r="H8">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="17.399999999999999" customHeight="1">
+    <row r="9">
       <c r="A9">
         <v>50</v>
       </c>
@@ -6717,61 +6014,66 @@
         <v>180</v>
       </c>
       <c r="D9">
-        <v>0.78947400000000001</v>
+        <v>0.789474</v>
       </c>
       <c r="E9">
-        <v>5.5999999999999995E-4</v>
+        <v>0.00056</v>
       </c>
       <c r="F9">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="H9" s="4">
+        <v>0.028</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Namsos transformatorstasjon 300/380 kV</v>
+      </c>
+      <c r="H9">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>217</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>index</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>area0</v>
+      </c>
+      <c r="D1" t="str">
+        <v>area1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>bus0</v>
+      </c>
+      <c r="F1" t="str">
+        <v>bus1</v>
+      </c>
+      <c r="G1" t="str">
+        <v>lat</v>
+      </c>
+      <c r="H1" t="str">
+        <v>lon</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Pinj</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Grid/test_trøndelagsnettet.xlsx
+++ b/Grid/test_trøndelagsnettet.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2d06795444358214/Dokumenter/Kraftsystemer2/Kraftsystemer-2/Grid/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_9FB226B1E151B707924040B6B0AF1111307A89B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC15C1DF-1045-4B83-B5DF-6C59CBB0A7DF}"/>
+  <bookViews>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="bus" sheetId="1" r:id="rId1"/>
     <sheet name="gen" sheetId="2" r:id="rId2"/>
@@ -9,38 +19,744 @@
     <sheet name="trafo" sheetId="4" r:id="rId4"/>
     <sheet name="link" sheetId="5" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="242">
+  <si>
+    <t>bus_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>bidz</t>
+  </si>
+  <si>
+    <t>Vbase</t>
+  </si>
+  <si>
+    <t>lat</t>
+  </si>
+  <si>
+    <t>lon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S_base [MVA] </t>
+  </si>
+  <si>
+    <t>V [P.U]</t>
+  </si>
+  <si>
+    <t>Angle [rad]</t>
+  </si>
+  <si>
+    <t>P_gen</t>
+  </si>
+  <si>
+    <t>Q_gen</t>
+  </si>
+  <si>
+    <t>P_load</t>
+  </si>
+  <si>
+    <t>Q_load</t>
+  </si>
+  <si>
+    <t>S_max</t>
+  </si>
+  <si>
+    <t>V_max</t>
+  </si>
+  <si>
+    <t>V_min</t>
+  </si>
+  <si>
+    <t>Vågåmo trafo stasjon</t>
+  </si>
+  <si>
+    <t>NO3</t>
+  </si>
+  <si>
+    <t>Aura trafostasjon</t>
+  </si>
+  <si>
+    <t>Brattset trafostasjon</t>
+  </si>
+  <si>
+    <t>Orkdal transformatorstasjon</t>
+  </si>
+  <si>
+    <t>Viklandet trafostasjon</t>
+  </si>
+  <si>
+    <t>Klæbu transformatorstasjon</t>
+  </si>
+  <si>
+    <t>Thamshavn trafostasjon</t>
+  </si>
+  <si>
+    <t>Grytten trafostasjon</t>
+  </si>
+  <si>
+    <t>Verdal trafostasjon</t>
+  </si>
+  <si>
+    <t>Strinda koblingsstasjon</t>
+  </si>
+  <si>
+    <t>Grana koblingsstasjon</t>
+  </si>
+  <si>
+    <t>Nea trafostasjon</t>
+  </si>
+  <si>
+    <t>Ørskog trafostasjon</t>
+  </si>
+  <si>
+    <t>Ogndal trafostasjon</t>
+  </si>
+  <si>
+    <t>Eidum trafostasjon</t>
+  </si>
+  <si>
+    <t>Svelgen trafostasjon</t>
+  </si>
+  <si>
+    <t>Namsos (Statnett) trafostasjon</t>
+  </si>
+  <si>
+    <t>Svelgen 300 kV</t>
+  </si>
+  <si>
+    <t>Brattset 380 kV</t>
+  </si>
+  <si>
+    <t>Namsos 380 kV</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>type2</t>
+  </si>
+  <si>
+    <t>Pmax</t>
+  </si>
+  <si>
+    <t>Qmax</t>
+  </si>
+  <si>
+    <t>Qmin</t>
+  </si>
+  <si>
+    <t>bus</t>
+  </si>
+  <si>
+    <t>Grytten</t>
+  </si>
+  <si>
+    <t>Hydro</t>
+  </si>
+  <si>
+    <t>Reservoir</t>
+  </si>
+  <si>
+    <t>Tevla</t>
+  </si>
+  <si>
+    <t>Pumped Storage</t>
+  </si>
+  <si>
+    <t>Svelgfoss</t>
+  </si>
+  <si>
+    <t>Run-Of-River</t>
+  </si>
+  <si>
+    <t>Driva</t>
+  </si>
+  <si>
+    <t>Brattset</t>
+  </si>
+  <si>
+    <t>Brattingfoss</t>
+  </si>
+  <si>
+    <t>Bratsberg</t>
+  </si>
+  <si>
+    <t>Askara</t>
+  </si>
+  <si>
+    <t>Nea</t>
+  </si>
+  <si>
+    <t>Mosvik</t>
+  </si>
+  <si>
+    <t>Ovre fiskumfoss</t>
+  </si>
+  <si>
+    <t>Harpefossen</t>
+  </si>
+  <si>
+    <t>Knutfoss</t>
+  </si>
+  <si>
+    <t>Oyberget</t>
+  </si>
+  <si>
+    <t>Rka nyhamna</t>
+  </si>
+  <si>
+    <t>Thermal</t>
+  </si>
+  <si>
+    <t>OCGT</t>
+  </si>
+  <si>
+    <t>Midtre tessa</t>
+  </si>
+  <si>
+    <t>Trolheim</t>
+  </si>
+  <si>
+    <t>Grana</t>
+  </si>
+  <si>
+    <t>Gresslifoss</t>
+  </si>
+  <si>
+    <t>Hegsetfoss</t>
+  </si>
+  <si>
+    <t>Istad</t>
+  </si>
+  <si>
+    <t>Gjerdsvik</t>
+  </si>
+  <si>
+    <t>Eidefossen</t>
+  </si>
+  <si>
+    <t>Fausa</t>
+  </si>
+  <si>
+    <t>Follafoss</t>
+  </si>
+  <si>
+    <t>Framruste</t>
+  </si>
+  <si>
+    <t>Furset</t>
+  </si>
+  <si>
+    <t>Norddalen</t>
+  </si>
+  <si>
+    <t>Vessingfoss</t>
+  </si>
+  <si>
+    <t>Svorkmo</t>
+  </si>
+  <si>
+    <t>Tussa</t>
+  </si>
+  <si>
+    <t>Tafjord</t>
+  </si>
+  <si>
+    <t>Fjaremsfossen</t>
+  </si>
+  <si>
+    <t>Bogna</t>
+  </si>
+  <si>
+    <t>Aunfoss</t>
+  </si>
+  <si>
+    <t>Fossan</t>
+  </si>
+  <si>
+    <t>Nedrenea</t>
+  </si>
+  <si>
+    <t>Litledalen</t>
+  </si>
+  <si>
+    <t>Kvitfossen</t>
+  </si>
+  <si>
+    <t>Kanstadbotn</t>
+  </si>
+  <si>
+    <t>Julskaret</t>
+  </si>
+  <si>
+    <t>Innvik</t>
+  </si>
+  <si>
+    <t>Byrkjelo</t>
+  </si>
+  <si>
+    <t>Byafossen</t>
+  </si>
+  <si>
+    <t>Brunstad</t>
+  </si>
+  <si>
+    <t>Brekkefoss</t>
+  </si>
+  <si>
+    <t>Asen</t>
+  </si>
+  <si>
+    <t>Eiriksdal</t>
+  </si>
+  <si>
+    <t>Funna</t>
+  </si>
+  <si>
+    <t>Hopselva</t>
+  </si>
+  <si>
+    <t>Giskemo</t>
+  </si>
+  <si>
+    <t>Fossheim</t>
+  </si>
+  <si>
+    <t>Embla</t>
+  </si>
+  <si>
+    <t>Eid</t>
+  </si>
+  <si>
+    <t>Lokaunet</t>
+  </si>
+  <si>
+    <t>Amela</t>
+  </si>
+  <si>
+    <t>Skjak</t>
+  </si>
+  <si>
+    <t>Skogheim</t>
+  </si>
+  <si>
+    <t>Usma selbu</t>
+  </si>
+  <si>
+    <t>Soa</t>
+  </si>
+  <si>
+    <t>Sorbrandal</t>
+  </si>
+  <si>
+    <t>Stadheim</t>
+  </si>
+  <si>
+    <t>Steinsvik</t>
+  </si>
+  <si>
+    <t>Stordal</t>
+  </si>
+  <si>
+    <t>Skulafossen</t>
+  </si>
+  <si>
+    <t>Trysilfossen</t>
+  </si>
+  <si>
+    <t>Urke</t>
+  </si>
+  <si>
+    <t>Trandal</t>
+  </si>
+  <si>
+    <t>Sykkylven</t>
+  </si>
+  <si>
+    <t>Vassli</t>
+  </si>
+  <si>
+    <t>Tjeldbergodden</t>
+  </si>
+  <si>
+    <t>Morre</t>
+  </si>
+  <si>
+    <t>Meraker</t>
+  </si>
+  <si>
+    <t>Osbu</t>
+  </si>
+  <si>
+    <t>Osen</t>
+  </si>
+  <si>
+    <t>Riksheimdal</t>
+  </si>
+  <si>
+    <t>Oksenelvane</t>
+  </si>
+  <si>
+    <t>Trollheim</t>
+  </si>
+  <si>
+    <t>Agdenes</t>
+  </si>
+  <si>
+    <t>Aselva</t>
+  </si>
+  <si>
+    <t>Brandaa</t>
+  </si>
+  <si>
+    <t>Bryggja</t>
+  </si>
+  <si>
+    <t>Eidsfossen sfe</t>
+  </si>
+  <si>
+    <t>Eidum</t>
+  </si>
+  <si>
+    <t>Fossan halogalan</t>
+  </si>
+  <si>
+    <t>Fr.stad bioel</t>
+  </si>
+  <si>
+    <t>Groa</t>
+  </si>
+  <si>
+    <t>Holla</t>
+  </si>
+  <si>
+    <t>Hopen</t>
+  </si>
+  <si>
+    <t>Innset</t>
+  </si>
+  <si>
+    <t>Jardola</t>
+  </si>
+  <si>
+    <t>Kassdalen</t>
+  </si>
+  <si>
+    <t>Kurasfossen</t>
+  </si>
+  <si>
+    <t>Namsos</t>
+  </si>
+  <si>
+    <t>Nordsvorka</t>
+  </si>
+  <si>
+    <t>Ogndal</t>
+  </si>
+  <si>
+    <t>Orkdal</t>
+  </si>
+  <si>
+    <t>Selbu</t>
+  </si>
+  <si>
+    <t>Thamshavn</t>
+  </si>
+  <si>
+    <t>Vagamo</t>
+  </si>
+  <si>
+    <t>Verdal</t>
+  </si>
+  <si>
+    <t>Verma</t>
+  </si>
+  <si>
+    <t>Via</t>
+  </si>
+  <si>
+    <t>Viddal</t>
+  </si>
+  <si>
+    <t>line_id</t>
+  </si>
+  <si>
+    <t>area0</t>
+  </si>
+  <si>
+    <t>bus0</t>
+  </si>
+  <si>
+    <t>bus1</t>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>R_per_m</t>
+  </si>
+  <si>
+    <t>X_per_m</t>
+  </si>
+  <si>
+    <t>B_per_m</t>
+  </si>
+  <si>
+    <t>eic code</t>
+  </si>
+  <si>
+    <t>[63.0581865391036, 63.169235, 63.271747122419]</t>
+  </si>
+  <si>
+    <t>[9.6024199750926, 9.95773300000001, 9.93306218856054]</t>
+  </si>
+  <si>
+    <t>Thamshavn trafostasjon – Grana koblingsstasjon</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>[62.6815788399503, 62.6288473888959]</t>
+  </si>
+  <si>
+    <t>[10.1228770726635, 10.2663749273365]</t>
+  </si>
+  <si>
+    <t>Brattset trafostasjon – Brattset trafostasjon</t>
+  </si>
+  <si>
+    <t>3rr4</t>
+  </si>
+  <si>
+    <t>[62.764642333228, 62.6818480622148]</t>
+  </si>
+  <si>
+    <t>[9.93059299951052, 10.1222020004895]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>[63.0578905163084, 62.7649652979347]</t>
+  </si>
+  <si>
+    <t>[9.60225399160166, 9.93006400839835]</t>
+  </si>
+  <si>
+    <t>Grana koblingsstasjon – Brattset trafostasjon</t>
+  </si>
+  <si>
+    <t>[62.4779336946648, 61.7329656956376]</t>
+  </si>
+  <si>
+    <t>[7.03366082879706, 5.21884217120294]</t>
+  </si>
+  <si>
+    <t>Ørskog trafostasjon – Svelgen trafostasjon</t>
+  </si>
+  <si>
+    <t>[63.979469495752, 63.951246, 63.7796426966659]</t>
+  </si>
+  <si>
+    <t>[11.4783430752882, 11.578217, 11.4725900216729]</t>
+  </si>
+  <si>
+    <t>Ogndal trafostasjon – Verdal trafostasjon</t>
+  </si>
+  <si>
+    <t>[63.7792842667966, 63.4574296446683]</t>
+  </si>
+  <si>
+    <t>[11.4722350100571, 11.0181519899429]</t>
+  </si>
+  <si>
+    <t>Verdal trafostasjon – Eidum trafostasjon</t>
+  </si>
+  <si>
+    <t>[63.4013872743893, 63.423488, 63.4571907093831]</t>
+  </si>
+  <si>
+    <t>[10.4402013779148, 10.813293, 11.0174939283141]</t>
+  </si>
+  <si>
+    <t>Eidum trafostasjon – Strinda koblingsstasjon</t>
+  </si>
+  <si>
+    <t>[63.779267150403, 63.703506, 63.409354, 63.2769667913878]</t>
+  </si>
+  <si>
+    <t>[11.4726336570695, 11.538391, 11.15387, 10.4580241866236]</t>
+  </si>
+  <si>
+    <t>Verdal trafostasjon – Klæbu transformatorstasjon</t>
+  </si>
+  <si>
+    <t>[63.2770887040084, 63.4011611611364]</t>
+  </si>
+  <si>
+    <t>[10.4575822753626, 10.4397867246374]</t>
+  </si>
+  <si>
+    <t>Strinda koblingsstasjon – Klæbu transformatorstasjon</t>
+  </si>
+  <si>
+    <t>[63.2719119610727, 63.268241, 63.23672, 63.2768450273625]</t>
+  </si>
+  <si>
+    <t>[9.93345548452976, 9.979706, 10.04837, 10.4571728802973]</t>
+  </si>
+  <si>
+    <t>Klæbu transformatorstasjon – Orkdal transformatorstasjon</t>
+  </si>
+  <si>
+    <t>[62.6799952696754, 63.021959, 63.202068, 63.2717982207385]</t>
+  </si>
+  <si>
+    <t>[8.48028947595439, 8.897552, 9.79156500000001, 9.93271247746952]</t>
+  </si>
+  <si>
+    <t>Orkdal transformatorstasjon – Aura trafostasjon</t>
+  </si>
+  <si>
+    <t>[61.8861304294624, 62.6796217603448]</t>
+  </si>
+  <si>
+    <t>[9.06357629708208, 8.48021670291793]</t>
+  </si>
+  <si>
+    <t>Aura trafostasjon – Vågåmo trafo stasjon</t>
+  </si>
+  <si>
+    <t>[63.9797705313635, 64.4536577724636]</t>
+  </si>
+  <si>
+    <t>[11.4780240828036, 11.6207309171964]</t>
+  </si>
+  <si>
+    <t>Ogndal trafostasjon – Namsos (Statnett) trafostasjon</t>
+  </si>
+  <si>
+    <t>[62.5263493502315, 62.6797261154976]</t>
+  </si>
+  <si>
+    <t>[7.79520216211446, 8.47966983788554]</t>
+  </si>
+  <si>
+    <t>Viklandet trafostasjon – Grytten trafostasjon</t>
+  </si>
+  <si>
+    <t>[63.2769332188306, 63.325632, 63.085435, 62.6800121989769]</t>
+  </si>
+  <si>
+    <t>[10.4571743955897, 9.986572, 8.751984, 8.480202620587]</t>
+  </si>
+  <si>
+    <t>Klæbu transformatorstasjon – Viklandet trafostasjon</t>
+  </si>
+  <si>
+    <t>[62.4780980928918, 62.5262309524377]</t>
+  </si>
+  <si>
+    <t>[7.03444016980177, 7.79435683019823]</t>
+  </si>
+  <si>
+    <t>Ørskog trafostasjon – Grytten trafostasjon</t>
+  </si>
+  <si>
+    <t>[63.0357063153294, 63.061804, 63.22373, 63.2768185449166]</t>
+  </si>
+  <si>
+    <t>[11.7274675384392, 11.469727, 10.778961, 10.4580312550914]</t>
+  </si>
+  <si>
+    <t>Klæbu transformatorstasjon – Nea trafostasjon</t>
+  </si>
+  <si>
+    <t>[61.73283, 61.88593]</t>
+  </si>
+  <si>
+    <t>[5.218506, 9.063721]</t>
+  </si>
+  <si>
+    <t>[61.88593, 62.62872]</t>
+  </si>
+  <si>
+    <t>[9.063721, 10.26672]</t>
+  </si>
+  <si>
+    <t>[62.628719, 63.035662]</t>
+  </si>
+  <si>
+    <t>[10.26672, 11.72791]</t>
+  </si>
+  <si>
+    <t>[63.035662, 64.453849]</t>
+  </si>
+  <si>
+    <t>[11.72791, 11.62079]</t>
+  </si>
+  <si>
+    <t>transformer_id</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Klæbu transformatorstasjon – Klæbu transformatorstasjon</t>
+  </si>
+  <si>
+    <t>Thamshavn trafostasjon – Orkdal transformatorstasjon</t>
+  </si>
+  <si>
+    <t>Ørskog trafostasjon – Ørskog trafostasjon</t>
+  </si>
+  <si>
+    <t>Aura trafostasjon – Viklandet trafostasjon</t>
+  </si>
+  <si>
+    <t>Svelgen transformatorstasjon 132/300 kV</t>
+  </si>
+  <si>
+    <t>Brattset transformatorstasjon 132/300 kV</t>
+  </si>
+  <si>
+    <t>Brattset transformatorstasjon 132/380 kV</t>
+  </si>
+  <si>
+    <t>Namsos transformatorstasjon 300/380 kV</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>area1</t>
+  </si>
+  <si>
+    <t>Pinj</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -70,13 +786,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -401,74 +1125,75 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P26"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>bus_id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>bidz</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Vbase</v>
-      </c>
-      <c r="E1" t="str">
-        <v>lat</v>
-      </c>
-      <c r="F1" t="str">
-        <v>lon</v>
-      </c>
-      <c r="G1" t="str">
-        <v xml:space="preserve">S_base [MVA] </v>
-      </c>
-      <c r="H1" t="str">
-        <v>V [P.U]</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Angle [rad]</v>
-      </c>
-      <c r="J1" t="str">
-        <v>P_gen</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Q_gen</v>
-      </c>
-      <c r="L1" t="str">
-        <v>P_load</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Q_load</v>
-      </c>
-      <c r="N1" t="str">
-        <v>S_max</v>
-      </c>
-      <c r="O1" t="str">
-        <v>V_max</v>
-      </c>
-      <c r="P1" t="str">
-        <v>V_min</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>30</v>
       </c>
-      <c r="B2" t="str">
-        <v>Vågåmo trafo stasjon</v>
-      </c>
-      <c r="C2" t="str">
-        <v>NO3</v>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
       <c r="D2">
         <v>300</v>
       </c>
       <c r="E2">
-        <v>61.88593100000001</v>
+        <v>61.885931000000006</v>
       </c>
       <c r="F2">
         <v>9.063721000000001</v>
@@ -504,24 +1229,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>45</v>
       </c>
-      <c r="B3" t="str">
-        <v>Aura trafostasjon</v>
-      </c>
-      <c r="C3" t="str">
-        <v>NO3</v>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
       <c r="D3">
         <v>300</v>
       </c>
       <c r="E3">
-        <v>62.679816</v>
+        <v>62.679816000000002</v>
       </c>
       <c r="F3">
-        <v>8.480072000000009</v>
+        <v>8.4800720000000087</v>
       </c>
       <c r="G3">
         <v>100</v>
@@ -554,21 +1279,21 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A4">
         <v>46</v>
       </c>
-      <c r="B4" t="str">
-        <v>Brattset trafostasjon</v>
-      </c>
-      <c r="C4" t="str">
-        <v>NO3</v>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
       </c>
       <c r="D4">
         <v>132</v>
       </c>
       <c r="E4">
-        <v>62.628719</v>
+        <v>62.628718999999997</v>
       </c>
       <c r="F4">
         <v>10.266724</v>
@@ -604,21 +1329,21 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A5">
         <v>60</v>
       </c>
-      <c r="B5" t="str">
-        <v>Orkdal transformatorstasjon</v>
-      </c>
-      <c r="C5" t="str">
-        <v>NO3</v>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
       </c>
       <c r="D5">
         <v>300</v>
       </c>
       <c r="E5">
-        <v>63.271947</v>
+        <v>63.271946999999997</v>
       </c>
       <c r="F5">
         <v>9.933014</v>
@@ -654,24 +1379,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>61</v>
       </c>
-      <c r="B6" t="str">
-        <v>Viklandet trafostasjon</v>
-      </c>
-      <c r="C6" t="str">
-        <v>NO3</v>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
       </c>
       <c r="D6">
         <v>380</v>
       </c>
       <c r="E6">
-        <v>62.679816</v>
+        <v>62.679816000000002</v>
       </c>
       <c r="F6">
-        <v>8.480072000000009</v>
+        <v>8.4800720000000087</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -704,24 +1429,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>62</v>
       </c>
-      <c r="B7" t="str">
-        <v>Brattset trafostasjon</v>
-      </c>
-      <c r="C7" t="str">
-        <v>NO3</v>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
       </c>
       <c r="D7">
         <v>132</v>
       </c>
       <c r="E7">
-        <v>62.681707</v>
+        <v>62.681707000000003</v>
       </c>
       <c r="F7">
-        <v>10.122528</v>
+        <v>10.122528000000001</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -754,15 +1479,15 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>76</v>
       </c>
-      <c r="B8" t="str">
-        <v>Klæbu transformatorstasjon</v>
-      </c>
-      <c r="C8" t="str">
-        <v>NO3</v>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
       </c>
       <c r="D8">
         <v>300</v>
@@ -783,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K8">
         <v>12.5</v>
@@ -804,21 +1529,21 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>77</v>
       </c>
-      <c r="B9" t="str">
-        <v>Thamshavn trafostasjon</v>
-      </c>
-      <c r="C9" t="str">
-        <v>NO3</v>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
       </c>
       <c r="D9">
         <v>132</v>
       </c>
       <c r="E9">
-        <v>63.271947</v>
+        <v>63.271946999999997</v>
       </c>
       <c r="F9">
         <v>9.933014</v>
@@ -854,15 +1579,15 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>78</v>
       </c>
-      <c r="B10" t="str">
-        <v>Klæbu transformatorstasjon</v>
-      </c>
-      <c r="C10" t="str">
-        <v>NO3</v>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
       </c>
       <c r="D10">
         <v>380</v>
@@ -904,24 +1629,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A11">
         <v>79</v>
       </c>
-      <c r="B11" t="str">
-        <v>Grytten trafostasjon</v>
-      </c>
-      <c r="C11" t="str">
-        <v>NO3</v>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
       </c>
       <c r="D11">
         <v>380</v>
       </c>
       <c r="E11">
-        <v>62.526259</v>
+        <v>62.526259000000003</v>
       </c>
       <c r="F11">
-        <v>7.7948</v>
+        <v>7.7948000000000004</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -954,24 +1679,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>80</v>
       </c>
-      <c r="B12" t="str">
-        <v>Brattset trafostasjon</v>
-      </c>
-      <c r="C12" t="str">
-        <v>NO3</v>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
       </c>
       <c r="D12">
         <v>132</v>
       </c>
       <c r="E12">
-        <v>62.76478299999999</v>
+        <v>62.764782999999987</v>
       </c>
       <c r="F12">
-        <v>9.93026700000001</v>
+        <v>9.9302670000000095</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -983,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="K12">
         <v>50</v>
@@ -1004,24 +1729,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A13">
         <v>105</v>
       </c>
-      <c r="B13" t="str">
-        <v>Verdal trafostasjon</v>
-      </c>
-      <c r="C13" t="str">
-        <v>NO3</v>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
       </c>
       <c r="D13">
         <v>300</v>
       </c>
       <c r="E13">
-        <v>63.779452</v>
+        <v>63.779451999999999</v>
       </c>
       <c r="F13">
-        <v>11.472473</v>
+        <v>11.472473000000001</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -1033,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="K13">
         <v>125</v>
@@ -1054,24 +1779,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A14">
         <v>106</v>
       </c>
-      <c r="B14" t="str">
-        <v>Strinda koblingsstasjon</v>
-      </c>
-      <c r="C14" t="str">
-        <v>NO3</v>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
       </c>
       <c r="D14">
         <v>300</v>
       </c>
       <c r="E14">
-        <v>63.401361</v>
+        <v>63.401361000000001</v>
       </c>
       <c r="F14">
-        <v>10.439758</v>
+        <v>10.439757999999999</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -1104,24 +1829,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A15">
         <v>107</v>
       </c>
-      <c r="B15" t="str">
-        <v>Grana koblingsstasjon</v>
-      </c>
-      <c r="C15" t="str">
-        <v>NO3</v>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
       </c>
       <c r="D15">
         <v>132</v>
       </c>
       <c r="E15">
-        <v>63.058071</v>
+        <v>63.058070999999998</v>
       </c>
       <c r="F15">
-        <v>9.602051</v>
+        <v>9.6020509999999994</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -1154,21 +1879,21 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>108</v>
       </c>
-      <c r="B16" t="str">
-        <v>Nea trafostasjon</v>
-      </c>
-      <c r="C16" t="str">
-        <v>NO3</v>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
       </c>
       <c r="D16">
         <v>380</v>
       </c>
       <c r="E16">
-        <v>63.035662</v>
+        <v>63.035662000000002</v>
       </c>
       <c r="F16">
         <v>11.727905</v>
@@ -1192,7 +1917,7 @@
         <v>70</v>
       </c>
       <c r="M16">
-        <v>400</v>
+        <v>23.5</v>
       </c>
       <c r="N16">
         <v>1200</v>
@@ -1204,24 +1929,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A17">
         <v>109</v>
       </c>
-      <c r="B17" t="str">
-        <v>Ørskog trafostasjon</v>
-      </c>
-      <c r="C17" t="str">
-        <v>NO3</v>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
       </c>
       <c r="D17">
         <v>380</v>
       </c>
       <c r="E17">
-        <v>62.47807</v>
+        <v>62.478070000000002</v>
       </c>
       <c r="F17">
-        <v>7.033997</v>
+        <v>7.0339970000000003</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -1233,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K17">
         <v>12.5</v>
@@ -1254,21 +1979,21 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A18">
         <v>138</v>
       </c>
-      <c r="B18" t="str">
-        <v>Ogndal trafostasjon</v>
-      </c>
-      <c r="C18" t="str">
-        <v>NO3</v>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
       </c>
       <c r="D18">
         <v>300</v>
       </c>
       <c r="E18">
-        <v>63.979576</v>
+        <v>63.979576000000002</v>
       </c>
       <c r="F18">
         <v>11.477966</v>
@@ -1283,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K18">
         <v>25</v>
@@ -1304,24 +2029,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A19">
         <v>139</v>
       </c>
-      <c r="B19" t="str">
-        <v>Eidum trafostasjon</v>
-      </c>
-      <c r="C19" t="str">
-        <v>NO3</v>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
       </c>
       <c r="D19">
         <v>300</v>
       </c>
       <c r="E19">
-        <v>63.45726</v>
+        <v>63.457259999999998</v>
       </c>
       <c r="F19">
-        <v>11.017914</v>
+        <v>11.017913999999999</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -1354,24 +2079,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A20">
         <v>141</v>
       </c>
-      <c r="B20" t="str">
-        <v>Ørskog trafostasjon</v>
-      </c>
-      <c r="C20" t="str">
-        <v>NO3</v>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
       </c>
       <c r="D20">
         <v>132</v>
       </c>
       <c r="E20">
-        <v>62.47807</v>
+        <v>62.478070000000002</v>
       </c>
       <c r="F20">
-        <v>7.033997</v>
+        <v>7.0339970000000003</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -1404,24 +2129,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A21">
         <v>161</v>
       </c>
-      <c r="B21" t="str">
-        <v>Svelgen trafostasjon</v>
-      </c>
-      <c r="C21" t="str">
-        <v>NO3</v>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
       </c>
       <c r="D21">
         <v>132</v>
       </c>
       <c r="E21">
-        <v>61.732826</v>
+        <v>61.732826000000003</v>
       </c>
       <c r="F21">
-        <v>5.218506</v>
+        <v>5.2185059999999996</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -1454,21 +2179,21 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A22">
         <v>176</v>
       </c>
-      <c r="B22" t="str">
-        <v>Namsos (Statnett) trafostasjon</v>
-      </c>
-      <c r="C22" t="str">
-        <v>NO3</v>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
       </c>
       <c r="D22">
         <v>300</v>
       </c>
       <c r="E22">
-        <v>64.453849</v>
+        <v>64.453849000000005</v>
       </c>
       <c r="F22">
         <v>11.620789</v>
@@ -1504,15 +2229,15 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A23">
         <v>177</v>
       </c>
-      <c r="B23" t="str">
-        <v>Svelgen 300 kV</v>
-      </c>
-      <c r="C23" t="str">
-        <v>NO3</v>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
       </c>
       <c r="D23">
         <v>300</v>
@@ -1521,7 +2246,7 @@
         <v>61.73283</v>
       </c>
       <c r="F23">
-        <v>5.218506</v>
+        <v>5.2185059999999996</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -1554,24 +2279,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A24">
         <v>178</v>
       </c>
-      <c r="B24" t="str">
-        <v>Brattset trafostasjon</v>
-      </c>
-      <c r="C24" t="str">
-        <v>NO3</v>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
       </c>
       <c r="D24">
         <v>300</v>
       </c>
       <c r="E24">
-        <v>62.628719</v>
+        <v>62.628718999999997</v>
       </c>
       <c r="F24">
-        <v>10.26672</v>
+        <v>10.266719999999999</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -1604,24 +2329,24 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A25">
         <v>179</v>
       </c>
-      <c r="B25" t="str">
-        <v>Brattset 380 kV</v>
-      </c>
-      <c r="C25" t="str">
-        <v>NO3</v>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
       </c>
       <c r="D25">
         <v>380</v>
       </c>
       <c r="E25">
-        <v>62.628719</v>
+        <v>62.628718999999997</v>
       </c>
       <c r="F25">
-        <v>10.26672</v>
+        <v>10.266719999999999</v>
       </c>
       <c r="G25">
         <v>100</v>
@@ -1654,21 +2379,21 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.6">
       <c r="A26">
         <v>180</v>
       </c>
-      <c r="B26" t="str">
-        <v>Namsos 380 kV</v>
-      </c>
-      <c r="C26" t="str">
-        <v>NO3</v>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
       </c>
       <c r="D26">
         <v>380</v>
       </c>
       <c r="E26">
-        <v>64.453849</v>
+        <v>64.453849000000005</v>
       </c>
       <c r="F26">
         <v>11.62079</v>
@@ -1705,54 +2430,56 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P26"/>
+    <ignoredError sqref="A1:P7 A9:P11 A8:I8 K8:P8 A14:P15 A12:I12 K12:P12 A13:I13 K13:P13 A19:P26 A17:I17 K17:P17 A18:I18 K18:P18 A16:L16 N16:P16" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I105"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>type2</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Pmax</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Qmax</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Qmin</v>
-      </c>
-      <c r="G1" t="str">
-        <v>bus</v>
-      </c>
-      <c r="H1" t="str">
-        <v>lat</v>
-      </c>
-      <c r="I1" t="str">
-        <v>lon</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Grytten</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Reservoir</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
       </c>
       <c r="D2">
         <v>143</v>
@@ -1767,21 +2494,21 @@
         <v>45</v>
       </c>
       <c r="H2">
-        <v>62.492536</v>
+        <v>62.492536000000001</v>
       </c>
       <c r="I2">
-        <v>8.804476</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Tevla</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Pumped Storage</v>
+        <v>8.8044759999999993</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
       </c>
       <c r="D3">
         <v>60</v>
@@ -1796,21 +2523,21 @@
         <v>108</v>
       </c>
       <c r="H3">
-        <v>63.38513759999999</v>
+        <v>63.385137599999993</v>
       </c>
       <c r="I3">
-        <v>11.8719306</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Svelgfoss</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Run-Of-River</v>
+        <v>11.871930600000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
       </c>
       <c r="D4">
         <v>251</v>
@@ -1825,21 +2552,21 @@
         <v>161</v>
       </c>
       <c r="H4">
-        <v>61.7685236</v>
+        <v>61.768523600000002</v>
       </c>
       <c r="I4">
-        <v>5.2955096</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Driva</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Run-Of-River</v>
+        <v>5.2955095999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
       </c>
       <c r="D5">
         <v>160</v>
@@ -1854,21 +2581,21 @@
         <v>45</v>
       </c>
       <c r="H5">
-        <v>62.59448809999999</v>
+        <v>62.594488099999992</v>
       </c>
       <c r="I5">
-        <v>8.886649400000003</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Brattset</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Run-Of-River</v>
+        <v>8.8866494000000031</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
       </c>
       <c r="D6">
         <v>92</v>
@@ -1883,21 +2610,21 @@
         <v>80</v>
       </c>
       <c r="H6">
-        <v>62.802274</v>
+        <v>62.802273999999997</v>
       </c>
       <c r="I6">
         <v>10.0126685</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Brattingfoss</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Pumped Storage</v>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
       </c>
       <c r="D7">
         <v>14</v>
@@ -1912,21 +2639,21 @@
         <v>138</v>
       </c>
       <c r="H7">
-        <v>64.043305</v>
+        <v>64.043305000000004</v>
       </c>
       <c r="I7">
         <v>11.08352</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Bratsberg</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Run-Of-River</v>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
       </c>
       <c r="D8">
         <v>140</v>
@@ -1941,27 +2668,27 @@
         <v>106</v>
       </c>
       <c r="H8">
-        <v>63.3493642</v>
+        <v>63.349364199999997</v>
       </c>
       <c r="I8">
-        <v>10.4819594</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Askara</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Run-Of-River</v>
+        <v>10.481959399999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
       </c>
       <c r="D9">
-        <v>157.3</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="E9">
-        <v>157.3</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1970,21 +2697,21 @@
         <v>161</v>
       </c>
       <c r="H9">
-        <v>61.78333329999999</v>
+        <v>61.783333299999988</v>
       </c>
       <c r="I9">
-        <v>5.6666667</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Nea</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Reservoir</v>
+        <v>5.6666667000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
       </c>
       <c r="D10">
         <v>259.8</v>
@@ -1999,21 +2726,21 @@
         <v>108</v>
       </c>
       <c r="H10">
-        <v>63.1617916</v>
+        <v>63.161791600000001</v>
       </c>
       <c r="I10">
         <v>11.1900113</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Mosvik</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Run-Of-River</v>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
       </c>
       <c r="D11">
         <v>46</v>
@@ -2034,15 +2761,15 @@
         <v>11.0058121</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Ovre fiskumfoss</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Run-Of-River</v>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -2063,15 +2790,15 @@
         <v>12.458487</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Harpefossen</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Reservoir</v>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -2086,21 +2813,21 @@
         <v>161</v>
       </c>
       <c r="H13">
-        <v>61.9579615</v>
+        <v>61.957961500000003</v>
       </c>
       <c r="I13">
-        <v>5.9323598</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Knutfoss</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Hydro</v>
+        <v>5.9323598000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
       </c>
       <c r="D14">
         <v>5.4</v>
@@ -2115,21 +2842,21 @@
         <v>176</v>
       </c>
       <c r="H14">
-        <v>64.5228</v>
+        <v>64.522800000000004</v>
       </c>
       <c r="I14">
-        <v>12.4264</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Oyberget</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Hydro</v>
+        <v>12.426399999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
       </c>
       <c r="D15">
         <v>109</v>
@@ -2144,21 +2871,21 @@
         <v>30</v>
       </c>
       <c r="H15">
-        <v>61.9342</v>
+        <v>61.934199999999997</v>
       </c>
       <c r="I15">
-        <v>8.0307</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Rka nyhamna</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Thermal</v>
-      </c>
-      <c r="C16" t="str">
-        <v>OCGT</v>
+        <v>8.0306999999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
       </c>
       <c r="D16">
         <v>253.2</v>
@@ -2176,18 +2903,18 @@
         <v>62.8489</v>
       </c>
       <c r="I16">
-        <v>6.9433</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Midtre tessa</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Hydro</v>
+        <v>6.9432999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -2202,21 +2929,21 @@
         <v>30</v>
       </c>
       <c r="H17">
-        <v>61.846</v>
+        <v>61.845999999999997</v>
       </c>
       <c r="I17">
-        <v>8.9611</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Trolheim</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Hydro</v>
+        <v>8.9611000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
       </c>
       <c r="D18">
         <v>169.2</v>
@@ -2231,21 +2958,21 @@
         <v>106</v>
       </c>
       <c r="H18">
-        <v>63.4305149</v>
+        <v>63.430514899999999</v>
       </c>
       <c r="I18">
         <v>10.3950528</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Grana</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Hydro</v>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
       </c>
       <c r="D19">
         <v>90</v>
@@ -2263,18 +2990,18 @@
         <v>62.8776461</v>
       </c>
       <c r="I19">
-        <v>9.715195199999998</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Gresslifoss</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Hydro</v>
+        <v>9.7151951999999984</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
       </c>
       <c r="D20">
         <v>26</v>
@@ -2289,27 +3016,27 @@
         <v>108</v>
       </c>
       <c r="H20">
-        <v>63.0577</v>
+        <v>63.057699999999997</v>
       </c>
       <c r="I20">
-        <v>11.4394</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Hegsetfoss</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Hydro</v>
+        <v>11.439399999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
       </c>
       <c r="D21">
-        <v>40.3</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="E21">
-        <v>40.3</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2318,21 +3045,21 @@
         <v>108</v>
       </c>
       <c r="H21">
-        <v>63.1653</v>
+        <v>63.165300000000002</v>
       </c>
       <c r="I21">
-        <v>11.2307</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Istad</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Hydro</v>
+        <v>11.230700000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -2347,21 +3074,21 @@
         <v>141</v>
       </c>
       <c r="H22">
-        <v>62.74637</v>
+        <v>62.746369999999999</v>
       </c>
       <c r="I22">
         <v>7.2199947</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Gjerdsvik</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Hydro</v>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
       </c>
       <c r="D23">
         <v>6.2</v>
@@ -2376,21 +3103,21 @@
         <v>161</v>
       </c>
       <c r="H23">
-        <v>62.26424599999999</v>
+        <v>62.264245999999993</v>
       </c>
       <c r="I23">
-        <v>5.580342</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Eidefossen</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Hydro</v>
+        <v>5.5803419999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
       </c>
       <c r="D24">
         <v>14</v>
@@ -2408,18 +3135,18 @@
         <v>61.80454379999999</v>
       </c>
       <c r="I24">
-        <v>9.3017814</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Fausa</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Hydro</v>
+        <v>9.3017813999999994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -2434,21 +3161,21 @@
         <v>141</v>
       </c>
       <c r="H25">
-        <v>62.3575</v>
+        <v>62.357500000000002</v>
       </c>
       <c r="I25">
         <v>6.8948</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Follafoss</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Hydro</v>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
       </c>
       <c r="D26">
         <v>48.5</v>
@@ -2463,21 +3190,21 @@
         <v>138</v>
       </c>
       <c r="H26">
-        <v>63.98555750000001</v>
+        <v>63.985557500000013</v>
       </c>
       <c r="I26">
         <v>11.1072278</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Framruste</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C27" t="str">
-        <v>Hydro</v>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>44</v>
       </c>
       <c r="D27">
         <v>85</v>
@@ -2492,21 +3219,21 @@
         <v>79</v>
       </c>
       <c r="H27">
-        <v>61.9600094</v>
+        <v>61.960009399999997</v>
       </c>
       <c r="I27">
-        <v>7.851177000000003</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Furset</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Hydro</v>
+        <v>7.8511770000000034</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
       </c>
       <c r="D28">
         <v>5.4</v>
@@ -2521,21 +3248,21 @@
         <v>141</v>
       </c>
       <c r="H28">
-        <v>62.2828</v>
+        <v>62.282800000000002</v>
       </c>
       <c r="I28">
-        <v>6.8848</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Norddalen</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Reservoir</v>
+        <v>6.8848000000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -2550,21 +3277,21 @@
         <v>141</v>
       </c>
       <c r="H29">
-        <v>62.2997684</v>
+        <v>62.299768399999998</v>
       </c>
       <c r="I29">
-        <v>7.254570999999999</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Vessingfoss</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Hydro</v>
+        <v>7.2545709999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
       </c>
       <c r="D30">
         <v>45</v>
@@ -2579,21 +3306,21 @@
         <v>108</v>
       </c>
       <c r="H30">
-        <v>62.9957</v>
+        <v>62.995699999999999</v>
       </c>
       <c r="I30">
         <v>11.8285</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Svorkmo</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Hydro</v>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
       </c>
       <c r="D31">
         <v>86</v>
@@ -2608,21 +3335,21 @@
         <v>107</v>
       </c>
       <c r="H31">
-        <v>63.16366485</v>
+        <v>63.163664850000004</v>
       </c>
       <c r="I31">
-        <v>9.75744035</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Tussa</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Hydro</v>
+        <v>9.7574403499999995</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A32" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" t="s">
+        <v>44</v>
       </c>
       <c r="D32">
         <v>64</v>
@@ -2637,21 +3364,21 @@
         <v>141</v>
       </c>
       <c r="H32">
-        <v>62.17864530000001</v>
+        <v>62.178645300000007</v>
       </c>
       <c r="I32">
-        <v>6.083348200000001</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Tafjord</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Run-Of-River</v>
+        <v>6.0833482000000014</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
       </c>
       <c r="D33">
         <v>319.2</v>
@@ -2666,21 +3393,21 @@
         <v>141</v>
       </c>
       <c r="H33">
-        <v>62.23115129999998</v>
+        <v>62.231151299999979</v>
       </c>
       <c r="I33">
-        <v>7.415328700000002</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Fjaremsfossen</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C34" t="str">
-        <v>Run-Of-River</v>
+        <v>7.4153287000000017</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A34" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
       </c>
       <c r="D34">
         <v>23</v>
@@ -2695,21 +3422,21 @@
         <v>76</v>
       </c>
       <c r="H34">
-        <v>63.32211</v>
+        <v>63.322110000000002</v>
       </c>
       <c r="I34">
-        <v>10.43658</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Bogna</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Hydro</v>
+        <v>10.436579999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
       </c>
       <c r="D35">
         <v>60</v>
@@ -2724,21 +3451,21 @@
         <v>176</v>
       </c>
       <c r="H35">
-        <v>64.2215</v>
+        <v>64.221500000000006</v>
       </c>
       <c r="I35">
-        <v>12.0369</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Aunfoss</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C36" t="str">
-        <v>Hydro</v>
+        <v>12.036899999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" t="s">
+        <v>44</v>
       </c>
       <c r="D36">
         <v>36</v>
@@ -2756,18 +3483,18 @@
         <v>64.31045300000001</v>
       </c>
       <c r="I36">
-        <v>11.5208419</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Fossan</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C37" t="str">
-        <v>Hydro</v>
+        <v>11.520841900000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A37" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" t="s">
+        <v>44</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -2782,21 +3509,21 @@
         <v>108</v>
       </c>
       <c r="H37">
-        <v>63.0273</v>
+        <v>63.027299999999997</v>
       </c>
       <c r="I37">
         <v>11.6968</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Nedrenea</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C38" t="str">
-        <v>Hydro</v>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A38" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s">
+        <v>44</v>
       </c>
       <c r="D38">
         <v>70</v>
@@ -2811,21 +3538,21 @@
         <v>108</v>
       </c>
       <c r="H38">
-        <v>63.1517</v>
+        <v>63.151699999999998</v>
       </c>
       <c r="I38">
-        <v>11.2396</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Litledalen</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Hydro</v>
+        <v>11.239599999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" t="s">
+        <v>44</v>
       </c>
       <c r="D39">
         <v>19.5</v>
@@ -2843,18 +3570,18 @@
         <v>62.6666667</v>
       </c>
       <c r="I39">
-        <v>7.533333299999999</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>Kvitfossen</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C40" t="str">
-        <v>Hydro</v>
+        <v>7.5333332999999989</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A40" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" t="s">
+        <v>44</v>
       </c>
       <c r="D40">
         <v>7.8</v>
@@ -2869,21 +3596,21 @@
         <v>30</v>
       </c>
       <c r="H40">
-        <v>62.21024269999999</v>
+        <v>62.210242699999988</v>
       </c>
       <c r="I40">
-        <v>8.933041699999997</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>Kanstadbotn</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Hydro</v>
+        <v>8.9330416999999969</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A41" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" t="s">
+        <v>44</v>
       </c>
       <c r="D41">
         <v>5.8</v>
@@ -2898,21 +3625,21 @@
         <v>45</v>
       </c>
       <c r="H41">
-        <v>62.676</v>
+        <v>62.676000000000002</v>
       </c>
       <c r="I41">
         <v>8.157</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Julskaret</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C42" t="str">
-        <v>Hydro</v>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A42" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" t="s">
+        <v>44</v>
       </c>
       <c r="D42">
         <v>8</v>
@@ -2927,21 +3654,21 @@
         <v>76</v>
       </c>
       <c r="H42">
-        <v>63.1403</v>
+        <v>63.140300000000003</v>
       </c>
       <c r="I42">
         <v>10.9664</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Innvik</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Hydro</v>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A43" t="s">
+        <v>90</v>
+      </c>
+      <c r="B43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" t="s">
+        <v>44</v>
       </c>
       <c r="D43">
         <v>17</v>
@@ -2956,21 +3683,21 @@
         <v>109</v>
       </c>
       <c r="H43">
-        <v>61.8517407</v>
+        <v>61.851740700000001</v>
       </c>
       <c r="I43">
-        <v>6.6169455</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Byrkjelo</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C44" t="str">
-        <v>Hydro</v>
+        <v>6.6169454999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
       </c>
       <c r="D44">
         <v>25.2</v>
@@ -2985,27 +3712,27 @@
         <v>161</v>
       </c>
       <c r="H44">
-        <v>61.733299</v>
+        <v>61.733299000000002</v>
       </c>
       <c r="I44">
-        <v>6.5069117</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Byafossen</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Hydro</v>
+        <v>6.5069116999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A45" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" t="s">
+        <v>44</v>
       </c>
       <c r="D45">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E45">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -3014,21 +3741,21 @@
         <v>138</v>
       </c>
       <c r="H45">
-        <v>64.0319904</v>
+        <v>64.031990399999998</v>
       </c>
       <c r="I45">
         <v>11.5484121</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Brunstad</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Hydro</v>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" t="s">
+        <v>44</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -3043,21 +3770,21 @@
         <v>141</v>
       </c>
       <c r="H46">
-        <v>62.3816339</v>
+        <v>62.381633899999997</v>
       </c>
       <c r="I46">
-        <v>6.5741103</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Brekkefoss</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C47" t="str">
-        <v>Hydro</v>
+        <v>6.5741103000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A47" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" t="s">
+        <v>44</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -3072,21 +3799,21 @@
         <v>161</v>
       </c>
       <c r="H47">
-        <v>61.72315379999999</v>
+        <v>61.723153799999992</v>
       </c>
       <c r="I47">
-        <v>5.837689399999999</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Asen</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C48" t="str">
-        <v>Hydro</v>
+        <v>5.8376893999999986</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A48" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" t="s">
+        <v>44</v>
       </c>
       <c r="D48">
         <v>10.4</v>
@@ -3101,21 +3828,21 @@
         <v>139</v>
       </c>
       <c r="H48">
-        <v>63.6082353</v>
+        <v>63.608235299999997</v>
       </c>
       <c r="I48">
-        <v>11.0517689</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Eiriksdal</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C49" t="str">
-        <v>Hydro</v>
+        <v>11.051768900000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" t="s">
+        <v>44</v>
       </c>
       <c r="D49">
         <v>100</v>
@@ -3130,21 +3857,21 @@
         <v>79</v>
       </c>
       <c r="H49">
-        <v>62.4761474</v>
+        <v>62.476147400000002</v>
       </c>
       <c r="I49">
-        <v>8.1743356</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Funna</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C50" t="str">
-        <v>Hydro</v>
+        <v>8.1743355999999991</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50" t="s">
+        <v>44</v>
       </c>
       <c r="D50">
         <v>21.7</v>
@@ -3159,21 +3886,21 @@
         <v>139</v>
       </c>
       <c r="H50">
-        <v>63.4515598</v>
+        <v>63.451559799999998</v>
       </c>
       <c r="I50">
-        <v>11.7632609</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Hopselva</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C51" t="str">
-        <v>Hydro</v>
+        <v>11.763260900000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A51" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51" t="s">
+        <v>44</v>
       </c>
       <c r="D51">
         <v>5.2</v>
@@ -3188,21 +3915,21 @@
         <v>161</v>
       </c>
       <c r="H51">
-        <v>61.714849</v>
+        <v>61.714849000000001</v>
       </c>
       <c r="I51">
-        <v>5.823575099999999</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Giskemo</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C52" t="str">
-        <v>Hydro</v>
+        <v>5.8235750999999993</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" t="s">
+        <v>44</v>
       </c>
       <c r="D52">
         <v>5.4</v>
@@ -3217,21 +3944,21 @@
         <v>141</v>
       </c>
       <c r="H52">
-        <v>62.48135749999999</v>
+        <v>62.481357499999987</v>
       </c>
       <c r="I52">
         <v>6.8139132</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Fossheim</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C53" t="str">
-        <v>Hydro</v>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" t="s">
+        <v>44</v>
+      </c>
+      <c r="C53" t="s">
+        <v>44</v>
       </c>
       <c r="D53">
         <v>9</v>
@@ -3246,21 +3973,21 @@
         <v>30</v>
       </c>
       <c r="H53">
-        <v>61.83838539999999</v>
+        <v>61.838385399999993</v>
       </c>
       <c r="I53">
-        <v>8.5725325</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>Embla</v>
-      </c>
-      <c r="B54" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C54" t="str">
-        <v>Hydro</v>
+        <v>8.5725324999999994</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A54" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" t="s">
+        <v>44</v>
       </c>
       <c r="D54">
         <v>5.5</v>
@@ -3275,21 +4002,21 @@
         <v>141</v>
       </c>
       <c r="H54">
-        <v>62.2171</v>
+        <v>62.217100000000002</v>
       </c>
       <c r="I54">
-        <v>6.9098</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>Eid</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C55" t="str">
-        <v>Hydro</v>
+        <v>6.9097999999999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A55" t="s">
+        <v>102</v>
+      </c>
+      <c r="B55" t="s">
+        <v>44</v>
+      </c>
+      <c r="C55" t="s">
+        <v>44</v>
       </c>
       <c r="D55">
         <v>10.6</v>
@@ -3304,21 +4031,21 @@
         <v>161</v>
       </c>
       <c r="H55">
-        <v>61.9206441</v>
+        <v>61.920644099999997</v>
       </c>
       <c r="I55">
-        <v>6.0118765</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>Lokaunet</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C56" t="str">
-        <v>Hydro</v>
+        <v>6.0118764999999996</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A56" t="s">
+        <v>103</v>
+      </c>
+      <c r="B56" t="s">
+        <v>44</v>
+      </c>
+      <c r="C56" t="s">
+        <v>44</v>
       </c>
       <c r="D56">
         <v>11.5</v>
@@ -3333,21 +4060,21 @@
         <v>76</v>
       </c>
       <c r="H56">
-        <v>63.26819279999999</v>
+        <v>63.268192799999987</v>
       </c>
       <c r="I56">
         <v>10.4582701</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>Amela</v>
-      </c>
-      <c r="B57" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C57" t="str">
-        <v>Hydro</v>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A57" t="s">
+        <v>104</v>
+      </c>
+      <c r="B57" t="s">
+        <v>44</v>
+      </c>
+      <c r="C57" t="s">
+        <v>44</v>
       </c>
       <c r="D57">
         <v>40</v>
@@ -3362,21 +4089,21 @@
         <v>161</v>
       </c>
       <c r="H57">
-        <v>62.0091257</v>
+        <v>62.009125699999998</v>
       </c>
       <c r="I57">
-        <v>5.8372718</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>Skjak</v>
-      </c>
-      <c r="B58" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C58" t="str">
-        <v>Hydro</v>
+        <v>5.8372717999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A58" t="s">
+        <v>105</v>
+      </c>
+      <c r="B58" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58" t="s">
+        <v>44</v>
       </c>
       <c r="D58">
         <v>35</v>
@@ -3391,21 +4118,21 @@
         <v>79</v>
       </c>
       <c r="H58">
-        <v>61.9467976</v>
+        <v>61.946797599999996</v>
       </c>
       <c r="I58">
         <v>7.828136999999999</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Skogheim</v>
-      </c>
-      <c r="B59" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C59" t="str">
-        <v>Hydro</v>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A59" t="s">
+        <v>106</v>
+      </c>
+      <c r="B59" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" t="s">
+        <v>44</v>
       </c>
       <c r="D59">
         <v>9</v>
@@ -3420,21 +4147,21 @@
         <v>161</v>
       </c>
       <c r="H59">
-        <v>61.8166667</v>
+        <v>61.816666699999999</v>
       </c>
       <c r="I59">
         <v>6.15</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>Usma selbu</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Hydro</v>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A60" t="s">
+        <v>107</v>
+      </c>
+      <c r="B60" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60" t="s">
+        <v>44</v>
       </c>
       <c r="D60">
         <v>16.3</v>
@@ -3449,21 +4176,21 @@
         <v>139</v>
       </c>
       <c r="H60">
-        <v>63.21924539999999</v>
+        <v>63.219245399999991</v>
       </c>
       <c r="I60">
         <v>11.04129</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>Soa</v>
-      </c>
-      <c r="B61" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Hydro</v>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A61" t="s">
+        <v>108</v>
+      </c>
+      <c r="B61" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61" t="s">
+        <v>44</v>
       </c>
       <c r="D61">
         <v>45</v>
@@ -3478,21 +4205,21 @@
         <v>107</v>
       </c>
       <c r="H61">
-        <v>63.29057</v>
+        <v>63.290570000000002</v>
       </c>
       <c r="I61">
-        <v>9.089089999999999</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Sorbrandal</v>
-      </c>
-      <c r="B62" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Hydro</v>
+        <v>9.0890899999999988</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A62" t="s">
+        <v>109</v>
+      </c>
+      <c r="B62" t="s">
+        <v>44</v>
+      </c>
+      <c r="C62" t="s">
+        <v>44</v>
       </c>
       <c r="D62">
         <v>8</v>
@@ -3507,27 +4234,27 @@
         <v>161</v>
       </c>
       <c r="H62">
-        <v>62.16746260000001</v>
+        <v>62.167462600000007</v>
       </c>
       <c r="I62">
-        <v>5.560866099999997</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>Stadheim</v>
-      </c>
-      <c r="B63" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C63" t="str">
-        <v>Hydro</v>
+        <v>5.5608660999999966</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A63" t="s">
+        <v>110</v>
+      </c>
+      <c r="B63" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" t="s">
+        <v>44</v>
       </c>
       <c r="D63">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E63">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3536,21 +4263,21 @@
         <v>141</v>
       </c>
       <c r="H63">
-        <v>62.30964</v>
+        <v>62.309640000000002</v>
       </c>
       <c r="I63">
-        <v>6.93582</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>Steinsvik</v>
-      </c>
-      <c r="B64" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C64" t="str">
-        <v>Hydro</v>
+        <v>6.9358199999999997</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A64" t="s">
+        <v>111</v>
+      </c>
+      <c r="B64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C64" t="s">
+        <v>44</v>
       </c>
       <c r="D64">
         <v>10</v>
@@ -3565,21 +4292,21 @@
         <v>161</v>
       </c>
       <c r="H64">
-        <v>62.0046615</v>
+        <v>62.004661499999997</v>
       </c>
       <c r="I64">
-        <v>5.8543174</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>Stordal</v>
-      </c>
-      <c r="B65" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C65" t="str">
-        <v>Hydro</v>
+        <v>5.8543174000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A65" t="s">
+        <v>112</v>
+      </c>
+      <c r="B65" t="s">
+        <v>44</v>
+      </c>
+      <c r="C65" t="s">
+        <v>44</v>
       </c>
       <c r="D65">
         <v>36.6</v>
@@ -3594,21 +4321,21 @@
         <v>141</v>
       </c>
       <c r="H65">
-        <v>62.38181789999999</v>
+        <v>62.381817899999987</v>
       </c>
       <c r="I65">
-        <v>6.992054700000002</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>Skulafossen</v>
-      </c>
-      <c r="B66" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C66" t="str">
-        <v>Hydro</v>
+        <v>6.9920547000000024</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B66" t="s">
+        <v>44</v>
+      </c>
+      <c r="C66" t="s">
+        <v>44</v>
       </c>
       <c r="D66">
         <v>5</v>
@@ -3623,21 +4350,21 @@
         <v>77</v>
       </c>
       <c r="H66">
-        <v>63.2666667</v>
+        <v>63.266666700000002</v>
       </c>
       <c r="I66">
-        <v>9.833333300000001</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>Trysilfossen</v>
-      </c>
-      <c r="B67" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C67" t="str">
-        <v>Hydro</v>
+        <v>9.8333333000000014</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A67" t="s">
+        <v>114</v>
+      </c>
+      <c r="B67" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" t="s">
+        <v>44</v>
       </c>
       <c r="D67">
         <v>3.7</v>
@@ -3655,18 +4382,18 @@
         <v>61.74977719999999</v>
       </c>
       <c r="I67">
-        <v>6.276685100000001</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Urke</v>
-      </c>
-      <c r="B68" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C68" t="str">
-        <v>Hydro</v>
+        <v>6.2766851000000008</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A68" t="s">
+        <v>115</v>
+      </c>
+      <c r="B68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C68" t="s">
+        <v>44</v>
       </c>
       <c r="D68">
         <v>5.7</v>
@@ -3681,21 +4408,21 @@
         <v>141</v>
       </c>
       <c r="H68">
-        <v>62.21287539999999</v>
+        <v>62.212875399999987</v>
       </c>
       <c r="I68">
-        <v>6.5668393</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>Trandal</v>
-      </c>
-      <c r="B69" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Hydro</v>
+        <v>6.5668392999999998</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A69" t="s">
+        <v>116</v>
+      </c>
+      <c r="B69" t="s">
+        <v>44</v>
+      </c>
+      <c r="C69" t="s">
+        <v>44</v>
       </c>
       <c r="D69">
         <v>5.6</v>
@@ -3710,21 +4437,21 @@
         <v>141</v>
       </c>
       <c r="H69">
-        <v>62.2608457</v>
+        <v>62.260845699999997</v>
       </c>
       <c r="I69">
-        <v>6.500545799999999</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Sykkylven</v>
-      </c>
-      <c r="B70" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C70" t="str">
-        <v>Hydro</v>
+        <v>6.5005457999999994</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A70" t="s">
+        <v>117</v>
+      </c>
+      <c r="B70" t="s">
+        <v>44</v>
+      </c>
+      <c r="C70" t="s">
+        <v>44</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -3739,21 +4466,21 @@
         <v>141</v>
       </c>
       <c r="H70">
-        <v>62.3919003</v>
+        <v>62.391900300000003</v>
       </c>
       <c r="I70">
-        <v>6.598008900000001</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Vassli</v>
-      </c>
-      <c r="B71" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C71" t="str">
-        <v>Hydro</v>
+        <v>6.5980089000000008</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A71" t="s">
+        <v>118</v>
+      </c>
+      <c r="B71" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" t="s">
+        <v>44</v>
       </c>
       <c r="D71">
         <v>12</v>
@@ -3768,21 +4495,21 @@
         <v>77</v>
       </c>
       <c r="H71">
-        <v>63.21666670000001</v>
+        <v>63.216666700000012</v>
       </c>
       <c r="I71">
-        <v>9.633333300000002</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Tjeldbergodden</v>
-      </c>
-      <c r="B72" t="str">
-        <v>Thermal</v>
-      </c>
-      <c r="C72" t="str">
-        <v>OCGT</v>
+        <v>9.6333333000000021</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A72" t="s">
+        <v>119</v>
+      </c>
+      <c r="B72" t="s">
+        <v>62</v>
+      </c>
+      <c r="C72" t="s">
+        <v>63</v>
       </c>
       <c r="D72">
         <v>37.5</v>
@@ -3797,21 +4524,21 @@
         <v>107</v>
       </c>
       <c r="H72">
-        <v>63.40843160000001</v>
+        <v>63.408431600000007</v>
       </c>
       <c r="I72">
-        <v>8.6937046</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Morre</v>
-      </c>
-      <c r="B73" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C73" t="str">
-        <v>Hydro</v>
+        <v>8.6937046000000002</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A73" t="s">
+        <v>120</v>
+      </c>
+      <c r="B73" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73" t="s">
+        <v>44</v>
       </c>
       <c r="D73">
         <v>16</v>
@@ -3826,21 +4553,21 @@
         <v>138</v>
       </c>
       <c r="H73">
-        <v>63.966667</v>
+        <v>63.966667000000001</v>
       </c>
       <c r="I73">
-        <v>10.2</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Meraker</v>
-      </c>
-      <c r="B74" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C74" t="str">
-        <v>Hydro</v>
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A74" t="s">
+        <v>121</v>
+      </c>
+      <c r="B74" t="s">
+        <v>44</v>
+      </c>
+      <c r="C74" t="s">
+        <v>44</v>
       </c>
       <c r="D74">
         <v>108</v>
@@ -3855,21 +4582,21 @@
         <v>139</v>
       </c>
       <c r="H74">
-        <v>63.4161689</v>
+        <v>63.416168900000002</v>
       </c>
       <c r="I74">
         <v>11.7372151</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>Osbu</v>
-      </c>
-      <c r="B75" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C75" t="str">
-        <v>Hydro</v>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A75" t="s">
+        <v>122</v>
+      </c>
+      <c r="B75" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" t="s">
+        <v>44</v>
       </c>
       <c r="D75">
         <v>28</v>
@@ -3884,21 +4611,21 @@
         <v>45</v>
       </c>
       <c r="H75">
-        <v>62.5166667</v>
+        <v>62.516666700000002</v>
       </c>
       <c r="I75">
         <v>8.5</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Osen</v>
-      </c>
-      <c r="B76" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C76" t="str">
-        <v>Hydro</v>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A76" t="s">
+        <v>123</v>
+      </c>
+      <c r="B76" t="s">
+        <v>44</v>
+      </c>
+      <c r="C76" t="s">
+        <v>44</v>
       </c>
       <c r="D76">
         <v>5</v>
@@ -3913,21 +4640,21 @@
         <v>176</v>
       </c>
       <c r="H76">
-        <v>64.42113979999999</v>
+        <v>64.421139799999992</v>
       </c>
       <c r="I76">
         <v>10.0377767</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>Riksheimdal</v>
-      </c>
-      <c r="B77" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C77" t="str">
-        <v>Hydro</v>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A77" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" t="s">
+        <v>44</v>
       </c>
       <c r="D77">
         <v>9.5</v>
@@ -3942,21 +4669,21 @@
         <v>141</v>
       </c>
       <c r="H77">
-        <v>62.35751</v>
+        <v>62.357509999999998</v>
       </c>
       <c r="I77">
-        <v>6.571916000000001</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>Oksenelvane</v>
-      </c>
-      <c r="B78" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C78" t="str">
-        <v>Run-Of-River</v>
+        <v>6.5719160000000008</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A78" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" t="s">
+        <v>44</v>
+      </c>
+      <c r="C78" t="s">
+        <v>49</v>
       </c>
       <c r="D78">
         <v>30</v>
@@ -3971,21 +4698,21 @@
         <v>161</v>
       </c>
       <c r="H78">
-        <v>61.84183</v>
+        <v>61.841830000000002</v>
       </c>
       <c r="I78">
-        <v>5.80134</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>Trollheim</v>
-      </c>
-      <c r="B79" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C79" t="str">
-        <v>Reservoir</v>
+        <v>5.8013399999999997</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A79" t="s">
+        <v>126</v>
+      </c>
+      <c r="B79" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" t="s">
+        <v>45</v>
       </c>
       <c r="D79">
         <v>130</v>
@@ -4003,18 +4730,18 @@
         <v>63.002761</v>
       </c>
       <c r="I79">
-        <v>9.019152</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>Agdenes</v>
-      </c>
-      <c r="B80" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C80" t="str">
-        <v>Hydro</v>
+        <v>9.0191520000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A80" t="s">
+        <v>127</v>
+      </c>
+      <c r="B80" t="s">
+        <v>44</v>
+      </c>
+      <c r="C80" t="s">
+        <v>44</v>
       </c>
       <c r="D80">
         <v>1.5</v>
@@ -4029,21 +4756,21 @@
         <v>77</v>
       </c>
       <c r="H80">
-        <v>63.5137872</v>
+        <v>63.513787200000003</v>
       </c>
       <c r="I80">
-        <v>9.6812502</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>Aselva</v>
-      </c>
-      <c r="B81" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C81" t="str">
-        <v>Hydro</v>
+        <v>9.6812501999999991</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A81" t="s">
+        <v>128</v>
+      </c>
+      <c r="B81" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" t="s">
+        <v>44</v>
       </c>
       <c r="D81">
         <v>3.5</v>
@@ -4058,27 +4785,27 @@
         <v>77</v>
       </c>
       <c r="H81">
-        <v>63.61501170000001</v>
+        <v>63.615011700000011</v>
       </c>
       <c r="I81">
-        <v>9.7131293</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>Brandaa</v>
-      </c>
-      <c r="B82" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C82" t="str">
-        <v>Hydro</v>
+        <v>9.7131293000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A82" t="s">
+        <v>129</v>
+      </c>
+      <c r="B82" t="s">
+        <v>44</v>
+      </c>
+      <c r="C82" t="s">
+        <v>44</v>
       </c>
       <c r="D82">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="E82">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4087,21 +4814,21 @@
         <v>107</v>
       </c>
       <c r="H82">
-        <v>63.0955621</v>
+        <v>63.095562100000002</v>
       </c>
       <c r="I82">
-        <v>9.1879675</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>Bryggja</v>
-      </c>
-      <c r="B83" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C83" t="str">
-        <v>Hydro</v>
+        <v>9.1879674999999992</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A83" t="s">
+        <v>130</v>
+      </c>
+      <c r="B83" t="s">
+        <v>44</v>
+      </c>
+      <c r="C83" t="s">
+        <v>44</v>
       </c>
       <c r="D83">
         <v>0.3</v>
@@ -4116,27 +4843,27 @@
         <v>161</v>
       </c>
       <c r="H83">
-        <v>61.9407247</v>
+        <v>61.940724699999997</v>
       </c>
       <c r="I83">
-        <v>5.448953899999999</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>Eidsfossen sfe</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Hydro</v>
+        <v>5.4489538999999994</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A84" t="s">
+        <v>131</v>
+      </c>
+      <c r="B84" t="s">
+        <v>44</v>
+      </c>
+      <c r="C84" t="s">
+        <v>44</v>
       </c>
       <c r="D84">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="E84">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4148,18 +4875,18 @@
         <v>61.7557051</v>
       </c>
       <c r="I84">
-        <v>6.246569999999998</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Eidum</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C85" t="str">
-        <v>Hydro</v>
+        <v>6.2465699999999984</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A85" t="s">
+        <v>132</v>
+      </c>
+      <c r="B85" t="s">
+        <v>44</v>
+      </c>
+      <c r="C85" t="s">
+        <v>44</v>
       </c>
       <c r="D85">
         <v>4.8</v>
@@ -4174,21 +4901,21 @@
         <v>139</v>
       </c>
       <c r="H85">
-        <v>63.443507</v>
+        <v>63.443506999999997</v>
       </c>
       <c r="I85">
-        <v>10.9815216</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Fossan halogalan</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C86" t="str">
-        <v>Hydro</v>
+        <v>10.981521600000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A86" t="s">
+        <v>133</v>
+      </c>
+      <c r="B86" t="s">
+        <v>44</v>
+      </c>
+      <c r="C86" t="s">
+        <v>44</v>
       </c>
       <c r="D86">
         <v>8.1</v>
@@ -4203,21 +4930,21 @@
         <v>139</v>
       </c>
       <c r="H86">
-        <v>63.26999549999999</v>
+        <v>63.269995499999993</v>
       </c>
       <c r="I86">
-        <v>11.0069364</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Fr.stad bioel</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C87" t="str">
-        <v>Hydro</v>
+        <v>11.006936400000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A87" t="s">
+        <v>134</v>
+      </c>
+      <c r="B87" t="s">
+        <v>44</v>
+      </c>
+      <c r="C87" t="s">
+        <v>44</v>
       </c>
       <c r="D87">
         <v>5.5</v>
@@ -4235,18 +4962,18 @@
         <v>62.2034454</v>
       </c>
       <c r="I87">
-        <v>5.1708738</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>Groa</v>
-      </c>
-      <c r="B88" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C88" t="str">
-        <v>Hydro</v>
+        <v>5.1708737999999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A88" t="s">
+        <v>135</v>
+      </c>
+      <c r="B88" t="s">
+        <v>44</v>
+      </c>
+      <c r="C88" t="s">
+        <v>44</v>
       </c>
       <c r="D88">
         <v>40</v>
@@ -4261,21 +4988,21 @@
         <v>45</v>
       </c>
       <c r="H88">
-        <v>62.64398370000001</v>
+        <v>62.643983700000007</v>
       </c>
       <c r="I88">
-        <v>8.729954000000001</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>Holla</v>
-      </c>
-      <c r="B89" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C89" t="str">
-        <v>Hydro</v>
+        <v>8.7299540000000011</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A89" t="s">
+        <v>136</v>
+      </c>
+      <c r="B89" t="s">
+        <v>44</v>
+      </c>
+      <c r="C89" t="s">
+        <v>44</v>
       </c>
       <c r="D89">
         <v>0.4</v>
@@ -4293,18 +5020,18 @@
         <v>63.313609</v>
       </c>
       <c r="I89">
-        <v>9.142308</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>Hopen</v>
-      </c>
-      <c r="B90" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C90" t="str">
-        <v>Hydro</v>
+        <v>9.1423079999999999</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A90" t="s">
+        <v>137</v>
+      </c>
+      <c r="B90" t="s">
+        <v>44</v>
+      </c>
+      <c r="C90" t="s">
+        <v>44</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -4319,21 +5046,21 @@
         <v>45</v>
       </c>
       <c r="H90">
-        <v>63.4634417</v>
+        <v>63.463441699999997</v>
       </c>
       <c r="I90">
         <v>8.0138783</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>Innset</v>
-      </c>
-      <c r="B91" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C91" t="str">
-        <v>Hydro</v>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A91" t="s">
+        <v>138</v>
+      </c>
+      <c r="B91" t="s">
+        <v>44</v>
+      </c>
+      <c r="C91" t="s">
+        <v>44</v>
       </c>
       <c r="D91">
         <v>105</v>
@@ -4348,21 +5075,21 @@
         <v>62</v>
       </c>
       <c r="H91">
-        <v>62.719549</v>
+        <v>62.719549000000001</v>
       </c>
       <c r="I91">
         <v>10.0280798</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>Jardola</v>
-      </c>
-      <c r="B92" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C92" t="str">
-        <v>Hydro</v>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A92" t="s">
+        <v>139</v>
+      </c>
+      <c r="B92" t="s">
+        <v>44</v>
+      </c>
+      <c r="C92" t="s">
+        <v>44</v>
       </c>
       <c r="D92">
         <v>4.8</v>
@@ -4380,18 +5107,18 @@
         <v>61.7171059</v>
       </c>
       <c r="I92">
-        <v>6.2347907</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Kassdalen</v>
-      </c>
-      <c r="B93" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C93" t="str">
-        <v>Hydro</v>
+        <v>6.2347906999999996</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A93" t="s">
+        <v>140</v>
+      </c>
+      <c r="B93" t="s">
+        <v>44</v>
+      </c>
+      <c r="C93" t="s">
+        <v>44</v>
       </c>
       <c r="D93">
         <v>2.4</v>
@@ -4406,21 +5133,21 @@
         <v>108</v>
       </c>
       <c r="H93">
-        <v>62.7933251</v>
+        <v>62.793325099999997</v>
       </c>
       <c r="I93">
-        <v>11.1883103</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>Kurasfossen</v>
-      </c>
-      <c r="B94" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C94" t="str">
-        <v>Hydro</v>
+        <v>11.188310299999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A94" t="s">
+        <v>141</v>
+      </c>
+      <c r="B94" t="s">
+        <v>44</v>
+      </c>
+      <c r="C94" t="s">
+        <v>44</v>
       </c>
       <c r="D94">
         <v>12.7</v>
@@ -4435,21 +5162,21 @@
         <v>108</v>
       </c>
       <c r="H94">
-        <v>62.67890179999999</v>
+        <v>62.678901799999991</v>
       </c>
       <c r="I94">
         <v>11.4618021</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Namsos</v>
-      </c>
-      <c r="B95" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C95" t="str">
-        <v>Hydro</v>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A95" t="s">
+        <v>142</v>
+      </c>
+      <c r="B95" t="s">
+        <v>44</v>
+      </c>
+      <c r="C95" t="s">
+        <v>44</v>
       </c>
       <c r="D95">
         <v>12.7</v>
@@ -4464,21 +5191,21 @@
         <v>176</v>
       </c>
       <c r="H95">
-        <v>64.50405110000001</v>
+        <v>64.504051100000012</v>
       </c>
       <c r="I95">
         <v>11.510163</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>Nordsvorka</v>
-      </c>
-      <c r="B96" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C96" t="str">
-        <v>Hydro</v>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A96" t="s">
+        <v>143</v>
+      </c>
+      <c r="B96" t="s">
+        <v>44</v>
+      </c>
+      <c r="C96" t="s">
+        <v>44</v>
       </c>
       <c r="D96">
         <v>3</v>
@@ -4493,21 +5220,21 @@
         <v>107</v>
       </c>
       <c r="H96">
-        <v>63.04507650000001</v>
+        <v>63.045076500000008</v>
       </c>
       <c r="I96">
-        <v>8.8672097</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>Ogndal</v>
-      </c>
-      <c r="B97" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C97" t="str">
-        <v>Hydro</v>
+        <v>8.8672097000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A97" t="s">
+        <v>144</v>
+      </c>
+      <c r="B97" t="s">
+        <v>44</v>
+      </c>
+      <c r="C97" t="s">
+        <v>44</v>
       </c>
       <c r="D97">
         <v>13.7</v>
@@ -4522,21 +5249,21 @@
         <v>138</v>
       </c>
       <c r="H97">
-        <v>64.01501929999999</v>
+        <v>64.015019299999992</v>
       </c>
       <c r="I97">
         <v>11.4952627</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>Orkdal</v>
-      </c>
-      <c r="B98" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C98" t="str">
-        <v>Hydro</v>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A98" t="s">
+        <v>145</v>
+      </c>
+      <c r="B98" t="s">
+        <v>44</v>
+      </c>
+      <c r="C98" t="s">
+        <v>44</v>
       </c>
       <c r="D98">
         <v>41</v>
@@ -4551,21 +5278,21 @@
         <v>77</v>
       </c>
       <c r="H98">
-        <v>63.30241299999999</v>
+        <v>63.302412999999987</v>
       </c>
       <c r="I98">
-        <v>9.8477711</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Selbu</v>
-      </c>
-      <c r="B99" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Hydro</v>
+        <v>9.8477710999999992</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A99" t="s">
+        <v>146</v>
+      </c>
+      <c r="B99" t="s">
+        <v>44</v>
+      </c>
+      <c r="C99" t="s">
+        <v>44</v>
       </c>
       <c r="D99">
         <v>1.3</v>
@@ -4580,21 +5307,21 @@
         <v>139</v>
       </c>
       <c r="H99">
-        <v>63.21924539999999</v>
+        <v>63.219245399999991</v>
       </c>
       <c r="I99">
         <v>11.04129</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>Thamshavn</v>
-      </c>
-      <c r="B100" t="str">
-        <v>Thermal</v>
-      </c>
-      <c r="C100" t="str">
-        <v>OCGT</v>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A100" t="s">
+        <v>147</v>
+      </c>
+      <c r="B100" t="s">
+        <v>62</v>
+      </c>
+      <c r="C100" t="s">
+        <v>63</v>
       </c>
       <c r="D100">
         <v>31</v>
@@ -4609,21 +5336,21 @@
         <v>77</v>
       </c>
       <c r="H100">
-        <v>63.32058490000001</v>
+        <v>63.320584900000007</v>
       </c>
       <c r="I100">
         <v>9.8825433</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Vagamo</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C101" t="str">
-        <v>Hydro</v>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A101" t="s">
+        <v>148</v>
+      </c>
+      <c r="B101" t="s">
+        <v>44</v>
+      </c>
+      <c r="C101" t="s">
+        <v>44</v>
       </c>
       <c r="D101">
         <v>6.5</v>
@@ -4638,21 +5365,21 @@
         <v>30</v>
       </c>
       <c r="H101">
-        <v>61.87517010000001</v>
+        <v>61.875170100000012</v>
       </c>
       <c r="I101">
-        <v>9.0966266</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Verdal</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C102" t="str">
-        <v>Hydro</v>
+        <v>9.0966266000000005</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A102" t="s">
+        <v>149</v>
+      </c>
+      <c r="B102" t="s">
+        <v>44</v>
+      </c>
+      <c r="C102" t="s">
+        <v>44</v>
       </c>
       <c r="D102">
         <v>23.9</v>
@@ -4667,21 +5394,21 @@
         <v>105</v>
       </c>
       <c r="H102">
-        <v>63.75059810000001</v>
+        <v>63.750598100000012</v>
       </c>
       <c r="I102">
         <v>11.916895</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Verma</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C103" t="str">
-        <v>Hydro</v>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A103" t="s">
+        <v>150</v>
+      </c>
+      <c r="B103" t="s">
+        <v>44</v>
+      </c>
+      <c r="C103" t="s">
+        <v>44</v>
       </c>
       <c r="D103">
         <v>8.4</v>
@@ -4696,21 +5423,21 @@
         <v>79</v>
       </c>
       <c r="H103">
-        <v>62.34332970000001</v>
+        <v>62.343329700000012</v>
       </c>
       <c r="I103">
-        <v>8.0588759</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Via</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C104" t="str">
-        <v>Hydro</v>
+        <v>8.0588759000000003</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A104" t="s">
+        <v>151</v>
+      </c>
+      <c r="B104" t="s">
+        <v>44</v>
+      </c>
+      <c r="C104" t="s">
+        <v>44</v>
       </c>
       <c r="D104">
         <v>3.2</v>
@@ -4725,21 +5452,21 @@
         <v>109</v>
       </c>
       <c r="H104">
-        <v>61.87161410000001</v>
+        <v>61.871614100000009</v>
       </c>
       <c r="I104">
-        <v>6.8477066</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Viddal</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Hydro</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Hydro</v>
+        <v>6.8477066000000004</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A105" t="s">
+        <v>152</v>
+      </c>
+      <c r="B105" t="s">
+        <v>44</v>
+      </c>
+      <c r="C105" t="s">
+        <v>44</v>
       </c>
       <c r="D105">
         <v>5.5</v>
@@ -4754,74 +5481,75 @@
         <v>141</v>
       </c>
       <c r="H105">
-        <v>62.13974920000001</v>
+        <v>62.139749200000011</v>
       </c>
       <c r="I105">
-        <v>6.6117855</v>
+        <v>6.6117854999999999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I105"/>
+    <ignoredError sqref="A1:I105" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N23"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>line_id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>area0</v>
-      </c>
-      <c r="C1" t="str">
-        <v>bus0</v>
-      </c>
-      <c r="D1" t="str">
-        <v>bus1</v>
-      </c>
-      <c r="E1" t="str">
-        <v>length</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Vbase</v>
-      </c>
-      <c r="G1" t="str">
-        <v>lat</v>
-      </c>
-      <c r="H1" t="str">
-        <v>lon</v>
-      </c>
-      <c r="I1" t="str">
-        <v>R_per_m</v>
-      </c>
-      <c r="J1" t="str">
-        <v>X_per_m</v>
-      </c>
-      <c r="K1" t="str">
-        <v>B_per_m</v>
-      </c>
-      <c r="L1" t="str">
-        <v>name</v>
-      </c>
-      <c r="M1" t="str">
-        <v>eic code</v>
-      </c>
-      <c r="N1" t="str">
-        <v>S_max</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="A1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" t="s">
+        <v>161</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>1166</v>
       </c>
-      <c r="B2" t="str">
-        <v>NO3</v>
+      <c r="B2" t="s">
+        <v>17</v>
       </c>
       <c r="C2">
         <v>77</v>
@@ -4830,42 +5558,42 @@
         <v>107</v>
       </c>
       <c r="E2">
-        <v>33284.9843738102</v>
+        <v>33284.984373810199</v>
       </c>
       <c r="F2">
         <v>132</v>
       </c>
-      <c r="G2" t="str">
-        <v>[63.0581865391036, 63.169235, 63.271747122419]</v>
-      </c>
-      <c r="H2" t="str">
-        <v>[9.6024199750926, 9.95773300000001, 9.93306218856054]</v>
+      <c r="G2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H2" t="s">
+        <v>163</v>
       </c>
       <c r="I2">
-        <v>0.00005999996013291688</v>
+        <v>5.9999960132916883E-5</v>
       </c>
       <c r="J2">
-        <v>0.0003010000000000001</v>
+        <v>3.0100000000000011E-4</v>
       </c>
       <c r="K2">
-        <v>3e-9</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Thamshavn trafostasjon – Grana koblingsstasjon</v>
+        <v>3E-9</v>
+      </c>
+      <c r="L2" t="s">
+        <v>164</v>
       </c>
       <c r="M2">
         <v>10943</v>
       </c>
-      <c r="N2" t="str">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="N2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>1334</v>
       </c>
-      <c r="B3" t="str">
-        <v>NO3</v>
+      <c r="B3" t="s">
+        <v>17</v>
       </c>
       <c r="C3">
         <v>46</v>
@@ -4874,42 +5602,42 @@
         <v>62</v>
       </c>
       <c r="E3">
-        <v>9416.388128683471</v>
-      </c>
-      <c r="F3" t="str">
-        <v>132</v>
-      </c>
-      <c r="G3" t="str">
-        <v>[62.6815788399503, 62.6288473888959]</v>
-      </c>
-      <c r="H3" t="str">
-        <v>[10.1228770726635, 10.2663749273365]</v>
+        <v>9416.3881286834712</v>
+      </c>
+      <c r="F3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" t="s">
+        <v>168</v>
       </c>
       <c r="I3">
-        <v>0.00005999996013291685</v>
+        <v>5.9999960132916849E-5</v>
       </c>
       <c r="J3">
-        <v>0.0003009999999999999</v>
+        <v>3.0099999999999989E-4</v>
       </c>
       <c r="K3">
-        <v>3e-9</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Brattset trafostasjon – Brattset trafostasjon</v>
-      </c>
-      <c r="M3" t="str">
-        <v>3rr4</v>
-      </c>
-      <c r="N3" t="str">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>3E-9</v>
+      </c>
+      <c r="L3" t="s">
+        <v>169</v>
+      </c>
+      <c r="M3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A4">
         <v>1335</v>
       </c>
-      <c r="B4" t="str">
-        <v>NO3</v>
+      <c r="B4" t="s">
+        <v>17</v>
       </c>
       <c r="C4">
         <v>62</v>
@@ -4923,37 +5651,37 @@
       <c r="F4">
         <v>132</v>
       </c>
-      <c r="G4" t="str">
-        <v>[62.764642333228, 62.6818480622148]</v>
-      </c>
-      <c r="H4" t="str">
-        <v>[9.93059299951052, 10.1222020004895]</v>
+      <c r="G4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4" t="s">
+        <v>172</v>
       </c>
       <c r="I4">
-        <v>0.00005999996013291684</v>
+        <v>5.9999960132916842E-5</v>
       </c>
       <c r="J4">
-        <v>0.0003010000000000001</v>
+        <v>3.0100000000000011E-4</v>
       </c>
       <c r="K4">
-        <v>3e-9</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Brattset trafostasjon – Brattset trafostasjon</v>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>3E-9</v>
+      </c>
+      <c r="L4" t="s">
+        <v>169</v>
+      </c>
+      <c r="M4" t="s">
+        <v>173</v>
+      </c>
+      <c r="N4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A5">
         <v>1336</v>
       </c>
-      <c r="B5" t="str">
-        <v>NO3</v>
+      <c r="B5" t="s">
+        <v>17</v>
       </c>
       <c r="C5">
         <v>107</v>
@@ -4967,37 +5695,37 @@
       <c r="F5">
         <v>132</v>
       </c>
-      <c r="G5" t="str">
-        <v>[63.0578905163084, 62.7649652979347]</v>
-      </c>
-      <c r="H5" t="str">
-        <v>[9.60225399160166, 9.93006400839835]</v>
+      <c r="G5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H5" t="s">
+        <v>175</v>
       </c>
       <c r="I5">
-        <v>0.00005999996013291684</v>
+        <v>5.9999960132916842E-5</v>
       </c>
       <c r="J5">
-        <v>0.000301</v>
+        <v>3.01E-4</v>
       </c>
       <c r="K5">
-        <v>3e-9</v>
-      </c>
-      <c r="L5" t="str">
-        <v>Grana koblingsstasjon – Brattset trafostasjon</v>
+        <v>3E-9</v>
+      </c>
+      <c r="L5" t="s">
+        <v>176</v>
       </c>
       <c r="M5">
         <v>3343</v>
       </c>
-      <c r="N5" t="str">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="N5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>1165</v>
       </c>
-      <c r="B6" t="str">
-        <v>NO3</v>
+      <c r="B6" t="s">
+        <v>17</v>
       </c>
       <c r="C6">
         <v>141</v>
@@ -5011,37 +5739,37 @@
       <c r="F6">
         <v>132</v>
       </c>
-      <c r="G6" t="str">
-        <v>[62.4779336946648, 61.7329656956376]</v>
-      </c>
-      <c r="H6" t="str">
-        <v>[7.03366082879706, 5.21884217120294]</v>
+      <c r="G6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H6" t="s">
+        <v>178</v>
       </c>
       <c r="I6">
-        <v>0.00005999996013291685</v>
+        <v>5.9999960132916849E-5</v>
       </c>
       <c r="J6">
-        <v>0.0003010000000000001</v>
+        <v>3.0100000000000011E-4</v>
       </c>
       <c r="K6">
-        <v>3e-9</v>
-      </c>
-      <c r="L6" t="str">
-        <v>Ørskog trafostasjon – Svelgen trafostasjon</v>
-      </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6" t="str">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>3E-9</v>
+      </c>
+      <c r="L6" t="s">
+        <v>179</v>
+      </c>
+      <c r="M6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>1289</v>
       </c>
-      <c r="B7" t="str">
-        <v>NO3</v>
+      <c r="B7" t="s">
+        <v>17</v>
       </c>
       <c r="C7">
         <v>138</v>
@@ -5055,37 +5783,37 @@
       <c r="F7">
         <v>300</v>
       </c>
-      <c r="G7" t="str">
-        <v>[63.979469495752, 63.951246, 63.7796426966659]</v>
-      </c>
-      <c r="H7" t="str">
-        <v>[11.4783430752882, 11.578217, 11.4725900216729]</v>
+      <c r="G7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H7" t="s">
+        <v>181</v>
       </c>
       <c r="I7">
-        <v>0.00004000000000000001</v>
+        <v>4.000000000000001E-5</v>
       </c>
       <c r="J7">
-        <v>0.000265</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K7">
-        <v>3.9e-9</v>
-      </c>
-      <c r="L7" t="str">
-        <v>Ogndal trafostasjon – Verdal trafostasjon</v>
-      </c>
-      <c r="M7" t="str">
-        <v/>
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="L7" t="s">
+        <v>182</v>
+      </c>
+      <c r="M7" t="s">
+        <v>173</v>
       </c>
       <c r="N7">
         <v>500</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>1290</v>
       </c>
-      <c r="B8" t="str">
-        <v>NO3</v>
+      <c r="B8" t="s">
+        <v>17</v>
       </c>
       <c r="C8">
         <v>105</v>
@@ -5094,28 +5822,28 @@
         <v>139</v>
       </c>
       <c r="E8">
-        <v>42360.4172547092</v>
+        <v>42360.417254709202</v>
       </c>
       <c r="F8">
         <v>300</v>
       </c>
-      <c r="G8" t="str">
-        <v>[63.7792842667966, 63.4574296446683]</v>
-      </c>
-      <c r="H8" t="str">
-        <v>[11.4722350100571, 11.0181519899429]</v>
+      <c r="G8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" t="s">
+        <v>184</v>
       </c>
       <c r="I8">
-        <v>0.00004</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J8">
-        <v>0.000265</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K8">
-        <v>3.9e-9</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Verdal trafostasjon – Eidum trafostasjon</v>
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="L8" t="s">
+        <v>185</v>
       </c>
       <c r="M8">
         <v>343321</v>
@@ -5124,12 +5852,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>1291</v>
       </c>
-      <c r="B9" t="str">
-        <v>NO3</v>
+      <c r="B9" t="s">
+        <v>17</v>
       </c>
       <c r="C9">
         <v>139</v>
@@ -5138,42 +5866,42 @@
         <v>106</v>
       </c>
       <c r="E9">
-        <v>29662.1134927554</v>
+        <v>29662.113492755401</v>
       </c>
       <c r="F9">
         <v>300</v>
       </c>
-      <c r="G9" t="str">
-        <v>[63.4013872743893, 63.423488, 63.4571907093831]</v>
-      </c>
-      <c r="H9" t="str">
-        <v>[10.4402013779148, 10.813293, 11.0174939283141]</v>
+      <c r="G9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H9" t="s">
+        <v>187</v>
       </c>
       <c r="I9">
-        <v>0.00004000000000000002</v>
+        <v>4.0000000000000017E-5</v>
       </c>
       <c r="J9">
-        <v>0.000265</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K9">
-        <v>3.9e-9</v>
-      </c>
-      <c r="L9" t="str">
-        <v>Eidum trafostasjon – Strinda koblingsstasjon</v>
-      </c>
-      <c r="M9" t="str">
-        <v/>
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="L9" t="s">
+        <v>188</v>
+      </c>
+      <c r="M9" t="s">
+        <v>173</v>
       </c>
       <c r="N9">
         <v>500</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>1173</v>
       </c>
-      <c r="B10" t="str">
-        <v>NO3</v>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
       <c r="C10">
         <v>105</v>
@@ -5182,42 +5910,42 @@
         <v>76</v>
       </c>
       <c r="E10">
-        <v>84842.6985751086</v>
+        <v>84842.698575108603</v>
       </c>
       <c r="F10">
         <v>300</v>
       </c>
-      <c r="G10" t="str">
-        <v>[63.779267150403, 63.703506, 63.409354, 63.2769667913878]</v>
-      </c>
-      <c r="H10" t="str">
-        <v>[11.4726336570695, 11.538391, 11.15387, 10.4580241866236]</v>
+      <c r="G10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H10" t="s">
+        <v>190</v>
       </c>
       <c r="I10">
-        <v>0.00004</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J10">
-        <v>0.000265</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K10">
-        <v>3.9e-9</v>
-      </c>
-      <c r="L10" t="str">
-        <v>Verdal trafostasjon – Klæbu transformatorstasjon</v>
-      </c>
-      <c r="M10" t="str">
-        <v/>
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="L10" t="s">
+        <v>191</v>
+      </c>
+      <c r="M10" t="s">
+        <v>173</v>
       </c>
       <c r="N10">
         <v>500</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A11">
         <v>1174</v>
       </c>
-      <c r="B11" t="str">
-        <v>NO3</v>
+      <c r="B11" t="s">
+        <v>17</v>
       </c>
       <c r="C11">
         <v>106</v>
@@ -5231,37 +5959,37 @@
       <c r="F11">
         <v>300</v>
       </c>
-      <c r="G11" t="str">
-        <v>[63.2770887040084, 63.4011611611364]</v>
-      </c>
-      <c r="H11" t="str">
-        <v>[10.4575822753626, 10.4397867246374]</v>
+      <c r="G11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H11" t="s">
+        <v>193</v>
       </c>
       <c r="I11">
-        <v>0.00004</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J11">
-        <v>0.000265</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K11">
-        <v>3.9e-9</v>
-      </c>
-      <c r="L11" t="str">
-        <v>Strinda koblingsstasjon – Klæbu transformatorstasjon</v>
-      </c>
-      <c r="M11" t="str">
-        <v/>
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="L11" t="s">
+        <v>194</v>
+      </c>
+      <c r="M11" t="s">
+        <v>173</v>
       </c>
       <c r="N11">
         <v>500</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>1292</v>
       </c>
-      <c r="B12" t="str">
-        <v>NO3</v>
+      <c r="B12" t="s">
+        <v>17</v>
       </c>
       <c r="C12">
         <v>76</v>
@@ -5275,37 +6003,37 @@
       <c r="F12">
         <v>300</v>
       </c>
-      <c r="G12" t="str">
-        <v>[63.2719119610727, 63.268241, 63.23672, 63.2768450273625]</v>
-      </c>
-      <c r="H12" t="str">
-        <v>[9.93345548452976, 9.979706, 10.04837, 10.4571728802973]</v>
+      <c r="G12" t="s">
+        <v>195</v>
+      </c>
+      <c r="H12" t="s">
+        <v>196</v>
       </c>
       <c r="I12">
-        <v>0.00003999999999999999</v>
+        <v>3.999999999999999E-5</v>
       </c>
       <c r="J12">
-        <v>0.000265</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K12">
-        <v>3.9e-9</v>
-      </c>
-      <c r="L12" t="str">
-        <v>Klæbu transformatorstasjon – Orkdal transformatorstasjon</v>
-      </c>
-      <c r="M12" t="str">
-        <v/>
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="L12" t="s">
+        <v>197</v>
+      </c>
+      <c r="M12" t="s">
+        <v>173</v>
       </c>
       <c r="N12">
         <v>500</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A13">
         <v>1175</v>
       </c>
-      <c r="B13" t="str">
-        <v>NO3</v>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13">
         <v>60</v>
@@ -5319,37 +6047,37 @@
       <c r="F13">
         <v>300</v>
       </c>
-      <c r="G13" t="str">
-        <v>[62.6799952696754, 63.021959, 63.202068, 63.2717982207385]</v>
-      </c>
-      <c r="H13" t="str">
-        <v>[8.48028947595439, 8.897552, 9.79156500000001, 9.93271247746952]</v>
+      <c r="G13" t="s">
+        <v>198</v>
+      </c>
+      <c r="H13" t="s">
+        <v>199</v>
       </c>
       <c r="I13">
-        <v>0.00004</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J13">
-        <v>0.000265</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K13">
-        <v>3.9e-9</v>
-      </c>
-      <c r="L13" t="str">
-        <v>Orkdal transformatorstasjon – Aura trafostasjon</v>
-      </c>
-      <c r="M13" t="str">
-        <v/>
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="L13" t="s">
+        <v>200</v>
+      </c>
+      <c r="M13" t="s">
+        <v>173</v>
       </c>
       <c r="N13">
         <v>500</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A14">
         <v>6798</v>
       </c>
-      <c r="B14" t="str">
-        <v>NO3</v>
+      <c r="B14" t="s">
+        <v>17</v>
       </c>
       <c r="C14">
         <v>45</v>
@@ -5358,42 +6086,42 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>93475.106910837</v>
+        <v>93475.106910836999</v>
       </c>
       <c r="F14">
         <v>300</v>
       </c>
-      <c r="G14" t="str">
-        <v>[61.8861304294624, 62.6796217603448]</v>
-      </c>
-      <c r="H14" t="str">
-        <v>[9.06357629708208, 8.48021670291793]</v>
+      <c r="G14" t="s">
+        <v>201</v>
+      </c>
+      <c r="H14" t="s">
+        <v>202</v>
       </c>
       <c r="I14">
-        <v>0.00004</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J14">
-        <v>0.000265</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K14">
-        <v>3.9e-9</v>
-      </c>
-      <c r="L14" t="str">
-        <v>Aura trafostasjon – Vågåmo trafo stasjon</v>
-      </c>
-      <c r="M14" t="str">
-        <v/>
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="L14" t="s">
+        <v>203</v>
+      </c>
+      <c r="M14" t="s">
+        <v>173</v>
       </c>
       <c r="N14">
         <v>500</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A15">
         <v>1288</v>
       </c>
-      <c r="B15" t="str">
-        <v>NO3</v>
+      <c r="B15" t="s">
+        <v>17</v>
       </c>
       <c r="C15">
         <v>138</v>
@@ -5407,37 +6135,37 @@
       <c r="F15">
         <v>300</v>
       </c>
-      <c r="G15" t="str">
-        <v>[63.9797705313635, 64.4536577724636]</v>
-      </c>
-      <c r="H15" t="str">
-        <v>[11.4780240828036, 11.6207309171964]</v>
+      <c r="G15" t="s">
+        <v>204</v>
+      </c>
+      <c r="H15" t="s">
+        <v>205</v>
       </c>
       <c r="I15">
-        <v>0.00004</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J15">
-        <v>0.000265</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K15">
-        <v>3.9e-9</v>
-      </c>
-      <c r="L15" t="str">
-        <v>Ogndal trafostasjon – Namsos (Statnett) trafostasjon</v>
-      </c>
-      <c r="M15" t="str">
-        <v/>
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="L15" t="s">
+        <v>206</v>
+      </c>
+      <c r="M15" t="s">
+        <v>173</v>
       </c>
       <c r="N15">
         <v>500</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>6562</v>
       </c>
-      <c r="B16" t="str">
-        <v>NO3</v>
+      <c r="B16" t="s">
+        <v>17</v>
       </c>
       <c r="C16">
         <v>61</v>
@@ -5446,42 +6174,42 @@
         <v>79</v>
       </c>
       <c r="E16">
-        <v>39089.7952053636</v>
+        <v>39089.795205363604</v>
       </c>
       <c r="F16">
         <v>380</v>
       </c>
-      <c r="G16" t="str">
-        <v>[62.5263493502315, 62.6797261154976]</v>
-      </c>
-      <c r="H16" t="str">
-        <v>[7.79520216211446, 8.47966983788554]</v>
+      <c r="G16" t="s">
+        <v>207</v>
+      </c>
+      <c r="H16" t="s">
+        <v>208</v>
       </c>
       <c r="I16">
-        <v>0.00002999999999999999</v>
+        <v>2.9999999999999991E-5</v>
       </c>
       <c r="J16">
-        <v>0.0002459999999999999</v>
+        <v>2.4599999999999991E-4</v>
       </c>
       <c r="K16">
-        <v>4.1e-9</v>
-      </c>
-      <c r="L16" t="str">
-        <v>Viklandet trafostasjon – Grytten trafostasjon</v>
-      </c>
-      <c r="M16" t="str">
-        <v/>
+        <v>4.1000000000000003E-9</v>
+      </c>
+      <c r="L16" t="s">
+        <v>209</v>
+      </c>
+      <c r="M16" t="s">
+        <v>173</v>
       </c>
       <c r="N16">
         <v>600</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A17">
         <v>1293</v>
       </c>
-      <c r="B17" t="str">
-        <v>NO3</v>
+      <c r="B17" t="s">
+        <v>17</v>
       </c>
       <c r="C17">
         <v>78</v>
@@ -5490,42 +6218,42 @@
         <v>61</v>
       </c>
       <c r="E17">
-        <v>139115.670121624</v>
+        <v>139115.67012162399</v>
       </c>
       <c r="F17">
         <v>380</v>
       </c>
-      <c r="G17" t="str">
-        <v>[63.2769332188306, 63.325632, 63.085435, 62.6800121989769]</v>
-      </c>
-      <c r="H17" t="str">
-        <v>[10.4571743955897, 9.986572, 8.751984, 8.480202620587]</v>
+      <c r="G17" t="s">
+        <v>210</v>
+      </c>
+      <c r="H17" t="s">
+        <v>211</v>
       </c>
       <c r="I17">
-        <v>0.00003</v>
+        <v>3.0000000000000001E-5</v>
       </c>
       <c r="J17">
-        <v>0.0002460000000000001</v>
+        <v>2.4600000000000012E-4</v>
       </c>
       <c r="K17">
-        <v>4.1e-9</v>
-      </c>
-      <c r="L17" t="str">
-        <v>Klæbu transformatorstasjon – Viklandet trafostasjon</v>
-      </c>
-      <c r="M17" t="str">
-        <v/>
+        <v>4.1000000000000003E-9</v>
+      </c>
+      <c r="L17" t="s">
+        <v>212</v>
+      </c>
+      <c r="M17" t="s">
+        <v>173</v>
       </c>
       <c r="N17">
         <v>600</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A18">
         <v>1176</v>
       </c>
-      <c r="B18" t="str">
-        <v>NO3</v>
+      <c r="B18" t="s">
+        <v>17</v>
       </c>
       <c r="C18">
         <v>109</v>
@@ -5534,42 +6262,42 @@
         <v>79</v>
       </c>
       <c r="E18">
-        <v>39526.8787960495</v>
+        <v>39526.878796049503</v>
       </c>
       <c r="F18">
         <v>380</v>
       </c>
-      <c r="G18" t="str">
-        <v>[62.4780980928918, 62.5262309524377]</v>
-      </c>
-      <c r="H18" t="str">
-        <v>[7.03444016980177, 7.79435683019823]</v>
+      <c r="G18" t="s">
+        <v>213</v>
+      </c>
+      <c r="H18" t="s">
+        <v>214</v>
       </c>
       <c r="I18">
-        <v>0.00003</v>
+        <v>3.0000000000000001E-5</v>
       </c>
       <c r="J18">
-        <v>0.000246</v>
+        <v>2.4600000000000002E-4</v>
       </c>
       <c r="K18">
-        <v>4.1e-9</v>
-      </c>
-      <c r="L18" t="str">
-        <v>Ørskog trafostasjon – Grytten trafostasjon</v>
-      </c>
-      <c r="M18" t="str">
-        <v/>
+        <v>4.1000000000000003E-9</v>
+      </c>
+      <c r="L18" t="s">
+        <v>215</v>
+      </c>
+      <c r="M18" t="s">
+        <v>173</v>
       </c>
       <c r="N18">
         <v>600</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A19">
         <v>1317</v>
       </c>
-      <c r="B19" t="str">
-        <v>NO3</v>
+      <c r="B19" t="s">
+        <v>17</v>
       </c>
       <c r="C19">
         <v>78</v>
@@ -5578,42 +6306,42 @@
         <v>108</v>
       </c>
       <c r="E19">
-        <v>69764.07295620951</v>
+        <v>69764.072956209508</v>
       </c>
       <c r="F19">
         <v>380</v>
       </c>
-      <c r="G19" t="str">
-        <v>[63.0357063153294, 63.061804, 63.22373, 63.2768185449166]</v>
-      </c>
-      <c r="H19" t="str">
-        <v>[11.7274675384392, 11.469727, 10.778961, 10.4580312550914]</v>
+      <c r="G19" t="s">
+        <v>216</v>
+      </c>
+      <c r="H19" t="s">
+        <v>217</v>
       </c>
       <c r="I19">
-        <v>0.00003000000000000001</v>
+        <v>3.0000000000000011E-5</v>
       </c>
       <c r="J19">
-        <v>0.000246</v>
+        <v>2.4600000000000002E-4</v>
       </c>
       <c r="K19">
-        <v>4.1e-9</v>
-      </c>
-      <c r="L19" t="str">
-        <v>Klæbu transformatorstasjon – Nea trafostasjon</v>
-      </c>
-      <c r="M19" t="str">
-        <v/>
+        <v>4.1000000000000003E-9</v>
+      </c>
+      <c r="L19" t="s">
+        <v>218</v>
+      </c>
+      <c r="M19" t="s">
+        <v>173</v>
       </c>
       <c r="N19">
         <v>600</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A20">
         <v>6799</v>
       </c>
-      <c r="B20" t="str">
-        <v>NO3</v>
+      <c r="B20" t="s">
+        <v>17</v>
       </c>
       <c r="C20">
         <v>177</v>
@@ -5627,37 +6355,37 @@
       <c r="F20">
         <v>300</v>
       </c>
-      <c r="G20" t="str">
-        <v>[61.73283, 61.88593]</v>
-      </c>
-      <c r="H20" t="str">
-        <v>[5.218506, 9.063721]</v>
+      <c r="G20" t="s">
+        <v>219</v>
+      </c>
+      <c r="H20" t="s">
+        <v>220</v>
       </c>
       <c r="I20">
-        <v>0.00004</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J20">
-        <v>0.000265</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K20">
-        <v>3.9e-9</v>
-      </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20" t="str">
-        <v/>
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="L20" t="s">
+        <v>173</v>
+      </c>
+      <c r="M20" t="s">
+        <v>173</v>
       </c>
       <c r="N20">
         <v>600</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A21">
         <v>6800</v>
       </c>
-      <c r="B21" t="str">
-        <v>NO3</v>
+      <c r="B21" t="s">
+        <v>17</v>
       </c>
       <c r="C21">
         <v>30</v>
@@ -5671,37 +6399,37 @@
       <c r="F21">
         <v>300</v>
       </c>
-      <c r="G21" t="str">
-        <v>[61.88593, 62.62872]</v>
-      </c>
-      <c r="H21" t="str">
-        <v>[9.063721, 10.26672]</v>
+      <c r="G21" t="s">
+        <v>221</v>
+      </c>
+      <c r="H21" t="s">
+        <v>222</v>
       </c>
       <c r="I21">
-        <v>0.00004</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="J21">
-        <v>0.000265</v>
+        <v>2.6499999999999999E-4</v>
       </c>
       <c r="K21">
-        <v>3.9e-9</v>
-      </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
-      <c r="M21" t="str">
-        <v/>
+        <v>3.9000000000000002E-9</v>
+      </c>
+      <c r="L21" t="s">
+        <v>173</v>
+      </c>
+      <c r="M21" t="s">
+        <v>173</v>
       </c>
       <c r="N21">
         <v>600</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A22">
         <v>6801</v>
       </c>
-      <c r="B22" t="str">
-        <v>NO3</v>
+      <c r="B22" t="s">
+        <v>17</v>
       </c>
       <c r="C22">
         <v>179</v>
@@ -5715,37 +6443,37 @@
       <c r="F22">
         <v>380</v>
       </c>
-      <c r="G22" t="str">
-        <v>[62.628719, 63.035662]</v>
-      </c>
-      <c r="H22" t="str">
-        <v>[10.26672, 11.72791]</v>
+      <c r="G22" t="s">
+        <v>223</v>
+      </c>
+      <c r="H22" t="s">
+        <v>224</v>
       </c>
       <c r="I22">
-        <v>0.00003000000000000001</v>
+        <v>3.0000000000000011E-5</v>
       </c>
       <c r="J22">
-        <v>0.000246</v>
+        <v>2.4600000000000002E-4</v>
       </c>
       <c r="K22">
-        <v>4.1e-9</v>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <v/>
+        <v>4.1000000000000003E-9</v>
+      </c>
+      <c r="L22" t="s">
+        <v>173</v>
+      </c>
+      <c r="M22" t="s">
+        <v>173</v>
       </c>
       <c r="N22">
         <v>600</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.6">
       <c r="A23">
         <v>6802</v>
       </c>
-      <c r="B23" t="str">
-        <v>NO3</v>
+      <c r="B23" t="s">
+        <v>17</v>
       </c>
       <c r="C23">
         <v>108</v>
@@ -5759,69 +6487,71 @@
       <c r="F23">
         <v>380</v>
       </c>
-      <c r="G23" t="str">
-        <v>[63.035662, 64.453849]</v>
-      </c>
-      <c r="H23" t="str">
-        <v>[11.72791, 11.62079]</v>
+      <c r="G23" t="s">
+        <v>225</v>
+      </c>
+      <c r="H23" t="s">
+        <v>226</v>
       </c>
       <c r="I23">
-        <v>0.00003000000000000001</v>
+        <v>3.0000000000000011E-5</v>
       </c>
       <c r="J23">
-        <v>0.000246</v>
+        <v>2.4600000000000002E-4</v>
       </c>
       <c r="K23">
-        <v>4.1e-9</v>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v/>
+        <v>4.1000000000000003E-9</v>
+      </c>
+      <c r="L23" t="s">
+        <v>173</v>
+      </c>
+      <c r="M23" t="s">
+        <v>173</v>
       </c>
       <c r="N23">
         <v>600</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N23"/>
+    <ignoredError sqref="A1:N23" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>transformer_id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>bus0</v>
-      </c>
-      <c r="C1" t="str">
-        <v>bus1</v>
-      </c>
-      <c r="D1" t="str">
-        <v>ratio</v>
-      </c>
-      <c r="E1" t="str">
-        <v>R</v>
-      </c>
-      <c r="F1" t="str">
-        <v>X</v>
-      </c>
-      <c r="G1" t="str">
-        <v>name</v>
-      </c>
-      <c r="H1" t="str">
-        <v>S_max</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+      <c r="A1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>43</v>
       </c>
@@ -5832,22 +6562,22 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>0.7894736842105263</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="E2">
-        <v>0.0005600000000000001</v>
+        <v>5.6000000000000006E-4</v>
       </c>
       <c r="F2">
-        <v>0.028</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Klæbu transformatorstasjon – Klæbu transformatorstasjon</v>
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>231</v>
       </c>
       <c r="H2">
         <v>300</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>44</v>
       </c>
@@ -5861,19 +6591,19 @@
         <v>0.44</v>
       </c>
       <c r="E3">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="F3">
         <v>0.04</v>
       </c>
-      <c r="G3" t="str">
-        <v>Thamshavn trafostasjon – Orkdal transformatorstasjon</v>
+      <c r="G3" t="s">
+        <v>232</v>
       </c>
       <c r="H3">
         <v>300</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A4">
         <v>45</v>
       </c>
@@ -5887,19 +6617,19 @@
         <v>0.3473684210526316</v>
       </c>
       <c r="E4">
-        <v>0.0005600000000000001</v>
+        <v>5.6000000000000006E-4</v>
       </c>
       <c r="F4">
-        <v>0.028</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Ørskog trafostasjon – Ørskog trafostasjon</v>
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>233</v>
       </c>
       <c r="H4">
         <v>300</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A5">
         <v>46</v>
       </c>
@@ -5910,22 +6640,22 @@
         <v>61</v>
       </c>
       <c r="D5">
-        <v>0.7894736842105263</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="E5">
-        <v>0.0005600000000000001</v>
+        <v>5.6000000000000006E-4</v>
       </c>
       <c r="F5">
-        <v>0.028</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Aura trafostasjon – Viklandet trafostasjon</v>
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>234</v>
       </c>
       <c r="H5">
         <v>300</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>47</v>
       </c>
@@ -5939,19 +6669,19 @@
         <v>0.44</v>
       </c>
       <c r="E6">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="F6">
         <v>0.04</v>
       </c>
-      <c r="G6" t="str">
-        <v>Svelgen transformatorstasjon 132/300 kV</v>
+      <c r="G6" t="s">
+        <v>235</v>
       </c>
       <c r="H6">
         <v>300</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>48</v>
       </c>
@@ -5965,19 +6695,19 @@
         <v>0.44</v>
       </c>
       <c r="E7">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="F7">
         <v>0.04</v>
       </c>
-      <c r="G7" t="str">
-        <v>Brattset transformatorstasjon 132/300 kV</v>
+      <c r="G7" t="s">
+        <v>236</v>
       </c>
       <c r="H7">
         <v>300</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>49</v>
       </c>
@@ -5988,22 +6718,22 @@
         <v>179</v>
       </c>
       <c r="D8">
-        <v>0.347368</v>
+        <v>0.34736800000000001</v>
       </c>
       <c r="E8">
-        <v>0.00056</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="F8">
-        <v>0.028</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Brattset transformatorstasjon 132/380 kV</v>
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>237</v>
       </c>
       <c r="H8">
         <v>300</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>50</v>
       </c>
@@ -6014,16 +6744,16 @@
         <v>180</v>
       </c>
       <c r="D9">
-        <v>0.789474</v>
+        <v>0.78947400000000001</v>
       </c>
       <c r="E9">
-        <v>0.00056</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="F9">
-        <v>0.028</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Namsos transformatorstasjon 300/380 kV</v>
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>238</v>
       </c>
       <c r="H9">
         <v>300</v>
@@ -6032,48 +6762,49 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
+    <ignoredError sqref="A1:H9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>index</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>area0</v>
-      </c>
-      <c r="D1" t="str">
-        <v>area1</v>
-      </c>
-      <c r="E1" t="str">
-        <v>bus0</v>
-      </c>
-      <c r="F1" t="str">
-        <v>bus1</v>
-      </c>
-      <c r="G1" t="str">
-        <v>lat</v>
-      </c>
-      <c r="H1" t="str">
-        <v>lon</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Pinj</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+    <ignoredError sqref="A1:I1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>